--- a/Horarios/HorarioWAN_2026.xlsx
+++ b/Horarios/HorarioWAN_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecmx-my.sharepoint.com/personal/lperezf_tec_mx/Documents/Documents/GitLiz/WAN/Horarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="256" documentId="8_{553C0AF3-C17A-445D-8D11-BFA3025DB648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3273BE82-E5A0-4D62-9187-698DA76DA924}"/>
+  <xr:revisionPtr revIDLastSave="270" documentId="8_{553C0AF3-C17A-445D-8D11-BFA3025DB648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25BFB41A-EACB-4911-BF6F-EA6CCCE16A2C}"/>
   <bookViews>
-    <workbookView xWindow="28635" yWindow="-165" windowWidth="29130" windowHeight="15810" activeTab="2" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
   </bookViews>
   <sheets>
     <sheet name="WAN_201" sheetId="5" r:id="rId1"/>
@@ -338,7 +338,7 @@
     <t>PRESENTACIÓN DE LA PROPUESTA DE SOLUCIÓN AL RETO / EVALUACIÓN DEL RETO</t>
   </si>
   <si>
-    <t>Martes, miércoles y jueves (5:30 - 8:00) | Viernes (5:00 - 7:00)</t>
+    <t>Lunes, martes y jueves (5:30 - 8:00) | Viernes (5:00 - 7:00)</t>
   </si>
 </sst>
 </file>
@@ -533,9 +533,112 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -545,110 +648,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -989,10 +991,10 @@
       <c r="B1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="M1" s="45" t="s">
+      <c r="M1" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="N1" s="45" t="s">
+      <c r="N1" s="9" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1018,19 +1020,19 @@
       <c r="B3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="12" t="s">
+      <c r="D3" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="12" t="s">
+      <c r="F3" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="47" t="s">
         <v>18</v>
       </c>
       <c r="I3" s="1"/>
@@ -1041,7 +1043,7 @@
         <f>2.5+2.5+2.5+2.5+2</f>
         <v>12</v>
       </c>
-      <c r="M3" s="45">
+      <c r="M3" s="9">
         <f>K3</f>
         <v>12</v>
       </c>
@@ -1050,11 +1052,11 @@
       <c r="B4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="12"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="47"/>
       <c r="I4" s="1"/>
       <c r="J4" t="s">
         <v>12</v>
@@ -1071,11 +1073,11 @@
       <c r="B5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="9" t="s">
+      <c r="C5" s="43"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="43" t="s">
         <v>22</v>
       </c>
       <c r="J5" t="s">
@@ -1085,13 +1087,13 @@
         <f>2.5+2</f>
         <v>4.5</v>
       </c>
-      <c r="M5" s="47">
-        <v>2.5</v>
+      <c r="M5" s="10">
+        <v>1.5</v>
       </c>
       <c r="N5" s="2">
         <v>4.5</v>
       </c>
-      <c r="O5" s="48" t="s">
+      <c r="O5" s="11" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1099,38 +1101,38 @@
       <c r="B6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="12" t="s">
+      <c r="E6" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="9"/>
+      <c r="G6" s="43"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="9"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="43"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.35">
@@ -1160,19 +1162,19 @@
       <c r="B12" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="15" t="s">
+      <c r="C12" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="9" t="s">
+      <c r="F12" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="43" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="1"/>
@@ -1191,11 +1193,11 @@
       <c r="B13" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="9"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="43"/>
       <c r="J13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1210,15 +1212,15 @@
       <c r="B14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="17"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="29" t="s">
+      <c r="D14" s="35"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="28" t="s">
+      <c r="G14" s="44" t="s">
         <v>23</v>
       </c>
       <c r="J14" t="s">
@@ -1236,13 +1238,13 @@
       <c r="B15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="15" t="s">
+      <c r="C15" s="36"/>
+      <c r="D15" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="19"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="28"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="44"/>
       <c r="J15" t="s">
         <v>15</v>
       </c>
@@ -1257,13 +1259,13 @@
       <c r="B16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="16"/>
-      <c r="G16" s="28"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="36"/>
+      <c r="G16" s="44"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
@@ -1271,10 +1273,10 @@
       <c r="B17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="17"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="35"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.35">
@@ -1304,19 +1306,19 @@
       <c r="B21" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="32" t="s">
+      <c r="C21" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="20" t="s">
+      <c r="D21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="F21" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="20" t="s">
+      <c r="F21" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="22" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="1"/>
@@ -1335,11 +1337,11 @@
       <c r="B22" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C22" s="33"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="21"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="23"/>
       <c r="I22" s="1"/>
       <c r="J22" t="s">
         <v>12</v>
@@ -1356,23 +1358,23 @@
       <c r="B23" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="34"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="26" t="s">
+      <c r="C23" s="39"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="21"/>
+      <c r="G23" s="23"/>
       <c r="J23" s="1" t="s">
         <v>31</v>
       </c>
       <c r="K23" s="1">
         <v>4.5</v>
       </c>
-      <c r="M23" s="47">
+      <c r="M23" s="10">
         <v>4.5</v>
       </c>
-      <c r="O23" s="48" t="s">
+      <c r="O23" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1380,13 +1382,13 @@
       <c r="B24" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="34"/>
-      <c r="D24" s="29" t="s">
+      <c r="C24" s="39"/>
+      <c r="D24" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="16"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="21"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="23"/>
       <c r="J24" t="s">
         <v>32</v>
       </c>
@@ -1402,21 +1404,21 @@
       <c r="B25" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="34"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="22"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="24"/>
       <c r="O25" s="1"/>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="35"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="35"/>
       <c r="G26" s="6"/>
       <c r="O26" s="1"/>
     </row>
@@ -1452,19 +1454,19 @@
       <c r="B30" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="29" t="s">
+      <c r="C30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="20" t="s">
+      <c r="F30" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="22" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="1"/>
@@ -1484,11 +1486,11 @@
       <c r="B31" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="38"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="21"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="23"/>
       <c r="J31" t="s">
         <v>12</v>
       </c>
@@ -1505,27 +1507,27 @@
       <c r="B32" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="38"/>
-      <c r="E32" s="20" t="s">
+      <c r="D32" s="16"/>
+      <c r="E32" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="23" t="s">
+      <c r="F32" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="21"/>
+      <c r="G32" s="23"/>
       <c r="J32" s="1" t="s">
         <v>31</v>
       </c>
       <c r="K32" s="1">
         <v>2</v>
       </c>
-      <c r="M32" s="47">
+      <c r="M32" s="10">
         <v>2</v>
       </c>
-      <c r="O32" s="48" t="s">
+      <c r="O32" s="11" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1533,14 +1535,14 @@
       <c r="B33" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="30"/>
-      <c r="D33" s="29" t="s">
+      <c r="C33" s="25"/>
+      <c r="D33" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="36"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="21"/>
-      <c r="J33" s="46" t="s">
+      <c r="E33" s="26"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="23"/>
+      <c r="J33" t="s">
         <v>32</v>
       </c>
       <c r="K33" s="1">
@@ -1555,21 +1557,21 @@
       <c r="B34" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="22"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="24"/>
       <c r="O34" s="1"/>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="37"/>
-      <c r="F35" s="25"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="30"/>
       <c r="G35" s="6"/>
       <c r="O35" s="1"/>
     </row>
@@ -1605,19 +1607,19 @@
       <c r="B39" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C39" s="43" t="s">
+      <c r="C39" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="20" t="s">
+      <c r="D39" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="20" t="s">
+      <c r="F39" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="G39" s="40" t="s">
+      <c r="G39" s="12" t="s">
         <v>16</v>
       </c>
       <c r="I39" s="1"/>
@@ -1637,11 +1639,11 @@
       <c r="B40" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C40" s="44"/>
-      <c r="D40" s="39"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="21"/>
-      <c r="G40" s="41"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="13"/>
       <c r="I40" s="1"/>
       <c r="J40" t="s">
         <v>12</v>
@@ -1658,13 +1660,13 @@
       <c r="B41" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C41" s="26" t="s">
+      <c r="C41" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="38"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="21"/>
-      <c r="G41" s="41"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="36"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="13"/>
       <c r="I41" s="1"/>
       <c r="J41" t="s">
         <v>15</v>
@@ -1672,15 +1674,14 @@
       <c r="K41">
         <v>12</v>
       </c>
-      <c r="M41" s="47">
-        <f>2.5+5</f>
-        <v>7.5</v>
+      <c r="M41" s="10">
+        <v>4.5</v>
       </c>
       <c r="N41" s="2">
         <f>2+2.5+5</f>
         <v>9.5</v>
       </c>
-      <c r="O41" s="48" t="s">
+      <c r="O41" s="11" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1688,33 +1689,33 @@
       <c r="B42" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C42" s="27"/>
-      <c r="D42" s="29" t="s">
+      <c r="C42" s="34"/>
+      <c r="D42" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="16"/>
-      <c r="F42" s="21"/>
-      <c r="G42" s="41"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="13"/>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C43" s="27"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="21"/>
-      <c r="G43" s="42"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="14"/>
       <c r="K43" s="1">
         <f>SUM(K3:K41)</f>
         <v>111</v>
       </c>
       <c r="L43" s="1"/>
-      <c r="M43" s="45">
+      <c r="M43" s="9">
         <f>SUM(M3:M41)</f>
-        <v>63.5</v>
-      </c>
-      <c r="N43" s="45">
+        <v>59.5</v>
+      </c>
+      <c r="N43" s="9">
         <f>SUM(N3:N41)</f>
         <v>55</v>
       </c>
@@ -1723,10 +1724,10 @@
       <c r="B44" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C44" s="17"/>
-      <c r="D44" s="31"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="22"/>
+      <c r="C44" s="35"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="35"/>
+      <c r="F44" s="24"/>
       <c r="G44" s="6"/>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.35">
@@ -1868,10 +1869,10 @@
       <c r="B1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="M1" s="45" t="s">
+      <c r="M1" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="N1" s="45" t="s">
+      <c r="N1" s="9" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1897,19 +1898,19 @@
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="12" t="s">
+      <c r="D3" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="12" t="s">
+      <c r="F3" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="47" t="s">
         <v>18</v>
       </c>
       <c r="I3" s="1"/>
@@ -1920,7 +1921,7 @@
         <f>2.5+2.5+2.5+2.5+2</f>
         <v>12</v>
       </c>
-      <c r="M3" s="45">
+      <c r="M3" s="9">
         <f>K3</f>
         <v>12</v>
       </c>
@@ -1929,11 +1930,11 @@
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="12"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="47"/>
       <c r="I4" s="1"/>
       <c r="J4" t="s">
         <v>12</v>
@@ -1950,11 +1951,11 @@
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="9" t="s">
+      <c r="C5" s="43"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="43" t="s">
         <v>22</v>
       </c>
       <c r="J5" t="s">
@@ -1964,13 +1965,13 @@
         <f>2.5+2</f>
         <v>4.5</v>
       </c>
-      <c r="M5" s="47">
-        <v>2.5</v>
+      <c r="M5" s="10">
+        <v>1.5</v>
       </c>
       <c r="N5" s="2">
         <v>4.5</v>
       </c>
-      <c r="O5" s="48" t="s">
+      <c r="O5" s="11" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1978,38 +1979,38 @@
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="12" t="s">
+      <c r="E6" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="9"/>
+      <c r="G6" s="43"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="9"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="43"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.35">
@@ -2039,19 +2040,19 @@
       <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="15" t="s">
+      <c r="C12" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="9" t="s">
+      <c r="F12" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="43" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="1"/>
@@ -2070,11 +2071,11 @@
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="9"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="43"/>
       <c r="J13" s="1" t="s">
         <v>14</v>
       </c>
@@ -2089,15 +2090,15 @@
       <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="17"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="29" t="s">
+      <c r="D14" s="35"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="28" t="s">
+      <c r="G14" s="44" t="s">
         <v>23</v>
       </c>
       <c r="J14" t="s">
@@ -2115,13 +2116,13 @@
       <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="15" t="s">
+      <c r="C15" s="36"/>
+      <c r="D15" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="19"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="28"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="44"/>
       <c r="J15" t="s">
         <v>15</v>
       </c>
@@ -2136,13 +2137,13 @@
       <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="16"/>
-      <c r="G16" s="28"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="36"/>
+      <c r="G16" s="44"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
@@ -2150,10 +2151,10 @@
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="17"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="35"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.35">
@@ -2183,19 +2184,19 @@
       <c r="B21" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="32" t="s">
+      <c r="C21" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="20" t="s">
+      <c r="D21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="F21" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="20" t="s">
+      <c r="F21" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="22" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="1"/>
@@ -2214,11 +2215,11 @@
       <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="33"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="21"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="23"/>
       <c r="I22" s="1"/>
       <c r="J22" t="s">
         <v>12</v>
@@ -2235,23 +2236,23 @@
       <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="34"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="26" t="s">
+      <c r="C23" s="39"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="21"/>
+      <c r="G23" s="23"/>
       <c r="J23" s="1" t="s">
         <v>31</v>
       </c>
       <c r="K23" s="1">
         <v>4.5</v>
       </c>
-      <c r="M23" s="47">
+      <c r="M23" s="10">
         <v>4.5</v>
       </c>
-      <c r="O23" s="48" t="s">
+      <c r="O23" s="11" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2259,13 +2260,13 @@
       <c r="B24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="34"/>
-      <c r="D24" s="29" t="s">
+      <c r="C24" s="39"/>
+      <c r="D24" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="16"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="21"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="23"/>
       <c r="J24" t="s">
         <v>32</v>
       </c>
@@ -2281,21 +2282,21 @@
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="34"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="22"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="24"/>
       <c r="O25" s="1"/>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="35"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="35"/>
       <c r="G26" s="6"/>
       <c r="O26" s="1"/>
     </row>
@@ -2331,19 +2332,19 @@
       <c r="B30" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="29" t="s">
+      <c r="C30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="20" t="s">
+      <c r="F30" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="22" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="1"/>
@@ -2363,11 +2364,11 @@
       <c r="B31" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="38"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="21"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="23"/>
       <c r="J31" t="s">
         <v>12</v>
       </c>
@@ -2384,27 +2385,27 @@
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="38"/>
-      <c r="E32" s="20" t="s">
+      <c r="D32" s="16"/>
+      <c r="E32" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="23" t="s">
+      <c r="F32" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="21"/>
+      <c r="G32" s="23"/>
       <c r="J32" s="1" t="s">
         <v>31</v>
       </c>
       <c r="K32" s="1">
         <v>2</v>
       </c>
-      <c r="M32" s="47">
+      <c r="M32" s="10">
         <v>2</v>
       </c>
-      <c r="O32" s="48" t="s">
+      <c r="O32" s="11" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2412,14 +2413,14 @@
       <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="30"/>
-      <c r="D33" s="29" t="s">
+      <c r="C33" s="25"/>
+      <c r="D33" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="36"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="21"/>
-      <c r="J33" s="46" t="s">
+      <c r="E33" s="26"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="23"/>
+      <c r="J33" t="s">
         <v>32</v>
       </c>
       <c r="K33" s="1">
@@ -2434,21 +2435,21 @@
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="22"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="24"/>
       <c r="O34" s="1"/>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="37"/>
-      <c r="F35" s="25"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="30"/>
       <c r="G35" s="6"/>
       <c r="O35" s="1"/>
     </row>
@@ -2484,19 +2485,19 @@
       <c r="B39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="43" t="s">
+      <c r="C39" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="20" t="s">
+      <c r="D39" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="20" t="s">
+      <c r="F39" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="G39" s="40" t="s">
+      <c r="G39" s="12" t="s">
         <v>16</v>
       </c>
       <c r="I39" s="1"/>
@@ -2516,11 +2517,11 @@
       <c r="B40" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="44"/>
-      <c r="D40" s="39"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="21"/>
-      <c r="G40" s="41"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="13"/>
       <c r="I40" s="1"/>
       <c r="J40" t="s">
         <v>12</v>
@@ -2537,13 +2538,13 @@
       <c r="B41" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="26" t="s">
+      <c r="C41" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="38"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="21"/>
-      <c r="G41" s="41"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="36"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="13"/>
       <c r="I41" s="1"/>
       <c r="J41" t="s">
         <v>15</v>
@@ -2551,15 +2552,15 @@
       <c r="K41">
         <v>12</v>
       </c>
-      <c r="M41" s="47">
-        <f>2.5+5</f>
-        <v>7.5</v>
+      <c r="M41" s="10">
+        <f>4.5</f>
+        <v>4.5</v>
       </c>
       <c r="N41" s="2">
         <f>2+2.5+5</f>
         <v>9.5</v>
       </c>
-      <c r="O41" s="48" t="s">
+      <c r="O41" s="11" t="s">
         <v>47</v>
       </c>
     </row>
@@ -2567,33 +2568,33 @@
       <c r="B42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="27"/>
-      <c r="D42" s="29" t="s">
+      <c r="C42" s="34"/>
+      <c r="D42" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="16"/>
-      <c r="F42" s="21"/>
-      <c r="G42" s="41"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="13"/>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="27"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="21"/>
-      <c r="G43" s="42"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="14"/>
       <c r="K43" s="1">
         <f>SUM(K3:K41)</f>
         <v>111</v>
       </c>
       <c r="L43" s="1"/>
-      <c r="M43" s="45">
+      <c r="M43" s="9">
         <f>SUM(M3:M41)</f>
-        <v>63.5</v>
-      </c>
-      <c r="N43" s="45">
+        <v>59.5</v>
+      </c>
+      <c r="N43" s="9">
         <f>SUM(N3:N41)</f>
         <v>55</v>
       </c>
@@ -2602,10 +2603,10 @@
       <c r="B44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="17"/>
-      <c r="D44" s="31"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="22"/>
+      <c r="C44" s="35"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="35"/>
+      <c r="F44" s="24"/>
       <c r="G44" s="6"/>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.35">
@@ -2748,10 +2749,10 @@
       <c r="B1" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="M1" s="45" t="s">
+      <c r="M1" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="N1" s="45" t="s">
+      <c r="N1" s="9" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2777,19 +2778,19 @@
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="12" t="s">
+      <c r="D3" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="12" t="s">
+      <c r="F3" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="47" t="s">
         <v>18</v>
       </c>
       <c r="I3" s="1"/>
@@ -2800,7 +2801,7 @@
         <f>2.5+2.5+2.5+2.5+2</f>
         <v>12</v>
       </c>
-      <c r="M3" s="45">
+      <c r="M3" s="9">
         <f>K3</f>
         <v>12</v>
       </c>
@@ -2809,11 +2810,11 @@
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="12"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="47"/>
       <c r="I4" s="1"/>
       <c r="J4" t="s">
         <v>12</v>
@@ -2830,11 +2831,11 @@
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="9" t="s">
+      <c r="C5" s="43"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="43" t="s">
         <v>22</v>
       </c>
       <c r="J5" t="s">
@@ -2844,13 +2845,13 @@
         <f>2.5+2</f>
         <v>4.5</v>
       </c>
-      <c r="M5" s="47">
+      <c r="M5" s="10">
         <v>2.5</v>
       </c>
       <c r="N5" s="2">
         <v>4.5</v>
       </c>
-      <c r="O5" s="48" t="s">
+      <c r="O5" s="11" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2858,38 +2859,38 @@
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="12" t="s">
+      <c r="E6" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="9"/>
+      <c r="G6" s="43"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="9"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="43"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.35">
@@ -2919,19 +2920,19 @@
       <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="15" t="s">
+      <c r="C12" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="9" t="s">
+      <c r="F12" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="43" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="1"/>
@@ -2950,11 +2951,11 @@
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="9"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="43"/>
       <c r="J13" s="1" t="s">
         <v>14</v>
       </c>
@@ -2969,15 +2970,15 @@
       <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="17"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="29" t="s">
+      <c r="D14" s="35"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="28" t="s">
+      <c r="G14" s="44" t="s">
         <v>23</v>
       </c>
       <c r="J14" t="s">
@@ -2995,13 +2996,13 @@
       <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="15" t="s">
+      <c r="C15" s="36"/>
+      <c r="D15" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="19"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="28"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="44"/>
       <c r="J15" t="s">
         <v>15</v>
       </c>
@@ -3016,13 +3017,13 @@
       <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="16"/>
-      <c r="G16" s="28"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="36"/>
+      <c r="G16" s="44"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
@@ -3030,10 +3031,10 @@
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="17"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="35"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.35">
@@ -3063,19 +3064,19 @@
       <c r="B21" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="20" t="s">
+      <c r="C21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="F21" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="20" t="s">
+      <c r="F21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="22" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="1"/>
@@ -3094,11 +3095,11 @@
       <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="21"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="23"/>
       <c r="I22" s="1"/>
       <c r="J22" t="s">
         <v>12</v>
@@ -3115,25 +3116,25 @@
       <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="26" t="s">
+      <c r="C23" s="35"/>
+      <c r="D23" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="16"/>
-      <c r="F23" s="29" t="s">
+      <c r="E23" s="36"/>
+      <c r="F23" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="21"/>
+      <c r="G23" s="23"/>
       <c r="J23" s="1" t="s">
         <v>31</v>
       </c>
       <c r="K23" s="1">
         <v>4.5</v>
       </c>
-      <c r="M23" s="47">
+      <c r="M23" s="10">
         <v>4.5</v>
       </c>
-      <c r="O23" s="48" t="s">
+      <c r="O23" s="11" t="s">
         <v>45</v>
       </c>
     </row>
@@ -3141,13 +3142,13 @@
       <c r="B24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="27"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="21"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="23"/>
       <c r="J24" t="s">
         <v>32</v>
       </c>
@@ -3163,21 +3164,21 @@
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="30"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="22"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="24"/>
       <c r="O25" s="1"/>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="31"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="31"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="6"/>
       <c r="O26" s="1"/>
     </row>
@@ -3213,19 +3214,19 @@
       <c r="B30" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="29" t="s">
+      <c r="C30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="20" t="s">
+      <c r="F30" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="22" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="1"/>
@@ -3245,11 +3246,11 @@
       <c r="B31" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="21"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="23"/>
       <c r="J31" t="s">
         <v>12</v>
       </c>
@@ -3266,25 +3267,25 @@
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="38"/>
-      <c r="D32" s="38"/>
-      <c r="E32" s="20" t="s">
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="23" t="s">
+      <c r="F32" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="21"/>
+      <c r="G32" s="23"/>
       <c r="J32" s="1" t="s">
         <v>31</v>
       </c>
       <c r="K32" s="1">
         <v>2</v>
       </c>
-      <c r="M32" s="47">
+      <c r="M32" s="10">
         <v>2</v>
       </c>
-      <c r="O32" s="48" t="s">
+      <c r="O32" s="11" t="s">
         <v>46</v>
       </c>
     </row>
@@ -3292,16 +3293,16 @@
       <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C33" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="29" t="s">
+      <c r="D33" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="36"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="21"/>
-      <c r="J33" s="46" t="s">
+      <c r="E33" s="26"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="23"/>
+      <c r="J33" t="s">
         <v>32</v>
       </c>
       <c r="K33" s="1">
@@ -3316,21 +3317,21 @@
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="22"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="24"/>
       <c r="O34" s="1"/>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="37"/>
-      <c r="F35" s="25"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="30"/>
       <c r="G35" s="6"/>
       <c r="O35" s="1"/>
     </row>
@@ -3366,19 +3367,19 @@
       <c r="B39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="43" t="s">
+      <c r="C39" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="20" t="s">
+      <c r="D39" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="20" t="s">
+      <c r="E39" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F39" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39" s="20" t="s">
+      <c r="G39" s="22" t="s">
         <v>58</v>
       </c>
       <c r="I39" s="1"/>
@@ -3397,11 +3398,11 @@
       <c r="B40" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="44"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="21"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="36"/>
+      <c r="E40" s="48"/>
+      <c r="F40" s="36"/>
+      <c r="G40" s="23"/>
       <c r="I40" s="1"/>
       <c r="J40" t="s">
         <v>12</v>
@@ -3418,13 +3419,11 @@
       <c r="B41" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="21"/>
+      <c r="C41" s="36"/>
+      <c r="D41" s="36"/>
+      <c r="E41" s="48"/>
+      <c r="F41" s="36"/>
+      <c r="G41" s="23"/>
       <c r="I41" s="1"/>
       <c r="J41" t="s">
         <v>15</v>
@@ -3433,7 +3432,7 @@
         <f>2+5+5+5+4</f>
         <v>21</v>
       </c>
-      <c r="M41" s="47">
+      <c r="M41" s="10">
         <f>2.5+2.5+2.5+2</f>
         <v>9.5</v>
       </c>
@@ -3441,7 +3440,7 @@
         <f>2+2.5*3+4</f>
         <v>13.5</v>
       </c>
-      <c r="O41" s="48" t="s">
+      <c r="O41" s="11" t="s">
         <v>59</v>
       </c>
     </row>
@@ -3449,31 +3448,33 @@
       <c r="B42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="27"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="21"/>
+      <c r="C42" s="36"/>
+      <c r="D42" s="36"/>
+      <c r="E42" s="48"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="23"/>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="27"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="22"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="36"/>
+      <c r="E43" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="F43" s="36"/>
+      <c r="G43" s="24"/>
       <c r="K43" s="1">
         <f>SUM(K3:K41)</f>
         <v>120</v>
       </c>
       <c r="L43" s="1"/>
-      <c r="M43" s="45">
+      <c r="M43" s="9">
         <f>SUM(M3:M41)</f>
         <v>67</v>
       </c>
-      <c r="N43" s="45">
+      <c r="N43" s="9">
         <f>SUM(N3:N41)</f>
         <v>61.5</v>
       </c>
@@ -3482,10 +3483,10 @@
       <c r="B44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="17"/>
+      <c r="C44" s="35"/>
+      <c r="D44" s="35"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="35"/>
       <c r="G44" s="6"/>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.35">
@@ -3549,15 +3550,15 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="C39:C44"/>
+    <mergeCell ref="E39:E42"/>
+    <mergeCell ref="E43:E44"/>
     <mergeCell ref="D23:D26"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C33:C35"/>
     <mergeCell ref="D39:D44"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="E39:E44"/>
     <mergeCell ref="F39:F44"/>
     <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C41:C44"/>
     <mergeCell ref="D30:D32"/>
     <mergeCell ref="E30:E31"/>
     <mergeCell ref="F30:F31"/>

--- a/Horarios/HorarioWAN_2026.xlsx
+++ b/Horarios/HorarioWAN_2026.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecmx-my.sharepoint.com/personal/lperezf_tec_mx/Documents/Documents/GitLiz/WAN/Horarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="270" documentId="8_{553C0AF3-C17A-445D-8D11-BFA3025DB648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25BFB41A-EACB-4911-BF6F-EA6CCCE16A2C}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{FC23BDE9-CBF9-4CD9-B661-15FDB57BE38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93327C75-AB24-471B-A2C7-4F71A4952D9D}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
   </bookViews>
   <sheets>
     <sheet name="WAN_201" sheetId="5" r:id="rId1"/>
-    <sheet name="WAN_301" sheetId="7" r:id="rId2"/>
-    <sheet name="WAN_501" sheetId="8" r:id="rId3"/>
+    <sheet name="WAN_202" sheetId="7" r:id="rId2"/>
+    <sheet name="WAN_301" sheetId="8" r:id="rId3"/>
+    <sheet name="WAN_201_Completo" sheetId="9" r:id="rId4"/>
+    <sheet name="WAN_202_COMPLETO" sheetId="10" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="64">
   <si>
     <t>3:00 - 4:00</t>
   </si>
@@ -110,9 +112,6 @@
   </si>
   <si>
     <t>EXAMEN MÓDULO 1</t>
-  </si>
-  <si>
-    <t>PRESENTACIÓN DEL RETO CON EL SOCIO FORMADOR / RETO</t>
   </si>
   <si>
     <t>Liz</t>
@@ -338,14 +337,33 @@
     <t>PRESENTACIÓN DE LA PROPUESTA DE SOLUCIÓN AL RETO / EVALUACIÓN DEL RETO</t>
   </si>
   <si>
-    <t>Lunes, martes y jueves (5:30 - 8:00) | Viernes (5:00 - 7:00)</t>
+    <t>Faby</t>
+  </si>
+  <si>
+    <t>Martes a jueves de 6:00 a 8:00 p.m. y viernes de 5:00 a 7:00 p.m. o en el horario que sea la presentación del reto.</t>
+  </si>
+  <si>
+    <t>Lunes (3:00 - 4:30)</t>
+  </si>
+  <si>
+    <t>PRESENTACIÓN DEL RETO</t>
+  </si>
+  <si>
+    <t>Visita BOHN
+                           Módulo 1
+Módulo 1</t>
+  </si>
+  <si>
+    <t>Módulo 1                                               
+                                 Visita                           
+                                 BOHN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -369,8 +387,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -413,8 +454,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <gradientFill degree="45">
+        <stop position="0">
+          <color theme="9" tint="-0.25098422193060094"/>
+        </stop>
+        <stop position="1">
+          <color theme="7" tint="0.80001220740379042"/>
+        </stop>
+      </gradientFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -505,11 +562,54 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border diagonalUp="1">
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal style="thin">
+        <color indexed="64"/>
+      </diagonal>
+    </border>
+    <border diagonalUp="1">
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal style="thin">
+        <color indexed="64"/>
+      </diagonal>
+    </border>
+    <border diagonalUp="1">
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal style="thin">
+        <color indexed="64"/>
+      </diagonal>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -540,6 +640,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -549,6 +662,24 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -570,85 +701,73 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -671,6 +790,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -973,7 +1096,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:O54"/>
+  <dimension ref="B1:I44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -983,22 +1106,14 @@
     <col min="6" max="6" width="17.1796875" style="2" customWidth="1"/>
     <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
     <col min="8" max="8" width="4.36328125" customWidth="1"/>
-    <col min="10" max="10" width="15.7265625" customWidth="1"/>
-    <col min="13" max="14" width="10.90625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B1" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="M1" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="N1" s="9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B2" s="4"/>
       <c r="C2" s="3" t="s">
         <v>6</v>
@@ -1016,131 +1131,94 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="47" t="s">
+      <c r="C4" s="14"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="52"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="51" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="47" t="s">
+      <c r="D6" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="1">
-        <f>2.5+2.5+2.5+2.5+2</f>
-        <v>12</v>
-      </c>
-      <c r="M3" s="9">
-        <f>K3</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="43"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="47"/>
-      <c r="I4" s="1"/>
-      <c r="J4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K4">
-        <f>2.5+2.5+2.5</f>
-        <v>7.5</v>
-      </c>
-      <c r="N4" s="2">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="43"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5">
-        <f>2.5+2</f>
-        <v>4.5</v>
-      </c>
-      <c r="M5" s="10">
-        <v>1.5</v>
-      </c>
-      <c r="N5" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B6" s="3" t="s">
+      <c r="E6" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="53"/>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="47" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="47" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="47" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="43"/>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="52"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="43"/>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="46"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
       <c r="G8" s="5"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B10" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B11" s="4"/>
       <c r="C11" s="3" t="s">
         <v>6</v>
@@ -1158,133 +1236,93 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="26" t="s">
         <v>19</v>
       </c>
       <c r="E12" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="43" t="s">
+      <c r="F12" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="15" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="1"/>
-      <c r="J12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K12" s="1">
-        <f>3+2.5+3+2</f>
-        <v>10.5</v>
-      </c>
-      <c r="M12" s="2">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="32"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="15"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B14" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="43"/>
-      <c r="J13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="1">
-        <v>3</v>
-      </c>
-      <c r="M13" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B14" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="C14" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="35"/>
+      <c r="D14" s="22"/>
       <c r="E14" s="42"/>
-      <c r="F14" s="18" t="s">
+      <c r="F14" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="44" t="s">
+      <c r="G14" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="J14" t="s">
-        <v>12</v>
-      </c>
-      <c r="K14">
-        <f>2+2.5+2+2</f>
-        <v>8.5</v>
-      </c>
-      <c r="N14" s="2">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="36"/>
+        <v>37</v>
+      </c>
+      <c r="C15" s="40"/>
       <c r="D15" s="41" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="42"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="44"/>
-      <c r="J15" t="s">
-        <v>15</v>
-      </c>
-      <c r="K15">
-        <v>2</v>
-      </c>
-      <c r="N15" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="F15" s="40"/>
+      <c r="G15" s="43"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="40"/>
+      <c r="G16" s="43"/>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="36"/>
-      <c r="G16" s="44"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B17" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="35"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="22"/>
       <c r="G17" s="6"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B19" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B20" s="4"/>
       <c r="C20" s="3" t="s">
         <v>6</v>
@@ -1302,136 +1340,92 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="44" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="22" t="s">
+      <c r="C22" s="45"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="14"/>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="46"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K21" s="1">
-        <f>2.5+3</f>
-        <v>5.5</v>
-      </c>
-      <c r="M21" s="2">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B22" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" s="38"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="23"/>
-      <c r="I22" s="1"/>
-      <c r="J22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K22">
-        <f>2.5+2</f>
-        <v>4.5</v>
-      </c>
-      <c r="N22" s="2">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="23" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="3" t="s">
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="39"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="33" t="s">
+      <c r="C24" s="46"/>
+      <c r="D24" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="23"/>
-      <c r="J23" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K23" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="M23" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="O23" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B24" s="3" t="s">
+      <c r="E24" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="21"/>
+      <c r="G24" s="15"/>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="39"/>
-      <c r="D24" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="36"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="23"/>
-      <c r="J24" t="s">
-        <v>32</v>
-      </c>
-      <c r="K24">
-        <v>4.5</v>
-      </c>
-      <c r="N24" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="O24" s="1"/>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="46"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="15"/>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="39"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="24"/>
-      <c r="O25" s="1"/>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B26" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C26" s="40"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="22"/>
       <c r="G26" s="6"/>
-      <c r="O26" s="1"/>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="O27" s="1"/>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B28" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O28" s="1"/>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B29" s="4"/>
       <c r="C29" s="3" t="s">
         <v>6</v>
@@ -1448,143 +1442,94 @@
       <c r="G29" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="O29" s="1"/>
-    </row>
-    <row r="30" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="1"/>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B31" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="18" t="s">
+      <c r="C31" s="27"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="14"/>
+    </row>
+    <row r="32" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="22" t="s">
+      <c r="D32" s="27"/>
+      <c r="E32" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K30" s="1">
-        <f>3+2.5+2+3</f>
-        <v>10.5</v>
-      </c>
-      <c r="M30" s="2">
-        <v>10.5</v>
-      </c>
-      <c r="O30" s="1"/>
-    </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B31" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="23"/>
-      <c r="J31" t="s">
-        <v>12</v>
-      </c>
-      <c r="K31">
-        <f>2+2.5+2</f>
-        <v>6.5</v>
-      </c>
-      <c r="N31" s="2">
-        <v>6.5</v>
-      </c>
-      <c r="O31" s="1"/>
-    </row>
-    <row r="32" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="3" t="s">
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B33" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C33" s="33"/>
+      <c r="D33" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="16"/>
-      <c r="E32" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32" s="23"/>
-      <c r="J32" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K32" s="1">
-        <v>2</v>
-      </c>
-      <c r="M32" s="10">
-        <v>2</v>
-      </c>
-      <c r="O32" s="11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B33" s="3" t="s">
+      <c r="E33" s="35"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="15"/>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B34" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="25"/>
-      <c r="D33" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="26"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="23"/>
-      <c r="J33" t="s">
-        <v>32</v>
-      </c>
-      <c r="K33" s="1">
-        <v>5</v>
-      </c>
-      <c r="N33" s="2">
-        <v>5</v>
-      </c>
-      <c r="O33" s="1"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="15"/>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B35" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="29"/>
-      <c r="G34" s="24"/>
-      <c r="O34" s="1"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B35" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="39"/>
       <c r="G35" s="6"/>
-      <c r="O35" s="1"/>
-    </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="O36" s="1"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B37" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="O37" s="1"/>
-    </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B38" s="4"/>
       <c r="C38" s="3" t="s">
         <v>6</v>
@@ -1601,202 +1546,88 @@
       <c r="G38" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="O38" s="1"/>
-    </row>
-    <row r="39" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="39" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="1"/>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B40" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C39" s="31" t="s">
+      <c r="C40" s="15"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="18"/>
+      <c r="I40" s="1"/>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B41" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="27"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="18"/>
+      <c r="I41" s="1"/>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C42" s="21"/>
+      <c r="D42" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="G39" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K39" s="1">
-        <f>3+2.5</f>
-        <v>5.5</v>
-      </c>
-      <c r="M39" s="2">
-        <v>5.5</v>
-      </c>
-      <c r="O39" s="1"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B40" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C40" s="32"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="13"/>
-      <c r="I40" s="1"/>
-      <c r="J40" t="s">
-        <v>12</v>
-      </c>
-      <c r="K40">
-        <v>2.5</v>
-      </c>
-      <c r="N40" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="O40" s="1"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B41" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C41" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41" s="16"/>
-      <c r="E41" s="36"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="13"/>
-      <c r="I41" s="1"/>
-      <c r="J41" t="s">
-        <v>15</v>
-      </c>
-      <c r="K41">
-        <v>12</v>
-      </c>
-      <c r="M41" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="N41" s="2">
-        <f>2+2.5+5</f>
-        <v>9.5</v>
-      </c>
-      <c r="O41" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B42" s="3" t="s">
+      <c r="F42" s="24"/>
+      <c r="G42" s="18"/>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C42" s="34"/>
-      <c r="D42" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" s="36"/>
-      <c r="F42" s="23"/>
-      <c r="G42" s="13"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B43" s="3" t="s">
+      <c r="C43" s="21"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="19"/>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C43" s="34"/>
-      <c r="D43" s="25"/>
-      <c r="E43" s="36"/>
-      <c r="F43" s="23"/>
-      <c r="G43" s="14"/>
-      <c r="K43" s="1">
-        <f>SUM(K3:K41)</f>
-        <v>111</v>
-      </c>
-      <c r="L43" s="1"/>
-      <c r="M43" s="9">
-        <f>SUM(M3:M41)</f>
-        <v>59.5</v>
-      </c>
-      <c r="N43" s="9">
-        <f>SUM(N3:N41)</f>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B44" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C44" s="35"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="35"/>
-      <c r="F44" s="24"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="25"/>
       <c r="G44" s="6"/>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K46">
-        <f>5*4*5</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K47">
-        <f>4*5</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K48">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="49" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="K49">
-        <f>120-5-4</f>
-        <v>111</v>
-      </c>
-    </row>
-    <row r="50" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J50" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K50" s="1">
-        <f>K3+K12</f>
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="51" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J51" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K51" s="1">
-        <f>K13+K21+K30+K39</f>
-        <v>24.5</v>
-      </c>
-    </row>
-    <row r="52" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J52" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K52" s="1">
-        <f>K4+K14+K22+K31+K40</f>
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="53" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J53" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K53" s="1">
-        <f>K5+K15+K23+K24+K32+K33+K41</f>
-        <v>34.5</v>
-      </c>
-    </row>
-    <row r="54" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="K54">
-        <f>SUM(K50:K53)</f>
-        <v>111</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="43">
+  <mergeCells count="47">
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="E3:E5"/>
@@ -1807,6 +1638,8 @@
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="E6:E8"/>
     <mergeCell ref="F6:F8"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="G23:G25"/>
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="D12:D14"/>
     <mergeCell ref="E12:E15"/>
@@ -1819,27 +1652,29 @@
     <mergeCell ref="E16:E17"/>
     <mergeCell ref="C21:C26"/>
     <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E26"/>
     <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G25"/>
     <mergeCell ref="F23:F26"/>
     <mergeCell ref="D24:D26"/>
-    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="F39:F44"/>
     <mergeCell ref="C30:C31"/>
     <mergeCell ref="D30:D32"/>
     <mergeCell ref="E30:E31"/>
     <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G34"/>
     <mergeCell ref="C32:C35"/>
     <mergeCell ref="E32:E35"/>
     <mergeCell ref="F32:F35"/>
     <mergeCell ref="D33:D35"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="E39:E44"/>
-    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="G39:G43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1851,7 +1686,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:O54"/>
+  <dimension ref="B1:G44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -1861,22 +1696,14 @@
     <col min="6" max="6" width="17.1796875" style="2" customWidth="1"/>
     <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
     <col min="8" max="8" width="4.36328125" customWidth="1"/>
-    <col min="10" max="10" width="15.7265625" customWidth="1"/>
-    <col min="13" max="14" width="10.90625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B1" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="M1" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="N1" s="9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B2" s="4"/>
       <c r="C2" s="3" t="s">
         <v>6</v>
@@ -1894,131 +1721,92 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="47" t="s">
+      <c r="D3" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="47" t="s">
+      <c r="F3" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="1">
-        <f>2.5+2.5+2.5+2.5+2</f>
-        <v>12</v>
-      </c>
-      <c r="M3" s="9">
-        <f>K3</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="43"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="47"/>
-      <c r="I4" s="1"/>
-      <c r="J4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K4">
-        <f>2.5+2.5+2.5</f>
-        <v>7.5</v>
-      </c>
-      <c r="N4" s="2">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="C4" s="14"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="50"/>
+    </row>
+    <row r="5" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="43"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="43" t="s">
+      <c r="C5" s="14"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="J5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5">
-        <f>2.5+2</f>
-        <v>4.5</v>
-      </c>
-      <c r="M5" s="10">
-        <v>1.5</v>
-      </c>
-      <c r="N5" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="47" t="s">
+      <c r="E6" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="43"/>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="G6" s="15"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="43"/>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="15"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="46"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
       <c r="G8" s="5"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="4"/>
       <c r="C11" s="3" t="s">
         <v>6</v>
@@ -2036,133 +1824,92 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="15" t="s">
+      <c r="C12" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="26" t="s">
         <v>19</v>
       </c>
       <c r="E12" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="43" t="s">
+      <c r="F12" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K12" s="1">
-        <f>3+2.5+3+2</f>
-        <v>10.5</v>
-      </c>
-      <c r="M12" s="2">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="36"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="40"/>
       <c r="E13" s="42"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="43"/>
-      <c r="J13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="1">
-        <v>3</v>
-      </c>
-      <c r="M13" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="F13" s="32"/>
+      <c r="G13" s="15"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C14" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="35"/>
+      <c r="D14" s="22"/>
       <c r="E14" s="42"/>
-      <c r="F14" s="18" t="s">
+      <c r="F14" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="44" t="s">
+      <c r="G14" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="J14" t="s">
-        <v>12</v>
-      </c>
-      <c r="K14">
-        <f>2+2.5+2+2</f>
-        <v>8.5</v>
-      </c>
-      <c r="N14" s="2">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="36"/>
+      <c r="C15" s="40"/>
       <c r="D15" s="41" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="42"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="44"/>
-      <c r="J15" t="s">
-        <v>15</v>
-      </c>
-      <c r="K15">
-        <v>2</v>
-      </c>
-      <c r="N15" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="F15" s="40"/>
+      <c r="G15" s="43"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="36"/>
-      <c r="G16" s="44"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="40"/>
+      <c r="G16" s="43"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="35"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="22"/>
       <c r="G17" s="6"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B19" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B20" s="4"/>
       <c r="C20" s="3" t="s">
         <v>6</v>
@@ -2180,136 +1927,90 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="37" t="s">
+      <c r="C21" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="22" t="s">
+      <c r="D21" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K21" s="1">
-        <f>2.5+3</f>
-        <v>5.5</v>
-      </c>
-      <c r="M21" s="2">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="38"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="23"/>
-      <c r="I22" s="1"/>
-      <c r="J22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K22">
-        <f>2.5+2</f>
-        <v>4.5</v>
-      </c>
-      <c r="N22" s="2">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="23" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C22" s="45"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="14"/>
+    </row>
+    <row r="23" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="39"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="33" t="s">
+      <c r="C23" s="46"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="23"/>
-      <c r="J23" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K23" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="M23" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="O23" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="G23" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="39"/>
-      <c r="D24" s="18" t="s">
+      <c r="C24" s="46"/>
+      <c r="D24" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="36"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="23"/>
-      <c r="J24" t="s">
-        <v>32</v>
-      </c>
-      <c r="K24">
-        <v>4.5</v>
-      </c>
-      <c r="N24" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="O24" s="1"/>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="E24" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="21"/>
+      <c r="G24" s="15"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="39"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="24"/>
-      <c r="O25" s="1"/>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="C25" s="46"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="15"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="40"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="22"/>
       <c r="G26" s="6"/>
-      <c r="O26" s="1"/>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="O27" s="1"/>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B28" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O28" s="1"/>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B29" s="4"/>
       <c r="C29" s="3" t="s">
         <v>6</v>
@@ -2326,143 +2027,93 @@
       <c r="G29" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="O29" s="1"/>
-    </row>
-    <row r="30" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="18" t="s">
+      <c r="C30" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="22" t="s">
+      <c r="F30" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K30" s="1">
-        <f>3+2.5+2+3</f>
-        <v>10.5</v>
-      </c>
-      <c r="M30" s="2">
-        <v>10.5</v>
-      </c>
-      <c r="O30" s="1"/>
-    </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B31" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="23"/>
-      <c r="J31" t="s">
-        <v>12</v>
-      </c>
-      <c r="K31">
-        <f>2+2.5+2</f>
-        <v>6.5</v>
-      </c>
-      <c r="N31" s="2">
-        <v>6.5</v>
-      </c>
-      <c r="O31" s="1"/>
-    </row>
-    <row r="32" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C31" s="27"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="14"/>
+    </row>
+    <row r="32" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="16"/>
-      <c r="E32" s="22" t="s">
+      <c r="D32" s="27"/>
+      <c r="E32" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="28" t="s">
+      <c r="F32" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="23"/>
-      <c r="J32" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K32" s="1">
-        <v>2</v>
-      </c>
-      <c r="M32" s="10">
-        <v>2</v>
-      </c>
-      <c r="O32" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="G32" s="15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="25"/>
-      <c r="D33" s="18" t="s">
+      <c r="C33" s="33"/>
+      <c r="D33" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="26"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="23"/>
-      <c r="J33" t="s">
-        <v>32</v>
-      </c>
-      <c r="K33" s="1">
-        <v>5</v>
-      </c>
-      <c r="N33" s="2">
-        <v>5</v>
-      </c>
-      <c r="O33" s="1"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="E33" s="35"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="15"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="29"/>
-      <c r="G34" s="24"/>
-      <c r="O34" s="1"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="15"/>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="39"/>
       <c r="G35" s="6"/>
-      <c r="O35" s="1"/>
-    </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="O36" s="1"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B37" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="O37" s="1"/>
-    </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B38" s="4"/>
       <c r="C38" s="3" t="s">
         <v>6</v>
@@ -2479,226 +2130,112 @@
       <c r="G38" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="O38" s="1"/>
-    </row>
-    <row r="39" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="39" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="31" t="s">
+      <c r="C39" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="22" t="s">
+      <c r="D39" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="G39" s="12" t="s">
+      <c r="F39" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K39" s="1">
-        <f>3+2.5</f>
-        <v>5.5</v>
-      </c>
-      <c r="M39" s="2">
-        <v>5.5</v>
-      </c>
-      <c r="O39" s="1"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B40" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="32"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="13"/>
-      <c r="I40" s="1"/>
-      <c r="J40" t="s">
-        <v>12</v>
-      </c>
-      <c r="K40">
-        <v>2.5</v>
-      </c>
-      <c r="N40" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="O40" s="1"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="C40" s="15"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="18"/>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="33" t="s">
+      <c r="C41" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="16"/>
-      <c r="E41" s="36"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="13"/>
-      <c r="I41" s="1"/>
-      <c r="J41" t="s">
-        <v>15</v>
-      </c>
-      <c r="K41">
-        <v>12</v>
-      </c>
-      <c r="M41" s="10">
-        <f>4.5</f>
-        <v>4.5</v>
-      </c>
-      <c r="N41" s="2">
-        <f>2+2.5+5</f>
-        <v>9.5</v>
-      </c>
-      <c r="O41" s="11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="D41" s="27"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="18"/>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="34"/>
-      <c r="D42" s="18" t="s">
+      <c r="C42" s="21"/>
+      <c r="D42" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="36"/>
-      <c r="F42" s="23"/>
-      <c r="G42" s="13"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="E42" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="24"/>
+      <c r="G42" s="18"/>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="34"/>
-      <c r="D43" s="25"/>
-      <c r="E43" s="36"/>
-      <c r="F43" s="23"/>
-      <c r="G43" s="14"/>
-      <c r="K43" s="1">
-        <f>SUM(K3:K41)</f>
-        <v>111</v>
-      </c>
-      <c r="L43" s="1"/>
-      <c r="M43" s="9">
-        <f>SUM(M3:M41)</f>
-        <v>59.5</v>
-      </c>
-      <c r="N43" s="9">
-        <f>SUM(N3:N41)</f>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="C43" s="21"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="19"/>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="35"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="35"/>
-      <c r="F44" s="24"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="25"/>
       <c r="G44" s="6"/>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K46">
-        <f>5*4*5</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K47">
-        <f>4*5</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K48">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="49" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="K49">
-        <f>120-5-4</f>
-        <v>111</v>
-      </c>
-    </row>
-    <row r="50" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J50" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K50" s="1">
-        <f>K3+K12</f>
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="51" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J51" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K51" s="1">
-        <f>K13+K21+K30+K39</f>
-        <v>24.5</v>
-      </c>
-    </row>
-    <row r="52" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J52" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K52" s="1">
-        <f>K4+K14+K22+K31+K40</f>
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="53" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J53" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K53" s="1">
-        <f>K5+K15+K23+K24+K32+K33+K41</f>
-        <v>34.5</v>
-      </c>
-    </row>
-    <row r="54" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="K54">
-        <f>SUM(K50:K53)</f>
-        <v>111</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="43">
+  <mergeCells count="47">
     <mergeCell ref="C39:C40"/>
     <mergeCell ref="D39:D41"/>
-    <mergeCell ref="E39:E44"/>
     <mergeCell ref="F39:F44"/>
     <mergeCell ref="G39:G43"/>
     <mergeCell ref="C41:C44"/>
     <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="G23:G25"/>
     <mergeCell ref="C30:C31"/>
     <mergeCell ref="D30:D32"/>
     <mergeCell ref="E30:E31"/>
     <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G34"/>
     <mergeCell ref="C32:C35"/>
     <mergeCell ref="E32:E35"/>
     <mergeCell ref="F32:F35"/>
     <mergeCell ref="D33:D35"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="G32:G34"/>
     <mergeCell ref="C21:C26"/>
     <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E26"/>
     <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G25"/>
     <mergeCell ref="F23:F26"/>
     <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="E24:E26"/>
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="D12:D14"/>
     <mergeCell ref="E12:E15"/>
@@ -2730,7 +2267,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:O54"/>
+  <dimension ref="B1:P54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -2742,18 +2279,913 @@
     <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
     <col min="8" max="8" width="4.36328125" customWidth="1"/>
     <col min="10" max="10" width="15.7265625" customWidth="1"/>
+    <col min="13" max="15" width="10.90625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="O1" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B2" s="4"/>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="1">
+        <f>2.5+2.5+2.5+2.5+2</f>
+        <v>12</v>
+      </c>
+      <c r="M3" s="9">
+        <f>K3</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="50"/>
+      <c r="I4" s="1"/>
+      <c r="J4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4">
+        <f>2.5+2.5+2.5</f>
+        <v>7.5</v>
+      </c>
+      <c r="N4" s="2">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5">
+        <f>2.5+2</f>
+        <v>4.5</v>
+      </c>
+      <c r="M5" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="N5" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="P5" s="11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="15"/>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="15"/>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="5"/>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B10" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B11" s="4"/>
+      <c r="C11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" s="1">
+        <f>3+2.5+3+2</f>
+        <v>10.5</v>
+      </c>
+      <c r="M12" s="2">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="32"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="15"/>
+      <c r="J13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" s="1">
+        <v>3</v>
+      </c>
+      <c r="M13" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="22"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14">
+        <f>2+2.5+2+2</f>
+        <v>8.5</v>
+      </c>
+      <c r="N14" s="2">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="40"/>
+      <c r="D15" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="42"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="43"/>
+      <c r="J15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="N15" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="40"/>
+      <c r="G16" s="43"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="6"/>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B19" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B20" s="4"/>
+      <c r="C20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K21" s="1">
+        <f>3+3+2.5</f>
+        <v>8.5</v>
+      </c>
+      <c r="M21" s="2">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="40"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="14"/>
+      <c r="I22" s="1"/>
+      <c r="J22" t="s">
+        <v>12</v>
+      </c>
+      <c r="K22">
+        <f>2.5+4</f>
+        <v>6.5</v>
+      </c>
+      <c r="N22" s="2">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="22"/>
+      <c r="D23" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="16"/>
+      <c r="F23" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K23" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="M23" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="P23" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="21"/>
+      <c r="E24" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="33"/>
+      <c r="G24" s="15"/>
+      <c r="J24" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24">
+        <v>4.5</v>
+      </c>
+      <c r="N24" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B25" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="33"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="15"/>
+      <c r="P25" s="1"/>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="30"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="6"/>
+      <c r="P26" s="1"/>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="P27" s="1"/>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B28" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B29" s="4"/>
+      <c r="C29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="P29" s="1"/>
+    </row>
+    <row r="30" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K30" s="1">
+        <f>2.5+2.5+2+3</f>
+        <v>10</v>
+      </c>
+      <c r="M30" s="2">
+        <v>10</v>
+      </c>
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="14"/>
+      <c r="J31" t="s">
+        <v>12</v>
+      </c>
+      <c r="K31">
+        <f>2.5+2.5+2</f>
+        <v>7</v>
+      </c>
+      <c r="N31" s="2">
+        <v>7</v>
+      </c>
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K32" s="1">
+        <v>2</v>
+      </c>
+      <c r="M32" s="10">
+        <v>2</v>
+      </c>
+      <c r="P32" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="35"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="15"/>
+      <c r="J33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K33" s="1">
+        <v>5</v>
+      </c>
+      <c r="N33" s="2">
+        <v>5</v>
+      </c>
+      <c r="P33" s="1"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B34" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="15"/>
+      <c r="P34" s="1"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="6"/>
+      <c r="P35" s="1"/>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="P36" s="1"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B37" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="P37" s="1"/>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B38" s="4"/>
+      <c r="C38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="P38" s="1"/>
+    </row>
+    <row r="39" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K39" s="1">
+        <v>3</v>
+      </c>
+      <c r="M39" s="2">
+        <v>3</v>
+      </c>
+      <c r="P39" s="1"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="24"/>
+      <c r="I40" s="1"/>
+      <c r="J40" t="s">
+        <v>12</v>
+      </c>
+      <c r="K40">
+        <v>2.5</v>
+      </c>
+      <c r="N40" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="P40" s="1"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="15"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="24"/>
+      <c r="I41" s="1"/>
+      <c r="J41" t="s">
+        <v>15</v>
+      </c>
+      <c r="K41">
+        <v>18.5</v>
+      </c>
+      <c r="M41" s="10"/>
+      <c r="N41" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="O41" s="12">
+        <v>8</v>
+      </c>
+      <c r="P41" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="21"/>
+      <c r="D42" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" s="24"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" s="21"/>
+      <c r="D43" s="54"/>
+      <c r="E43" s="54"/>
+      <c r="F43" s="54"/>
+      <c r="G43" s="25"/>
+      <c r="K43" s="1">
+        <f>SUM(K3:K41)</f>
+        <v>120</v>
+      </c>
+      <c r="L43" s="1"/>
+      <c r="M43" s="9">
+        <f>SUM(M3:M41)</f>
+        <v>54</v>
+      </c>
+      <c r="N43" s="9">
+        <f>SUM(N3:N41)</f>
+        <v>58.5</v>
+      </c>
+      <c r="O43" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="22"/>
+      <c r="D44" s="55"/>
+      <c r="E44" s="55"/>
+      <c r="F44" s="55"/>
+      <c r="G44" s="6"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="K46">
+        <f>5*4*5</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="K47">
+        <f>4*5</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="K48">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="50" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J50" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K50" s="1">
+        <f>K3+K12</f>
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="51" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J51" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K51" s="1">
+        <f>K13+K21+K30+K39</f>
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="52" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J52" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K52" s="1">
+        <f>K4+K14+K22+K31+K40</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="53" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J53" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K53" s="1">
+        <f>K5+K15+K23+K24+K32+K33+K41</f>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="54" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="K54">
+        <f>SUM(K50:K53)</f>
+        <v>120</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="49">
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="F39:F41"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="D23:D26"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="E24:E26"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{335AC7A1-686F-4ADB-B09E-7B24D320AEEC}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:O54"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="2" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" style="2" customWidth="1"/>
+    <col min="3" max="4" width="12.6328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.7265625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="4.36328125" customWidth="1"/>
+    <col min="10" max="10" width="13.6328125" customWidth="1"/>
     <col min="13" max="14" width="10.90625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B1" s="8" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="2:15" x14ac:dyDescent="0.35">
@@ -2776,22 +3208,22 @@
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="47" t="s">
+      <c r="D3" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="47" t="s">
-        <v>18</v>
+      <c r="F3" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="51" t="s">
+        <v>62</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
@@ -2808,13 +3240,13 @@
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="43"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="47"/>
+        <v>35</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="52"/>
       <c r="I4" s="1"/>
       <c r="J4" t="s">
         <v>12</v>
@@ -2829,14 +3261,14 @@
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="43"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="43" t="s">
-        <v>22</v>
+        <v>36</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="51" t="s">
+        <v>63</v>
       </c>
       <c r="J5" t="s">
         <v>15</v>
@@ -2846,56 +3278,56 @@
         <v>4.5</v>
       </c>
       <c r="M5" s="10">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="N5" s="2">
         <v>4.5</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="47" t="s">
+      <c r="E6" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="43"/>
+      <c r="G6" s="53"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="43"/>
+        <v>38</v>
+      </c>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="52"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="46"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
+        <v>39</v>
+      </c>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B10" s="8" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.35">
@@ -2918,21 +3350,21 @@
     </row>
     <row r="12" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="26" t="s">
         <v>19</v>
       </c>
       <c r="E12" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="43" t="s">
+      <c r="F12" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="15" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="1"/>
@@ -2949,13 +3381,13 @@
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B13" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="36"/>
+        <v>35</v>
+      </c>
+      <c r="C13" s="32"/>
+      <c r="D13" s="40"/>
       <c r="E13" s="42"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="43"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="15"/>
       <c r="J13" s="1" t="s">
         <v>14</v>
       </c>
@@ -2968,17 +3400,17 @@
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="C14" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="35"/>
+      <c r="D14" s="22"/>
       <c r="E14" s="42"/>
-      <c r="F14" s="18" t="s">
+      <c r="F14" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="44" t="s">
+      <c r="G14" s="43" t="s">
         <v>23</v>
       </c>
       <c r="J14" t="s">
@@ -2994,15 +3426,15 @@
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="36"/>
+        <v>37</v>
+      </c>
+      <c r="C15" s="40"/>
       <c r="D15" s="41" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="42"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="44"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="43"/>
       <c r="J15" t="s">
         <v>15</v>
       </c>
@@ -3015,31 +3447,31 @@
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="36"/>
-      <c r="G16" s="44"/>
+        <v>38</v>
+      </c>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="40"/>
+      <c r="G16" s="43"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="35"/>
+        <v>39</v>
+      </c>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="22"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B19" s="8" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.35">
@@ -3060,23 +3492,23 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="44" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="14" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="1"/>
@@ -3084,49 +3516,49 @@
         <v>14</v>
       </c>
       <c r="K21" s="1">
-        <f>3+3+2.5</f>
-        <v>8.5</v>
+        <f>2.5+3</f>
+        <v>5.5</v>
       </c>
       <c r="M21" s="2">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B22" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="23"/>
+        <v>35</v>
+      </c>
+      <c r="C22" s="45"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="14"/>
       <c r="I22" s="1"/>
       <c r="J22" t="s">
         <v>12</v>
       </c>
       <c r="K22">
-        <f>2.5+4</f>
-        <v>6.5</v>
+        <f>2.5+2</f>
+        <v>4.5</v>
       </c>
       <c r="N22" s="2">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="23" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="35"/>
-      <c r="D23" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="46"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="36"/>
-      <c r="F23" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="23"/>
+      <c r="G23" s="15" t="s">
+        <v>13</v>
+      </c>
       <c r="J23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K23" s="1">
         <v>4.5</v>
@@ -3135,22 +3567,24 @@
         <v>4.5</v>
       </c>
       <c r="O23" s="11" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="46"/>
+      <c r="D24" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="34"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="23"/>
+      <c r="E24" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="21"/>
+      <c r="G24" s="15"/>
       <c r="J24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K24">
         <v>4.5</v>
@@ -3162,23 +3596,23 @@
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="25"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="24"/>
+        <v>38</v>
+      </c>
+      <c r="C25" s="46"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="15"/>
       <c r="O25" s="1"/>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="19"/>
+        <v>39</v>
+      </c>
+      <c r="C26" s="47"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="22"/>
       <c r="G26" s="6"/>
       <c r="O26" s="1"/>
     </row>
@@ -3187,7 +3621,7 @@
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B28" s="8" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="O28" s="1"/>
     </row>
@@ -3212,21 +3646,21 @@
     </row>
     <row r="30" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="22" t="s">
+      <c r="F30" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="14" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="1"/>
@@ -3234,50 +3668,54 @@
         <v>14</v>
       </c>
       <c r="K30" s="1">
-        <f>2.5+2.5+2+3</f>
-        <v>10</v>
+        <f>3+2.5+2+3</f>
+        <v>10.5</v>
       </c>
       <c r="M30" s="2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="O30" s="1"/>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B31" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="23"/>
+        <v>35</v>
+      </c>
+      <c r="C31" s="27"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="14"/>
       <c r="J31" t="s">
         <v>12</v>
       </c>
       <c r="K31">
-        <f>2.5+2.5+2</f>
-        <v>7</v>
+        <f>2+2.5+2</f>
+        <v>6.5</v>
       </c>
       <c r="N31" s="2">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="O31" s="1"/>
     </row>
     <row r="32" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="27"/>
+      <c r="E32" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="28" t="s">
+      <c r="F32" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="23"/>
+      <c r="G32" s="15" t="s">
+        <v>22</v>
+      </c>
       <c r="J32" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K32" s="1">
         <v>2</v>
@@ -3286,24 +3724,22 @@
         <v>2</v>
       </c>
       <c r="O32" s="11" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="33"/>
+      <c r="D33" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="26"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="23"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="15"/>
       <c r="J33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K33" s="1">
         <v>5</v>
@@ -3315,23 +3751,23 @@
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="29"/>
-      <c r="G34" s="24"/>
+        <v>38</v>
+      </c>
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="15"/>
       <c r="O34" s="1"/>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="30"/>
+        <v>39</v>
+      </c>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="39"/>
       <c r="G35" s="6"/>
       <c r="O35" s="1"/>
     </row>
@@ -3340,7 +3776,7 @@
     </row>
     <row r="37" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B37" s="8" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="O37" s="1"/>
     </row>
@@ -3365,29 +3801,30 @@
     </row>
     <row r="39" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C39" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="22" t="s">
+      <c r="D39" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="F39" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39" s="22" t="s">
-        <v>58</v>
+      <c r="F39" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39" s="17" t="s">
+        <v>16</v>
       </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1" t="s">
         <v>14</v>
       </c>
       <c r="K39" s="1">
-        <v>3</v>
+        <f>3+2.5</f>
+        <v>5.5</v>
       </c>
       <c r="M39" s="2">
         <v>5.5</v>
@@ -3396,19 +3833,19 @@
     </row>
     <row r="40" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B40" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="36"/>
-      <c r="D40" s="36"/>
-      <c r="E40" s="48"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="23"/>
+        <v>35</v>
+      </c>
+      <c r="C40" s="15"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="18"/>
       <c r="I40" s="1"/>
       <c r="J40" t="s">
         <v>12</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="N40" s="2">
         <v>2.5</v>
@@ -3417,76 +3854,78 @@
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="36"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="48"/>
-      <c r="F41" s="36"/>
-      <c r="G41" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="27"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="18"/>
       <c r="I41" s="1"/>
       <c r="J41" t="s">
         <v>15</v>
       </c>
       <c r="K41">
-        <f>2+5+5+5+4</f>
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="M41" s="10">
-        <f>2.5+2.5+2.5+2</f>
+        <v>4.5</v>
+      </c>
+      <c r="N41" s="2">
+        <f>2+2.5+5</f>
         <v>9.5</v>
       </c>
-      <c r="N41" s="2">
-        <f>2+2.5*3+4</f>
-        <v>13.5</v>
-      </c>
       <c r="O41" s="11" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C42" s="36"/>
-      <c r="D42" s="36"/>
-      <c r="E42" s="48"/>
-      <c r="F42" s="36"/>
-      <c r="G42" s="23"/>
+        <v>37</v>
+      </c>
+      <c r="C42" s="21"/>
+      <c r="D42" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="24"/>
+      <c r="G42" s="18"/>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C43" s="36"/>
-      <c r="D43" s="36"/>
-      <c r="E43" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F43" s="36"/>
-      <c r="G43" s="24"/>
+        <v>38</v>
+      </c>
+      <c r="C43" s="21"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="19"/>
       <c r="K43" s="1">
         <f>SUM(K3:K41)</f>
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="9">
         <f>SUM(M3:M41)</f>
-        <v>67</v>
+        <v>59.5</v>
       </c>
       <c r="N43" s="9">
         <f>SUM(N3:N41)</f>
-        <v>61.5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C44" s="35"/>
-      <c r="D44" s="35"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="35"/>
+        <v>39</v>
+      </c>
+      <c r="C44" s="22"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="25"/>
       <c r="G44" s="6"/>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.35">
@@ -3506,9 +3945,15 @@
         <v>120</v>
       </c>
     </row>
+    <row r="49" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="K49">
+        <f>120-5-4</f>
+        <v>111</v>
+      </c>
+    </row>
     <row r="50" spans="10:11" x14ac:dyDescent="0.35">
       <c r="J50" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K50" s="1">
         <f>K3+K12</f>
@@ -3517,7 +3962,7 @@
     </row>
     <row r="51" spans="10:11" x14ac:dyDescent="0.35">
       <c r="J51" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K51" s="1">
         <f>K13+K21+K30+K39</f>
@@ -3526,7 +3971,7 @@
     </row>
     <row r="52" spans="10:11" x14ac:dyDescent="0.35">
       <c r="J52" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K52" s="1">
         <f>K4+K14+K22+K31+K40</f>
@@ -3535,44 +3980,939 @@
     </row>
     <row r="53" spans="10:11" x14ac:dyDescent="0.35">
       <c r="J53" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K53" s="1">
         <f>K5+K15+K23+K24+K32+K33+K41</f>
-        <v>43.5</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="54" spans="10:11" x14ac:dyDescent="0.35">
       <c r="K54">
         <f>SUM(K50:K53)</f>
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="43">
-    <mergeCell ref="C39:C44"/>
-    <mergeCell ref="E39:E42"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="D23:D26"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="D39:D44"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="G39:G43"/>
+  <mergeCells count="47">
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C21:C26"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="C30:C31"/>
     <mergeCell ref="D30:D32"/>
     <mergeCell ref="E30:E31"/>
     <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G34"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="C32:C35"/>
     <mergeCell ref="E32:E35"/>
     <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G32:G34"/>
     <mergeCell ref="D33:D35"/>
-    <mergeCell ref="E21:E26"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B72F34B-8139-4D0E-8882-03145DDD5E1F}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:O54"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="2" customWidth="1"/>
+    <col min="2" max="2" width="10.90625" style="2"/>
+    <col min="3" max="4" width="12.6328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.7265625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="4.36328125" customWidth="1"/>
+    <col min="10" max="10" width="15.7265625" customWidth="1"/>
+    <col min="13" max="14" width="10.90625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B1" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B2" s="4"/>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="1">
+        <f>2.5+2.5+2.5+2.5+2</f>
+        <v>12</v>
+      </c>
+      <c r="M3" s="9">
+        <f>K3</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="50"/>
+      <c r="I4" s="1"/>
+      <c r="J4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4">
+        <f>2.5+2.5+2.5</f>
+        <v>7.5</v>
+      </c>
+      <c r="N4" s="2">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5">
+        <f>2.5+2</f>
+        <v>4.5</v>
+      </c>
+      <c r="M5" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="N5" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="15"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="15"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="5"/>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B10" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B11" s="4"/>
+      <c r="C11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" s="1">
+        <f>3+2.5+3+2</f>
+        <v>10.5</v>
+      </c>
+      <c r="M12" s="2">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="32"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="15"/>
+      <c r="J13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" s="1">
+        <v>3</v>
+      </c>
+      <c r="M13" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="22"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14">
+        <f>2+2.5+2+2</f>
+        <v>8.5</v>
+      </c>
+      <c r="N14" s="2">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="40"/>
+      <c r="D15" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="42"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="43"/>
+      <c r="J15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="N15" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="40"/>
+      <c r="G16" s="43"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="6"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B19" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B20" s="4"/>
+      <c r="C20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="44" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K21" s="1">
+        <f>2.5+3</f>
+        <v>5.5</v>
+      </c>
+      <c r="M21" s="2">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="45"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="14"/>
+      <c r="I22" s="1"/>
+      <c r="J22" t="s">
+        <v>12</v>
+      </c>
+      <c r="K22">
+        <f>2.5+2</f>
+        <v>4.5</v>
+      </c>
+      <c r="N22" s="2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="46"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K23" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="M23" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="O23" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="46"/>
+      <c r="D24" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="21"/>
+      <c r="G24" s="15"/>
+      <c r="J24" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24">
+        <v>4.5</v>
+      </c>
+      <c r="N24" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O24" s="1"/>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B25" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="46"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="15"/>
+      <c r="O25" s="1"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="47"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="6"/>
+      <c r="O26" s="1"/>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="O27" s="1"/>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B28" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="O28" s="1"/>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B29" s="4"/>
+      <c r="C29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O29" s="1"/>
+    </row>
+    <row r="30" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K30" s="1">
+        <f>3+2.5+2+3</f>
+        <v>10.5</v>
+      </c>
+      <c r="M30" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="O30" s="1"/>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="27"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="14"/>
+      <c r="J31" t="s">
+        <v>12</v>
+      </c>
+      <c r="K31">
+        <f>2+2.5+2</f>
+        <v>6.5</v>
+      </c>
+      <c r="N31" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="O31" s="1"/>
+    </row>
+    <row r="32" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="27"/>
+      <c r="E32" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K32" s="1">
+        <v>2</v>
+      </c>
+      <c r="M32" s="10">
+        <v>2</v>
+      </c>
+      <c r="O32" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="33"/>
+      <c r="D33" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="35"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="15"/>
+      <c r="J33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K33" s="1">
+        <v>5</v>
+      </c>
+      <c r="N33" s="2">
+        <v>5</v>
+      </c>
+      <c r="O33" s="1"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B34" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="15"/>
+      <c r="O34" s="1"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="6"/>
+      <c r="O35" s="1"/>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="O36" s="1"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B37" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O37" s="1"/>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B38" s="4"/>
+      <c r="C38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O38" s="1"/>
+    </row>
+    <row r="39" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K39" s="1">
+        <f>3+2.5</f>
+        <v>5.5</v>
+      </c>
+      <c r="M39" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="O39" s="1"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="15"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="18"/>
+      <c r="I40" s="1"/>
+      <c r="J40" t="s">
+        <v>12</v>
+      </c>
+      <c r="K40">
+        <v>2.5</v>
+      </c>
+      <c r="N40" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="O40" s="1"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="27"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="18"/>
+      <c r="I41" s="1"/>
+      <c r="J41" t="s">
+        <v>15</v>
+      </c>
+      <c r="K41">
+        <v>12</v>
+      </c>
+      <c r="M41" s="10">
+        <f>4.5</f>
+        <v>4.5</v>
+      </c>
+      <c r="N41" s="2">
+        <f>2+2.5+5</f>
+        <v>9.5</v>
+      </c>
+      <c r="O41" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="21"/>
+      <c r="D42" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="24"/>
+      <c r="G42" s="18"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" s="21"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="19"/>
+      <c r="K43" s="1">
+        <f>SUM(K3:K41)</f>
+        <v>111</v>
+      </c>
+      <c r="L43" s="1"/>
+      <c r="M43" s="9">
+        <f>SUM(M3:M41)</f>
+        <v>59.5</v>
+      </c>
+      <c r="N43" s="9">
+        <f>SUM(N3:N41)</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="22"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="25"/>
+      <c r="G44" s="6"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K46">
+        <f>5*4*5</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K47">
+        <f>4*5</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K48">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="K49">
+        <f>120-5-4</f>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J50" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K50" s="1">
+        <f>K3+K12</f>
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="51" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J51" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K51" s="1">
+        <f>K13+K21+K30+K39</f>
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="52" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J52" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K52" s="1">
+        <f>K4+K14+K22+K31+K40</f>
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="53" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J53" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K53" s="1">
+        <f>K5+K15+K23+K24+K32+K33+K41</f>
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="54" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="K54">
+        <f>SUM(K50:K53)</f>
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="47">
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="C21:C26"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E23"/>
     <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G25"/>
+    <mergeCell ref="G21:G22"/>
     <mergeCell ref="F23:F26"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="D12:D14"/>
     <mergeCell ref="E12:E15"/>

--- a/Horarios/HorarioWAN_2026.xlsx
+++ b/Horarios/HorarioWAN_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecmx-my.sharepoint.com/personal/lperezf_tec_mx/Documents/Documents/GitLiz/WAN/Horarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{FC23BDE9-CBF9-4CD9-B661-15FDB57BE38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93327C75-AB24-471B-A2C7-4F71A4952D9D}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{FC23BDE9-CBF9-4CD9-B661-15FDB57BE38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F06F5225-2BA6-4F22-8674-6156670CAE64}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
   </bookViews>
   <sheets>
     <sheet name="WAN_201" sheetId="5" r:id="rId1"/>
@@ -644,66 +644,66 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -722,6 +722,18 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -732,18 +744,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1101,8 +1101,7 @@
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="12.7265625" style="2" customWidth="1"/>
-    <col min="3" max="4" width="12.6328125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.7265625" style="2" customWidth="1"/>
+    <col min="3" max="5" width="14.6328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.1796875" style="2" customWidth="1"/>
     <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
     <col min="8" max="8" width="4.36328125" customWidth="1"/>
@@ -1135,7 +1134,7 @@
       <c r="B3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="31" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="48" t="s">
@@ -1156,7 +1155,7 @@
       <c r="B4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="14"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="49"/>
       <c r="E4" s="49"/>
       <c r="F4" s="49"/>
@@ -1167,7 +1166,7 @@
       <c r="B5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="14"/>
+      <c r="C5" s="31"/>
       <c r="D5" s="49"/>
       <c r="E5" s="49"/>
       <c r="F5" s="49"/>
@@ -1240,19 +1239,19 @@
       <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="41" t="s">
+      <c r="C12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="15" t="s">
+      <c r="F12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="1"/>
@@ -1261,25 +1260,25 @@
       <c r="B13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="15"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="14"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="29" t="s">
+      <c r="D14" s="26"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="43" t="s">
+      <c r="G14" s="47" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1287,34 +1286,34 @@
       <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="41" t="s">
+      <c r="C15" s="44"/>
+      <c r="D15" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="43"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="47"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="43"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="44"/>
+      <c r="G16" s="47"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="22"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="26"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.35">
@@ -1344,19 +1343,19 @@
       <c r="B21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="44" t="s">
+      <c r="C21" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F21" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="14" t="s">
+      <c r="F21" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="31" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="1"/>
@@ -1365,59 +1364,59 @@
       <c r="B22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="14"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="31"/>
       <c r="I22" s="1"/>
     </row>
     <row r="23" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="46"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="20" t="s">
+      <c r="C23" s="30"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="46"/>
-      <c r="D24" s="29" t="s">
+      <c r="C24" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F24" s="21"/>
-      <c r="G24" s="15"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="14"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="46"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="15"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="14"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="47"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="22"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="26"/>
       <c r="G26" s="6"/>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.35">
@@ -1447,19 +1446,19 @@
       <c r="B30" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="29" t="s">
+      <c r="C30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="14" t="s">
+      <c r="F30" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="1"/>
@@ -1468,27 +1467,27 @@
       <c r="B31" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="27"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="14"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="31"/>
     </row>
     <row r="32" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="27"/>
+      <c r="D32" s="17"/>
       <c r="E32" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F32" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1496,30 +1495,30 @@
       <c r="B33" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="33"/>
-      <c r="D33" s="29" t="s">
+      <c r="C33" s="28"/>
+      <c r="D33" s="27" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="35"/>
       <c r="F33" s="38"/>
-      <c r="G33" s="15"/>
+      <c r="G33" s="14"/>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
       <c r="E34" s="35"/>
       <c r="F34" s="38"/>
-      <c r="G34" s="15"/>
+      <c r="G34" s="14"/>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
       <c r="E35" s="36"/>
       <c r="F35" s="39"/>
       <c r="G35" s="6"/>
@@ -1551,19 +1550,19 @@
       <c r="B39" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="16" t="s">
+      <c r="D39" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="23" t="s">
+      <c r="F39" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="17" t="s">
+      <c r="G39" s="21" t="s">
         <v>16</v>
       </c>
       <c r="I39" s="1"/>
@@ -1572,72 +1571,84 @@
       <c r="B40" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="15"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="18"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="22"/>
       <c r="I40" s="1"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="20" t="s">
+      <c r="C41" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="27"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="18"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="22"/>
       <c r="I41" s="1"/>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="21"/>
-      <c r="D42" s="29" t="s">
+      <c r="C42" s="25"/>
+      <c r="D42" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="15" t="s">
+      <c r="E42" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="24"/>
-      <c r="G42" s="18"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="22"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C43" s="21"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="19"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="23"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="22"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="25"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="20"/>
       <c r="G44" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="E21:E26"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="D42:D44"/>
     <mergeCell ref="G21:G22"/>
     <mergeCell ref="G23:G25"/>
     <mergeCell ref="C12:C13"/>
@@ -1650,31 +1661,19 @@
     <mergeCell ref="G14:G16"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C21:C26"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="F21:F22"/>
     <mergeCell ref="F23:F26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1725,7 +1724,7 @@
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="31" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="48" t="s">
@@ -1745,7 +1744,7 @@
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="14"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="49"/>
       <c r="E4" s="49"/>
       <c r="F4" s="49"/>
@@ -1755,11 +1754,11 @@
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="14"/>
+      <c r="C5" s="31"/>
       <c r="D5" s="49"/>
       <c r="E5" s="49"/>
       <c r="F5" s="49"/>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1779,7 +1778,7 @@
       <c r="F6" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="15"/>
+      <c r="G6" s="14"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
@@ -1789,7 +1788,7 @@
       <c r="D7" s="49"/>
       <c r="E7" s="49"/>
       <c r="F7" s="49"/>
-      <c r="G7" s="15"/>
+      <c r="G7" s="14"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
@@ -1828,19 +1827,19 @@
       <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="41" t="s">
+      <c r="C12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="15" t="s">
+      <c r="F12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1848,25 +1847,25 @@
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="15"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="14"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="29" t="s">
+      <c r="D14" s="26"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="43" t="s">
+      <c r="G14" s="47" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1874,34 +1873,34 @@
       <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="41" t="s">
+      <c r="C15" s="44"/>
+      <c r="D15" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="43"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="47"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="43"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="44"/>
+      <c r="G16" s="47"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="22"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="26"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.35">
@@ -1931,19 +1930,19 @@
       <c r="B21" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="44" t="s">
+      <c r="C21" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="16" t="s">
+      <c r="D21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="14" t="s">
+      <c r="F21" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="31" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1951,23 +1950,23 @@
       <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="14"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="31"/>
     </row>
     <row r="23" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="46"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="20" t="s">
+      <c r="C23" s="42"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="14" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1975,34 +1974,34 @@
       <c r="B24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="46"/>
-      <c r="D24" s="29" t="s">
+      <c r="C24" s="42"/>
+      <c r="D24" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="21"/>
-      <c r="G24" s="15"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="14"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="46"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="15"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="14"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="47"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="22"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="26"/>
       <c r="G26" s="6"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
@@ -2032,19 +2031,19 @@
       <c r="B30" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="29" t="s">
+      <c r="C30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="14" t="s">
+      <c r="F30" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="31" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2052,27 +2051,27 @@
       <c r="B31" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="27"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="14"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="31"/>
     </row>
     <row r="32" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="27"/>
+      <c r="D32" s="17"/>
       <c r="E32" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F32" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2080,30 +2079,30 @@
       <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="33"/>
-      <c r="D33" s="29" t="s">
+      <c r="C33" s="28"/>
+      <c r="D33" s="27" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="35"/>
       <c r="F33" s="38"/>
-      <c r="G33" s="15"/>
+      <c r="G33" s="14"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
       <c r="E34" s="35"/>
       <c r="F34" s="38"/>
-      <c r="G34" s="15"/>
+      <c r="G34" s="14"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
       <c r="E35" s="36"/>
       <c r="F35" s="39"/>
       <c r="G35" s="6"/>
@@ -2135,19 +2134,19 @@
       <c r="B39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="16" t="s">
+      <c r="D39" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="23" t="s">
+      <c r="F39" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="17" t="s">
+      <c r="G39" s="21" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2155,68 +2154,83 @@
       <c r="B40" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="15"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="18"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="22"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="20" t="s">
+      <c r="C41" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="27"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="18"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="22"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="21"/>
-      <c r="D42" s="29" t="s">
+      <c r="C42" s="25"/>
+      <c r="D42" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="15" t="s">
+      <c r="E42" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="24"/>
-      <c r="G42" s="18"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="22"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="21"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="19"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="23"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="22"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="25"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="20"/>
       <c r="G44" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
     <mergeCell ref="G21:G22"/>
     <mergeCell ref="G23:G25"/>
     <mergeCell ref="C30:C31"/>
@@ -2233,29 +2247,14 @@
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="F21:F22"/>
     <mergeCell ref="F23:F26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E42:E44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2318,7 +2317,7 @@
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="31" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="48" t="s">
@@ -2350,7 +2349,7 @@
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="14"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="49"/>
       <c r="E4" s="49"/>
       <c r="F4" s="49"/>
@@ -2371,11 +2370,11 @@
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="14"/>
+      <c r="C5" s="31"/>
       <c r="D5" s="49"/>
       <c r="E5" s="49"/>
       <c r="F5" s="49"/>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>22</v>
       </c>
       <c r="J5" t="s">
@@ -2411,7 +2410,7 @@
       <c r="F6" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="15"/>
+      <c r="G6" s="14"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
@@ -2421,7 +2420,7 @@
       <c r="D7" s="49"/>
       <c r="E7" s="49"/>
       <c r="F7" s="49"/>
-      <c r="G7" s="15"/>
+      <c r="G7" s="14"/>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
@@ -2460,19 +2459,19 @@
       <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="41" t="s">
+      <c r="C12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="15" t="s">
+      <c r="F12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="1"/>
@@ -2491,11 +2490,11 @@
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="15"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="14"/>
       <c r="J13" s="1" t="s">
         <v>14</v>
       </c>
@@ -2510,15 +2509,15 @@
       <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="29" t="s">
+      <c r="D14" s="26"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="43" t="s">
+      <c r="G14" s="47" t="s">
         <v>23</v>
       </c>
       <c r="J14" t="s">
@@ -2536,13 +2535,13 @@
       <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="41" t="s">
+      <c r="C15" s="44"/>
+      <c r="D15" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="43"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="47"/>
       <c r="J15" t="s">
         <v>15</v>
       </c>
@@ -2557,13 +2556,13 @@
       <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="43"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="44"/>
+      <c r="G16" s="47"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
@@ -2571,10 +2570,10 @@
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="22"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="26"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.35">
@@ -2604,19 +2603,19 @@
       <c r="B21" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="16" t="s">
+      <c r="C21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="14" t="s">
+      <c r="F21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="31" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="1"/>
@@ -2635,11 +2634,11 @@
       <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="40"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="14"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="31"/>
       <c r="I22" s="1"/>
       <c r="J22" t="s">
         <v>12</v>
@@ -2656,15 +2655,15 @@
       <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="20" t="s">
+      <c r="C23" s="26"/>
+      <c r="D23" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="16"/>
-      <c r="F23" s="29" t="s">
+      <c r="E23" s="30"/>
+      <c r="F23" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="14" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -2684,15 +2683,15 @@
       <c r="B24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="21"/>
-      <c r="E24" s="15" t="s">
+      <c r="D24" s="25"/>
+      <c r="E24" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="33"/>
-      <c r="G24" s="15"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="14"/>
       <c r="J24" t="s">
         <v>31</v>
       </c>
@@ -2708,21 +2707,21 @@
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="33"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="15"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="14"/>
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="30"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="30"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="29"/>
       <c r="G26" s="6"/>
       <c r="P26" s="1"/>
     </row>
@@ -2758,19 +2757,19 @@
       <c r="B30" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="29" t="s">
+      <c r="C30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="14" t="s">
+      <c r="F30" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="1"/>
@@ -2790,11 +2789,11 @@
       <c r="B31" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="14"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="31"/>
       <c r="J31" t="s">
         <v>12</v>
       </c>
@@ -2811,15 +2810,15 @@
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
       <c r="E32" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F32" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="14" t="s">
         <v>22</v>
       </c>
       <c r="J32" s="1" t="s">
@@ -2839,15 +2838,15 @@
       <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C33" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="29" t="s">
+      <c r="D33" s="27" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="35"/>
       <c r="F33" s="38"/>
-      <c r="G33" s="15"/>
+      <c r="G33" s="14"/>
       <c r="J33" t="s">
         <v>31</v>
       </c>
@@ -2863,19 +2862,19 @@
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
       <c r="E34" s="35"/>
       <c r="F34" s="38"/>
-      <c r="G34" s="15"/>
+      <c r="G34" s="14"/>
       <c r="P34" s="1"/>
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
       <c r="E35" s="36"/>
       <c r="F35" s="39"/>
       <c r="G35" s="6"/>
@@ -2913,19 +2912,19 @@
       <c r="B39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="15" t="s">
+      <c r="D39" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="F39" s="15" t="s">
+      <c r="E39" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G39" s="23" t="s">
+      <c r="G39" s="18" t="s">
         <v>57</v>
       </c>
       <c r="I39" s="1"/>
@@ -2944,11 +2943,11 @@
       <c r="B40" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="24"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="19"/>
       <c r="I40" s="1"/>
       <c r="J40" t="s">
         <v>12</v>
@@ -2965,13 +2964,13 @@
       <c r="B41" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="20" t="s">
+      <c r="C41" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="15"/>
-      <c r="E41" s="27"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="24"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="19"/>
       <c r="I41" s="1"/>
       <c r="J41" t="s">
         <v>15</v>
@@ -2994,27 +2993,27 @@
       <c r="B42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="21"/>
-      <c r="D42" s="23" t="s">
+      <c r="C42" s="25"/>
+      <c r="D42" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E42" s="23" t="s">
+      <c r="E42" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="23" t="s">
+      <c r="F42" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="G42" s="24"/>
+      <c r="G42" s="19"/>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="21"/>
+      <c r="C43" s="25"/>
       <c r="D43" s="54"/>
       <c r="E43" s="54"/>
       <c r="F43" s="54"/>
-      <c r="G43" s="25"/>
+      <c r="G43" s="20"/>
       <c r="K43" s="1">
         <f>SUM(K3:K41)</f>
         <v>120</v>
@@ -3036,7 +3035,7 @@
       <c r="B44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="22"/>
+      <c r="C44" s="26"/>
       <c r="D44" s="55"/>
       <c r="E44" s="55"/>
       <c r="F44" s="55"/>
@@ -3103,11 +3102,34 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="D23:D26"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
     <mergeCell ref="G21:G22"/>
     <mergeCell ref="G23:G25"/>
     <mergeCell ref="G39:G43"/>
@@ -3124,34 +3146,11 @@
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="D42:D44"/>
     <mergeCell ref="F39:F41"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="D23:D26"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="F42:F44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3210,7 +3209,7 @@
       <c r="B3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="31" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="48" t="s">
@@ -3242,7 +3241,7 @@
       <c r="B4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="14"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="49"/>
       <c r="E4" s="49"/>
       <c r="F4" s="49"/>
@@ -3263,7 +3262,7 @@
       <c r="B5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="14"/>
+      <c r="C5" s="31"/>
       <c r="D5" s="49"/>
       <c r="E5" s="49"/>
       <c r="F5" s="49"/>
@@ -3352,19 +3351,19 @@
       <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="41" t="s">
+      <c r="C12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="15" t="s">
+      <c r="F12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="1"/>
@@ -3383,11 +3382,11 @@
       <c r="B13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="15"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="14"/>
       <c r="J13" s="1" t="s">
         <v>14</v>
       </c>
@@ -3402,15 +3401,15 @@
       <c r="B14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="29" t="s">
+      <c r="D14" s="26"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="43" t="s">
+      <c r="G14" s="47" t="s">
         <v>23</v>
       </c>
       <c r="J14" t="s">
@@ -3428,13 +3427,13 @@
       <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="41" t="s">
+      <c r="C15" s="44"/>
+      <c r="D15" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="43"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="47"/>
       <c r="J15" t="s">
         <v>15</v>
       </c>
@@ -3449,13 +3448,13 @@
       <c r="B16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="43"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="44"/>
+      <c r="G16" s="47"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
@@ -3463,10 +3462,10 @@
       <c r="B17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="22"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="26"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.35">
@@ -3496,19 +3495,19 @@
       <c r="B21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="44" t="s">
+      <c r="C21" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="16" t="s">
+      <c r="D21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="14" t="s">
+      <c r="F21" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="31" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="1"/>
@@ -3527,11 +3526,11 @@
       <c r="B22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="14"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="31"/>
       <c r="I22" s="1"/>
       <c r="J22" t="s">
         <v>12</v>
@@ -3548,13 +3547,13 @@
       <c r="B23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="46"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="20" t="s">
+      <c r="C23" s="42"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="14" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -3574,15 +3573,15 @@
       <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="46"/>
-      <c r="D24" s="29" t="s">
+      <c r="C24" s="42"/>
+      <c r="D24" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="21"/>
-      <c r="G24" s="15"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="14"/>
       <c r="J24" t="s">
         <v>31</v>
       </c>
@@ -3598,21 +3597,21 @@
       <c r="B25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="46"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="15"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="14"/>
       <c r="O25" s="1"/>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="47"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="22"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="26"/>
       <c r="G26" s="6"/>
       <c r="O26" s="1"/>
     </row>
@@ -3648,19 +3647,19 @@
       <c r="B30" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="29" t="s">
+      <c r="C30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="14" t="s">
+      <c r="F30" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="1"/>
@@ -3680,11 +3679,11 @@
       <c r="B31" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="27"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="14"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="31"/>
       <c r="J31" t="s">
         <v>12</v>
       </c>
@@ -3701,17 +3700,17 @@
       <c r="B32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="27"/>
+      <c r="D32" s="17"/>
       <c r="E32" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F32" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="14" t="s">
         <v>22</v>
       </c>
       <c r="J32" s="1" t="s">
@@ -3731,13 +3730,13 @@
       <c r="B33" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="33"/>
-      <c r="D33" s="29" t="s">
+      <c r="C33" s="28"/>
+      <c r="D33" s="27" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="35"/>
       <c r="F33" s="38"/>
-      <c r="G33" s="15"/>
+      <c r="G33" s="14"/>
       <c r="J33" t="s">
         <v>31</v>
       </c>
@@ -3753,19 +3752,19 @@
       <c r="B34" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
       <c r="E34" s="35"/>
       <c r="F34" s="38"/>
-      <c r="G34" s="15"/>
+      <c r="G34" s="14"/>
       <c r="O34" s="1"/>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
       <c r="E35" s="36"/>
       <c r="F35" s="39"/>
       <c r="G35" s="6"/>
@@ -3803,19 +3802,19 @@
       <c r="B39" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="16" t="s">
+      <c r="D39" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="23" t="s">
+      <c r="F39" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="17" t="s">
+      <c r="G39" s="21" t="s">
         <v>16</v>
       </c>
       <c r="I39" s="1"/>
@@ -3835,11 +3834,11 @@
       <c r="B40" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="15"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="18"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="22"/>
       <c r="I40" s="1"/>
       <c r="J40" t="s">
         <v>12</v>
@@ -3856,13 +3855,13 @@
       <c r="B41" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="20" t="s">
+      <c r="C41" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="27"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="18"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="22"/>
       <c r="I41" s="1"/>
       <c r="J41" t="s">
         <v>15</v>
@@ -3885,25 +3884,25 @@
       <c r="B42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="21"/>
-      <c r="D42" s="29" t="s">
+      <c r="C42" s="25"/>
+      <c r="D42" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="15" t="s">
+      <c r="E42" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="24"/>
-      <c r="G42" s="18"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="22"/>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C43" s="21"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="19"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="23"/>
       <c r="K43" s="1">
         <f>SUM(K3:K41)</f>
         <v>111</v>
@@ -3922,10 +3921,901 @@
       <c r="B44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="22"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="25"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="6"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K46">
+        <f>5*4*5</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K47">
+        <f>4*5</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K48">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="K49">
+        <f>120-5-4</f>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J50" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K50" s="1">
+        <f>K3+K12</f>
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="51" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J51" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K51" s="1">
+        <f>K13+K21+K30+K39</f>
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="52" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J52" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K52" s="1">
+        <f>K4+K14+K22+K31+K40</f>
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="53" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J53" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K53" s="1">
+        <f>K5+K15+K23+K24+K32+K33+K41</f>
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="54" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="K54">
+        <f>SUM(K50:K53)</f>
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="47">
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="C21:C26"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B72F34B-8139-4D0E-8882-03145DDD5E1F}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:O54"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="2" customWidth="1"/>
+    <col min="2" max="2" width="10.90625" style="2"/>
+    <col min="3" max="4" width="12.6328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.7265625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="4.36328125" customWidth="1"/>
+    <col min="10" max="10" width="15.7265625" customWidth="1"/>
+    <col min="13" max="14" width="10.90625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B1" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B2" s="4"/>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="1">
+        <f>2.5+2.5+2.5+2.5+2</f>
+        <v>12</v>
+      </c>
+      <c r="M3" s="9">
+        <f>K3</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="31"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="50"/>
+      <c r="I4" s="1"/>
+      <c r="J4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4">
+        <f>2.5+2.5+2.5</f>
+        <v>7.5</v>
+      </c>
+      <c r="N4" s="2">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="31"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5">
+        <f>2.5+2</f>
+        <v>4.5</v>
+      </c>
+      <c r="M5" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="N5" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="14"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="5"/>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B10" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B11" s="4"/>
+      <c r="C11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" s="1">
+        <f>3+2.5+3+2</f>
+        <v>10.5</v>
+      </c>
+      <c r="M12" s="2">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="33"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="14"/>
+      <c r="J13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" s="1">
+        <v>3</v>
+      </c>
+      <c r="M13" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="26"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14">
+        <f>2+2.5+2+2</f>
+        <v>8.5</v>
+      </c>
+      <c r="N14" s="2">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="44"/>
+      <c r="D15" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="46"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="47"/>
+      <c r="J15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="N15" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="44"/>
+      <c r="G16" s="47"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="6"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B19" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B20" s="4"/>
+      <c r="C20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K21" s="1">
+        <f>2.5+3</f>
+        <v>5.5</v>
+      </c>
+      <c r="M21" s="2">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="41"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="31"/>
+      <c r="I22" s="1"/>
+      <c r="J22" t="s">
+        <v>12</v>
+      </c>
+      <c r="K22">
+        <f>2.5+2</f>
+        <v>4.5</v>
+      </c>
+      <c r="N22" s="2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="42"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K23" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="M23" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="O23" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="42"/>
+      <c r="D24" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="25"/>
+      <c r="G24" s="14"/>
+      <c r="J24" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24">
+        <v>4.5</v>
+      </c>
+      <c r="N24" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O24" s="1"/>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B25" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="42"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="14"/>
+      <c r="O25" s="1"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="43"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="6"/>
+      <c r="O26" s="1"/>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="O27" s="1"/>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B28" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="O28" s="1"/>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B29" s="4"/>
+      <c r="C29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O29" s="1"/>
+    </row>
+    <row r="30" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K30" s="1">
+        <f>3+2.5+2+3</f>
+        <v>10.5</v>
+      </c>
+      <c r="M30" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="O30" s="1"/>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="17"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="31"/>
+      <c r="J31" t="s">
+        <v>12</v>
+      </c>
+      <c r="K31">
+        <f>2+2.5+2</f>
+        <v>6.5</v>
+      </c>
+      <c r="N31" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="O31" s="1"/>
+    </row>
+    <row r="32" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="17"/>
+      <c r="E32" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K32" s="1">
+        <v>2</v>
+      </c>
+      <c r="M32" s="10">
+        <v>2</v>
+      </c>
+      <c r="O32" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="28"/>
+      <c r="D33" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="35"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="14"/>
+      <c r="J33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K33" s="1">
+        <v>5</v>
+      </c>
+      <c r="N33" s="2">
+        <v>5</v>
+      </c>
+      <c r="O33" s="1"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B34" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="14"/>
+      <c r="O34" s="1"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="6"/>
+      <c r="O35" s="1"/>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="O36" s="1"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B37" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O37" s="1"/>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B38" s="4"/>
+      <c r="C38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O38" s="1"/>
+    </row>
+    <row r="39" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K39" s="1">
+        <f>3+2.5</f>
+        <v>5.5</v>
+      </c>
+      <c r="M39" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="O39" s="1"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="14"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="22"/>
+      <c r="I40" s="1"/>
+      <c r="J40" t="s">
+        <v>12</v>
+      </c>
+      <c r="K40">
+        <v>2.5</v>
+      </c>
+      <c r="N40" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="O40" s="1"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="17"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="22"/>
+      <c r="I41" s="1"/>
+      <c r="J41" t="s">
+        <v>15</v>
+      </c>
+      <c r="K41">
+        <v>12</v>
+      </c>
+      <c r="M41" s="10">
+        <f>4.5</f>
+        <v>4.5</v>
+      </c>
+      <c r="N41" s="2">
+        <f>2+2.5+5</f>
+        <v>9.5</v>
+      </c>
+      <c r="O41" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="25"/>
+      <c r="D42" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="19"/>
+      <c r="G42" s="22"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" s="25"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="23"/>
+      <c r="K43" s="1">
+        <f>SUM(K3:K41)</f>
+        <v>111</v>
+      </c>
+      <c r="L43" s="1"/>
+      <c r="M43" s="9">
+        <f>SUM(M3:M41)</f>
+        <v>59.5</v>
+      </c>
+      <c r="N43" s="9">
+        <f>SUM(N3:N41)</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="26"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="20"/>
       <c r="G44" s="6"/>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.35">
@@ -4046,895 +4936,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B72F34B-8139-4D0E-8882-03145DDD5E1F}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B1:O54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="10.90625" style="2"/>
-    <col min="3" max="4" width="12.6328125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.7265625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.1796875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="4.36328125" customWidth="1"/>
-    <col min="10" max="10" width="15.7265625" customWidth="1"/>
-    <col min="13" max="14" width="10.90625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B1" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B2" s="4"/>
-      <c r="C2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="1">
-        <f>2.5+2.5+2.5+2.5+2</f>
-        <v>12</v>
-      </c>
-      <c r="M3" s="9">
-        <f>K3</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="50"/>
-      <c r="I4" s="1"/>
-      <c r="J4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K4">
-        <f>2.5+2.5+2.5</f>
-        <v>7.5</v>
-      </c>
-      <c r="N4" s="2">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5">
-        <f>2.5+2</f>
-        <v>4.5</v>
-      </c>
-      <c r="M5" s="10">
-        <v>1.5</v>
-      </c>
-      <c r="N5" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="15"/>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="15"/>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="5"/>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B10" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B11" s="4"/>
-      <c r="C11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="41" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K12" s="1">
-        <f>3+2.5+3+2</f>
-        <v>10.5</v>
-      </c>
-      <c r="M12" s="2">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B13" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="15"/>
-      <c r="J13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="1">
-        <v>3</v>
-      </c>
-      <c r="M13" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B14" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="41" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="J14" t="s">
-        <v>12</v>
-      </c>
-      <c r="K14">
-        <f>2+2.5+2+2</f>
-        <v>8.5</v>
-      </c>
-      <c r="N14" s="2">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="41" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="43"/>
-      <c r="J15" t="s">
-        <v>15</v>
-      </c>
-      <c r="K15">
-        <v>2</v>
-      </c>
-      <c r="N15" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B16" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="43"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="6"/>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B19" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B20" s="4"/>
-      <c r="C20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" s="44" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F21" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K21" s="1">
-        <f>2.5+3</f>
-        <v>5.5</v>
-      </c>
-      <c r="M21" s="2">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B22" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="14"/>
-      <c r="I22" s="1"/>
-      <c r="J22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K22">
-        <f>2.5+2</f>
-        <v>4.5</v>
-      </c>
-      <c r="N22" s="2">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="23" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="46"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K23" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="M23" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="O23" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" s="46"/>
-      <c r="D24" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F24" s="21"/>
-      <c r="G24" s="15"/>
-      <c r="J24" t="s">
-        <v>31</v>
-      </c>
-      <c r="K24">
-        <v>4.5</v>
-      </c>
-      <c r="N24" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="O24" s="1"/>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B25" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="46"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="15"/>
-      <c r="O25" s="1"/>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="47"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="6"/>
-      <c r="O26" s="1"/>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="O27" s="1"/>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B28" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="O28" s="1"/>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B29" s="4"/>
-      <c r="C29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="O29" s="1"/>
-    </row>
-    <row r="30" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="F30" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K30" s="1">
-        <f>3+2.5+2+3</f>
-        <v>10.5</v>
-      </c>
-      <c r="M30" s="2">
-        <v>10.5</v>
-      </c>
-      <c r="O30" s="1"/>
-    </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B31" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" s="27"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="14"/>
-      <c r="J31" t="s">
-        <v>12</v>
-      </c>
-      <c r="K31">
-        <f>2+2.5+2</f>
-        <v>6.5</v>
-      </c>
-      <c r="N31" s="2">
-        <v>6.5</v>
-      </c>
-      <c r="O31" s="1"/>
-    </row>
-    <row r="32" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="27"/>
-      <c r="E32" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K32" s="1">
-        <v>2</v>
-      </c>
-      <c r="M32" s="10">
-        <v>2</v>
-      </c>
-      <c r="O32" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" s="33"/>
-      <c r="D33" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="35"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="15"/>
-      <c r="J33" t="s">
-        <v>31</v>
-      </c>
-      <c r="K33" s="1">
-        <v>5</v>
-      </c>
-      <c r="N33" s="2">
-        <v>5</v>
-      </c>
-      <c r="O33" s="1"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B34" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="15"/>
-      <c r="O34" s="1"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="6"/>
-      <c r="O35" s="1"/>
-    </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="O36" s="1"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B37" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O37" s="1"/>
-    </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B38" s="4"/>
-      <c r="C38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="O38" s="1"/>
-    </row>
-    <row r="39" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="G39" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K39" s="1">
-        <f>3+2.5</f>
-        <v>5.5</v>
-      </c>
-      <c r="M39" s="2">
-        <v>5.5</v>
-      </c>
-      <c r="O39" s="1"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B40" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="15"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="18"/>
-      <c r="I40" s="1"/>
-      <c r="J40" t="s">
-        <v>12</v>
-      </c>
-      <c r="K40">
-        <v>2.5</v>
-      </c>
-      <c r="N40" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="O40" s="1"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41" s="27"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="18"/>
-      <c r="I41" s="1"/>
-      <c r="J41" t="s">
-        <v>15</v>
-      </c>
-      <c r="K41">
-        <v>12</v>
-      </c>
-      <c r="M41" s="10">
-        <f>4.5</f>
-        <v>4.5</v>
-      </c>
-      <c r="N41" s="2">
-        <f>2+2.5+5</f>
-        <v>9.5</v>
-      </c>
-      <c r="O41" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C42" s="21"/>
-      <c r="D42" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="24"/>
-      <c r="G42" s="18"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C43" s="21"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="19"/>
-      <c r="K43" s="1">
-        <f>SUM(K3:K41)</f>
-        <v>111</v>
-      </c>
-      <c r="L43" s="1"/>
-      <c r="M43" s="9">
-        <f>SUM(M3:M41)</f>
-        <v>59.5</v>
-      </c>
-      <c r="N43" s="9">
-        <f>SUM(N3:N41)</f>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C44" s="22"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="25"/>
-      <c r="G44" s="6"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K46">
-        <f>5*4*5</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K47">
-        <f>4*5</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K48">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="49" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="K49">
-        <f>120-5-4</f>
-        <v>111</v>
-      </c>
-    </row>
-    <row r="50" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J50" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K50" s="1">
-        <f>K3+K12</f>
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="51" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J51" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K51" s="1">
-        <f>K13+K21+K30+K39</f>
-        <v>24.5</v>
-      </c>
-    </row>
-    <row r="52" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J52" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K52" s="1">
-        <f>K4+K14+K22+K31+K40</f>
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="53" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J53" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K53" s="1">
-        <f>K5+K15+K23+K24+K32+K33+K41</f>
-        <v>34.5</v>
-      </c>
-    </row>
-    <row r="54" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="K54">
-        <f>SUM(K50:K53)</f>
-        <v>111</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="47">
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="C21:C26"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Horarios/HorarioWAN_2026.xlsx
+++ b/Horarios/HorarioWAN_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecmx-my.sharepoint.com/personal/lperezf_tec_mx/Documents/Documents/GitLiz/WAN/Horarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{FC23BDE9-CBF9-4CD9-B661-15FDB57BE38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F06F5225-2BA6-4F22-8674-6156670CAE64}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{FC23BDE9-CBF9-4CD9-B661-15FDB57BE38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6ECF9B62-7998-4FB7-B4A0-165D1B3F8DC8}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
   </bookViews>
@@ -644,66 +644,78 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -720,18 +732,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -790,10 +790,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1134,7 +1130,7 @@
       <c r="B3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="20" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="48" t="s">
@@ -1155,7 +1151,7 @@
       <c r="B4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="31"/>
+      <c r="C4" s="20"/>
       <c r="D4" s="49"/>
       <c r="E4" s="49"/>
       <c r="F4" s="49"/>
@@ -1166,7 +1162,7 @@
       <c r="B5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="31"/>
+      <c r="C5" s="20"/>
       <c r="D5" s="49"/>
       <c r="E5" s="49"/>
       <c r="F5" s="49"/>
@@ -1239,19 +1235,19 @@
       <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="15" t="s">
+      <c r="C12" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="30" t="s">
         <v>19</v>
       </c>
       <c r="E12" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="14" t="s">
+      <c r="F12" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="19" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="1"/>
@@ -1260,11 +1256,11 @@
       <c r="B13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="33"/>
+      <c r="C13" s="36"/>
       <c r="D13" s="44"/>
       <c r="E13" s="46"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="14"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="19"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
@@ -1275,7 +1271,7 @@
       </c>
       <c r="D14" s="26"/>
       <c r="E14" s="46"/>
-      <c r="F14" s="27" t="s">
+      <c r="F14" s="33" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="47" t="s">
@@ -1300,7 +1296,7 @@
       </c>
       <c r="C16" s="44"/>
       <c r="D16" s="44"/>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F16" s="44"/>
@@ -1312,7 +1308,7 @@
       </c>
       <c r="C17" s="26"/>
       <c r="D17" s="26"/>
-      <c r="E17" s="33"/>
+      <c r="E17" s="36"/>
       <c r="F17" s="26"/>
       <c r="G17" s="6"/>
     </row>
@@ -1343,19 +1339,19 @@
       <c r="B21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="30" t="s">
+      <c r="C21" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="D21" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="40" t="s">
+      <c r="D21" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="31" t="s">
+      <c r="F21" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="20" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="1"/>
@@ -1364,24 +1360,24 @@
       <c r="B22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="30"/>
+      <c r="C22" s="18"/>
       <c r="D22" s="44"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="31"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="20"/>
       <c r="I22" s="1"/>
     </row>
     <row r="23" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="30"/>
+      <c r="C23" s="18"/>
       <c r="D23" s="26"/>
-      <c r="E23" s="42"/>
+      <c r="E23" s="16"/>
       <c r="F23" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="14" t="s">
+      <c r="G23" s="19" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1389,33 +1385,33 @@
       <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="D24" s="27" t="s">
+      <c r="D24" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="42"/>
+      <c r="E24" s="16"/>
       <c r="F24" s="25"/>
-      <c r="G24" s="14"/>
+      <c r="G24" s="19"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="14"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="42"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="16"/>
       <c r="F25" s="25"/>
-      <c r="G25" s="14"/>
+      <c r="G25" s="19"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="43"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="17"/>
       <c r="F26" s="26"/>
       <c r="G26" s="6"/>
     </row>
@@ -1446,19 +1442,19 @@
       <c r="B30" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="27" t="s">
+      <c r="C30" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="31" t="s">
+      <c r="F30" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="20" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="1"/>
@@ -1467,27 +1463,27 @@
       <c r="B31" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="31"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="20"/>
     </row>
     <row r="32" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="27" t="s">
+      <c r="C32" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="17"/>
-      <c r="E32" s="34" t="s">
+      <c r="D32" s="31"/>
+      <c r="E32" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="37" t="s">
+      <c r="F32" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="14" t="s">
+      <c r="G32" s="19" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1495,32 +1491,32 @@
       <c r="B33" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="28"/>
-      <c r="D33" s="27" t="s">
+      <c r="C33" s="37"/>
+      <c r="D33" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="35"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="14"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="19"/>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="14"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="19"/>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="39"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="43"/>
       <c r="G35" s="6"/>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.35">
@@ -1550,16 +1546,16 @@
       <c r="B39" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="30" t="s">
+      <c r="D39" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="18" t="s">
+      <c r="F39" s="27" t="s">
         <v>32</v>
       </c>
       <c r="G39" s="21" t="s">
@@ -1571,10 +1567,10 @@
       <c r="B40" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="14"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="19"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="28"/>
       <c r="G40" s="22"/>
       <c r="I40" s="1"/>
     </row>
@@ -1585,9 +1581,9 @@
       <c r="C41" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="17"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="19"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="28"/>
       <c r="G41" s="22"/>
       <c r="I41" s="1"/>
     </row>
@@ -1596,13 +1592,13 @@
         <v>37</v>
       </c>
       <c r="C42" s="25"/>
-      <c r="D42" s="27" t="s">
+      <c r="D42" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E42" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="19"/>
+      <c r="F42" s="28"/>
       <c r="G42" s="22"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.35">
@@ -1610,9 +1606,9 @@
         <v>38</v>
       </c>
       <c r="C43" s="25"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="19"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="28"/>
       <c r="G43" s="23"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.35">
@@ -1620,37 +1616,26 @@
         <v>39</v>
       </c>
       <c r="C44" s="26"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="20"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="29"/>
       <c r="G44" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="E21:E26"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="D12:D14"/>
     <mergeCell ref="E12:E15"/>
@@ -1661,19 +1646,30 @@
     <mergeCell ref="G14:G16"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="E16:E17"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E21:E26"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="G23:G25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1690,8 +1686,7 @@
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="10.90625" style="2"/>
-    <col min="3" max="4" width="12.6328125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.7265625" style="2" customWidth="1"/>
+    <col min="3" max="5" width="14.6328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.1796875" style="2" customWidth="1"/>
     <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
     <col min="8" max="8" width="4.36328125" customWidth="1"/>
@@ -1724,7 +1719,7 @@
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="20" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="48" t="s">
@@ -1744,7 +1739,7 @@
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="31"/>
+      <c r="C4" s="20"/>
       <c r="D4" s="49"/>
       <c r="E4" s="49"/>
       <c r="F4" s="49"/>
@@ -1754,11 +1749,11 @@
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="31"/>
+      <c r="C5" s="20"/>
       <c r="D5" s="49"/>
       <c r="E5" s="49"/>
       <c r="F5" s="49"/>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="19" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1778,7 +1773,7 @@
       <c r="F6" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="14"/>
+      <c r="G6" s="19"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
@@ -1788,7 +1783,7 @@
       <c r="D7" s="49"/>
       <c r="E7" s="49"/>
       <c r="F7" s="49"/>
-      <c r="G7" s="14"/>
+      <c r="G7" s="19"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
@@ -1827,19 +1822,19 @@
       <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="15" t="s">
+      <c r="C12" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="30" t="s">
         <v>19</v>
       </c>
       <c r="E12" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="14" t="s">
+      <c r="F12" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="19" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1847,11 +1842,11 @@
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="33"/>
+      <c r="C13" s="36"/>
       <c r="D13" s="44"/>
       <c r="E13" s="46"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="14"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="19"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
@@ -1862,7 +1857,7 @@
       </c>
       <c r="D14" s="26"/>
       <c r="E14" s="46"/>
-      <c r="F14" s="27" t="s">
+      <c r="F14" s="33" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="47" t="s">
@@ -1887,7 +1882,7 @@
       </c>
       <c r="C16" s="44"/>
       <c r="D16" s="44"/>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F16" s="44"/>
@@ -1899,7 +1894,7 @@
       </c>
       <c r="C17" s="26"/>
       <c r="D17" s="26"/>
-      <c r="E17" s="33"/>
+      <c r="E17" s="36"/>
       <c r="F17" s="26"/>
       <c r="G17" s="6"/>
     </row>
@@ -1930,19 +1925,19 @@
       <c r="B21" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="40" t="s">
+      <c r="C21" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="F21" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="31" t="s">
+      <c r="F21" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="20" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1950,57 +1945,57 @@
       <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="41"/>
+      <c r="C22" s="18"/>
       <c r="D22" s="44"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="31"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="20"/>
     </row>
     <row r="23" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="42"/>
+      <c r="C23" s="18"/>
       <c r="D23" s="26"/>
-      <c r="E23" s="30"/>
+      <c r="E23" s="16"/>
       <c r="F23" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="14" t="s">
+      <c r="G23" s="19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="42"/>
-      <c r="D24" s="27" t="s">
+      <c r="C24" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="14" t="s">
-        <v>61</v>
-      </c>
+      <c r="E24" s="16"/>
       <c r="F24" s="25"/>
-      <c r="G24" s="14"/>
+      <c r="G24" s="19"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="42"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="14"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="16"/>
       <c r="F25" s="25"/>
-      <c r="G25" s="14"/>
+      <c r="G25" s="19"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="43"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="14"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="17"/>
       <c r="F26" s="26"/>
       <c r="G26" s="6"/>
     </row>
@@ -2031,19 +2026,19 @@
       <c r="B30" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="27" t="s">
+      <c r="C30" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="31" t="s">
+      <c r="F30" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2051,27 +2046,27 @@
       <c r="B31" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="31"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="20"/>
     </row>
     <row r="32" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="27" t="s">
+      <c r="C32" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="17"/>
-      <c r="E32" s="34" t="s">
+      <c r="D32" s="31"/>
+      <c r="E32" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="37" t="s">
+      <c r="F32" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="14" t="s">
+      <c r="G32" s="19" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2079,32 +2074,32 @@
       <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="28"/>
-      <c r="D33" s="27" t="s">
+      <c r="C33" s="37"/>
+      <c r="D33" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="35"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="14"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="19"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="14"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="19"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="39"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="43"/>
       <c r="G35" s="6"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.35">
@@ -2134,16 +2129,16 @@
       <c r="B39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="30" t="s">
+      <c r="D39" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="18" t="s">
+      <c r="F39" s="27" t="s">
         <v>32</v>
       </c>
       <c r="G39" s="21" t="s">
@@ -2154,10 +2149,10 @@
       <c r="B40" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="14"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="19"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="28"/>
       <c r="G40" s="22"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
@@ -2167,9 +2162,9 @@
       <c r="C41" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="17"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="19"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="28"/>
       <c r="G41" s="22"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
@@ -2177,13 +2172,13 @@
         <v>3</v>
       </c>
       <c r="C42" s="25"/>
-      <c r="D42" s="27" t="s">
+      <c r="D42" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E42" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="19"/>
+      <c r="F42" s="28"/>
       <c r="G42" s="22"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.35">
@@ -2191,9 +2186,9 @@
         <v>4</v>
       </c>
       <c r="C43" s="25"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="19"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="28"/>
       <c r="G43" s="23"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.35">
@@ -2201,36 +2196,21 @@
         <v>5</v>
       </c>
       <c r="C44" s="26"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="20"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="29"/>
       <c r="G44" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E42:E44"/>
     <mergeCell ref="G21:G22"/>
     <mergeCell ref="G23:G25"/>
     <mergeCell ref="C30:C31"/>
@@ -2243,18 +2223,33 @@
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="G30:G31"/>
     <mergeCell ref="G32:G34"/>
-    <mergeCell ref="C21:C26"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="F21:F22"/>
     <mergeCell ref="F23:F26"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2317,7 +2312,7 @@
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="20" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="48" t="s">
@@ -2349,7 +2344,7 @@
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="31"/>
+      <c r="C4" s="20"/>
       <c r="D4" s="49"/>
       <c r="E4" s="49"/>
       <c r="F4" s="49"/>
@@ -2370,11 +2365,11 @@
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="31"/>
+      <c r="C5" s="20"/>
       <c r="D5" s="49"/>
       <c r="E5" s="49"/>
       <c r="F5" s="49"/>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="19" t="s">
         <v>22</v>
       </c>
       <c r="J5" t="s">
@@ -2410,7 +2405,7 @@
       <c r="F6" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="14"/>
+      <c r="G6" s="19"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
@@ -2420,7 +2415,7 @@
       <c r="D7" s="49"/>
       <c r="E7" s="49"/>
       <c r="F7" s="49"/>
-      <c r="G7" s="14"/>
+      <c r="G7" s="19"/>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
@@ -2459,19 +2454,19 @@
       <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="15" t="s">
+      <c r="C12" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="30" t="s">
         <v>19</v>
       </c>
       <c r="E12" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="14" t="s">
+      <c r="F12" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="19" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="1"/>
@@ -2490,11 +2485,11 @@
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="33"/>
+      <c r="C13" s="36"/>
       <c r="D13" s="44"/>
       <c r="E13" s="46"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="14"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="19"/>
       <c r="J13" s="1" t="s">
         <v>14</v>
       </c>
@@ -2514,7 +2509,7 @@
       </c>
       <c r="D14" s="26"/>
       <c r="E14" s="46"/>
-      <c r="F14" s="27" t="s">
+      <c r="F14" s="33" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="47" t="s">
@@ -2558,7 +2553,7 @@
       </c>
       <c r="C16" s="44"/>
       <c r="D16" s="44"/>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F16" s="44"/>
@@ -2572,7 +2567,7 @@
       </c>
       <c r="C17" s="26"/>
       <c r="D17" s="26"/>
-      <c r="E17" s="33"/>
+      <c r="E17" s="36"/>
       <c r="F17" s="26"/>
       <c r="G17" s="6"/>
     </row>
@@ -2603,19 +2598,19 @@
       <c r="B21" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="30" t="s">
+      <c r="C21" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="31" t="s">
+      <c r="F21" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="20" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="1"/>
@@ -2635,10 +2630,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="44"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="31"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="20"/>
       <c r="I22" s="1"/>
       <c r="J22" t="s">
         <v>12</v>
@@ -2659,11 +2654,11 @@
       <c r="D23" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="30"/>
-      <c r="F23" s="27" t="s">
+      <c r="E23" s="18"/>
+      <c r="F23" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="14" t="s">
+      <c r="G23" s="19" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -2683,15 +2678,15 @@
       <c r="B24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="27" t="s">
+      <c r="C24" s="33" t="s">
         <v>20</v>
       </c>
       <c r="D24" s="25"/>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="28"/>
-      <c r="G24" s="14"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="19"/>
       <c r="J24" t="s">
         <v>31</v>
       </c>
@@ -2707,21 +2702,21 @@
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="28"/>
+      <c r="C25" s="37"/>
       <c r="D25" s="25"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="14"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="19"/>
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="29"/>
+      <c r="C26" s="34"/>
       <c r="D26" s="26"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="29"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="34"/>
       <c r="G26" s="6"/>
       <c r="P26" s="1"/>
     </row>
@@ -2757,19 +2752,19 @@
       <c r="B30" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="27" t="s">
+      <c r="C30" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="31" t="s">
+      <c r="F30" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="20" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="1"/>
@@ -2789,11 +2784,11 @@
       <c r="B31" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="31"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="20"/>
       <c r="J31" t="s">
         <v>12</v>
       </c>
@@ -2810,15 +2805,15 @@
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="34" t="s">
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="37" t="s">
+      <c r="F32" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="14" t="s">
+      <c r="G32" s="19" t="s">
         <v>22</v>
       </c>
       <c r="J32" s="1" t="s">
@@ -2838,15 +2833,15 @@
       <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="27" t="s">
+      <c r="C33" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="27" t="s">
+      <c r="D33" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="35"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="14"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="19"/>
       <c r="J33" t="s">
         <v>31</v>
       </c>
@@ -2862,21 +2857,21 @@
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="14"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="19"/>
       <c r="P34" s="1"/>
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="39"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="43"/>
       <c r="G35" s="6"/>
       <c r="P35" s="1"/>
     </row>
@@ -2912,19 +2907,19 @@
       <c r="B39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="D39" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F39" s="14" t="s">
+      <c r="E39" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="G39" s="18" t="s">
+      <c r="G39" s="27" t="s">
         <v>57</v>
       </c>
       <c r="I39" s="1"/>
@@ -2943,11 +2938,11 @@
       <c r="B40" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="19"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="28"/>
       <c r="I40" s="1"/>
       <c r="J40" t="s">
         <v>12</v>
@@ -2967,10 +2962,10 @@
       <c r="C41" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="14"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="28"/>
       <c r="I41" s="1"/>
       <c r="J41" t="s">
         <v>15</v>
@@ -2994,16 +2989,16 @@
         <v>3</v>
       </c>
       <c r="C42" s="25"/>
-      <c r="D42" s="18" t="s">
+      <c r="D42" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="E42" s="18" t="s">
+      <c r="E42" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="18" t="s">
+      <c r="F42" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="G42" s="19"/>
+      <c r="G42" s="28"/>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
@@ -3013,7 +3008,7 @@
       <c r="D43" s="54"/>
       <c r="E43" s="54"/>
       <c r="F43" s="54"/>
-      <c r="G43" s="20"/>
+      <c r="G43" s="29"/>
       <c r="K43" s="1">
         <f>SUM(K3:K41)</f>
         <v>120</v>
@@ -3102,34 +3097,11 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="D23:D26"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="F42:F44"/>
     <mergeCell ref="G21:G22"/>
     <mergeCell ref="G23:G25"/>
     <mergeCell ref="G39:G43"/>
@@ -3146,11 +3118,34 @@
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="D42:D44"/>
     <mergeCell ref="F39:F41"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="D23:D26"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="E24:E26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3209,7 +3204,7 @@
       <c r="B3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="20" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="48" t="s">
@@ -3241,7 +3236,7 @@
       <c r="B4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="31"/>
+      <c r="C4" s="20"/>
       <c r="D4" s="49"/>
       <c r="E4" s="49"/>
       <c r="F4" s="49"/>
@@ -3262,7 +3257,7 @@
       <c r="B5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="31"/>
+      <c r="C5" s="20"/>
       <c r="D5" s="49"/>
       <c r="E5" s="49"/>
       <c r="F5" s="49"/>
@@ -3351,19 +3346,19 @@
       <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="15" t="s">
+      <c r="C12" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="30" t="s">
         <v>19</v>
       </c>
       <c r="E12" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="14" t="s">
+      <c r="F12" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="19" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="1"/>
@@ -3382,11 +3377,11 @@
       <c r="B13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="33"/>
+      <c r="C13" s="36"/>
       <c r="D13" s="44"/>
       <c r="E13" s="46"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="14"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="19"/>
       <c r="J13" s="1" t="s">
         <v>14</v>
       </c>
@@ -3406,7 +3401,7 @@
       </c>
       <c r="D14" s="26"/>
       <c r="E14" s="46"/>
-      <c r="F14" s="27" t="s">
+      <c r="F14" s="33" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="47" t="s">
@@ -3450,7 +3445,7 @@
       </c>
       <c r="C16" s="44"/>
       <c r="D16" s="44"/>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F16" s="44"/>
@@ -3464,7 +3459,7 @@
       </c>
       <c r="C17" s="26"/>
       <c r="D17" s="26"/>
-      <c r="E17" s="33"/>
+      <c r="E17" s="36"/>
       <c r="F17" s="26"/>
       <c r="G17" s="6"/>
     </row>
@@ -3495,19 +3490,19 @@
       <c r="B21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="40" t="s">
+      <c r="C21" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="30" t="s">
+      <c r="D21" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="31" t="s">
+      <c r="F21" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="20" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="1"/>
@@ -3526,11 +3521,11 @@
       <c r="B22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="41"/>
+      <c r="C22" s="15"/>
       <c r="D22" s="44"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="31"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="20"/>
       <c r="I22" s="1"/>
       <c r="J22" t="s">
         <v>12</v>
@@ -3547,13 +3542,13 @@
       <c r="B23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="42"/>
+      <c r="C23" s="16"/>
       <c r="D23" s="26"/>
-      <c r="E23" s="30"/>
+      <c r="E23" s="18"/>
       <c r="F23" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="14" t="s">
+      <c r="G23" s="19" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -3573,15 +3568,15 @@
       <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="42"/>
-      <c r="D24" s="27" t="s">
+      <c r="C24" s="16"/>
+      <c r="D24" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="19" t="s">
         <v>61</v>
       </c>
       <c r="F24" s="25"/>
-      <c r="G24" s="14"/>
+      <c r="G24" s="19"/>
       <c r="J24" t="s">
         <v>31</v>
       </c>
@@ -3597,20 +3592,20 @@
       <c r="B25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="42"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="14"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="19"/>
       <c r="F25" s="25"/>
-      <c r="G25" s="14"/>
+      <c r="G25" s="19"/>
       <c r="O25" s="1"/>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="43"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="14"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="19"/>
       <c r="F26" s="26"/>
       <c r="G26" s="6"/>
       <c r="O26" s="1"/>
@@ -3647,19 +3642,19 @@
       <c r="B30" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="27" t="s">
+      <c r="C30" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="31" t="s">
+      <c r="F30" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="20" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="1"/>
@@ -3679,11 +3674,11 @@
       <c r="B31" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="31"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="20"/>
       <c r="J31" t="s">
         <v>12</v>
       </c>
@@ -3700,17 +3695,17 @@
       <c r="B32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="27" t="s">
+      <c r="C32" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="17"/>
-      <c r="E32" s="34" t="s">
+      <c r="D32" s="31"/>
+      <c r="E32" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="37" t="s">
+      <c r="F32" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="14" t="s">
+      <c r="G32" s="19" t="s">
         <v>22</v>
       </c>
       <c r="J32" s="1" t="s">
@@ -3730,13 +3725,13 @@
       <c r="B33" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="28"/>
-      <c r="D33" s="27" t="s">
+      <c r="C33" s="37"/>
+      <c r="D33" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="35"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="14"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="19"/>
       <c r="J33" t="s">
         <v>31</v>
       </c>
@@ -3752,21 +3747,21 @@
       <c r="B34" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="14"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="19"/>
       <c r="O34" s="1"/>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="39"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="43"/>
       <c r="G35" s="6"/>
       <c r="O35" s="1"/>
     </row>
@@ -3802,16 +3797,16 @@
       <c r="B39" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="30" t="s">
+      <c r="D39" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="18" t="s">
+      <c r="F39" s="27" t="s">
         <v>32</v>
       </c>
       <c r="G39" s="21" t="s">
@@ -3834,10 +3829,10 @@
       <c r="B40" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="14"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="19"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="28"/>
       <c r="G40" s="22"/>
       <c r="I40" s="1"/>
       <c r="J40" t="s">
@@ -3858,9 +3853,9 @@
       <c r="C41" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="17"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="19"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="28"/>
       <c r="G41" s="22"/>
       <c r="I41" s="1"/>
       <c r="J41" t="s">
@@ -3885,13 +3880,13 @@
         <v>37</v>
       </c>
       <c r="C42" s="25"/>
-      <c r="D42" s="27" t="s">
+      <c r="D42" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E42" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="19"/>
+      <c r="F42" s="28"/>
       <c r="G42" s="22"/>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.35">
@@ -3899,9 +3894,9 @@
         <v>38</v>
       </c>
       <c r="C43" s="25"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="19"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="28"/>
       <c r="G43" s="23"/>
       <c r="K43" s="1">
         <f>SUM(K3:K41)</f>
@@ -3922,9 +3917,900 @@
         <v>39</v>
       </c>
       <c r="C44" s="26"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="20"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="6"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K46">
+        <f>5*4*5</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K47">
+        <f>4*5</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K48">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="K49">
+        <f>120-5-4</f>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J50" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K50" s="1">
+        <f>K3+K12</f>
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="51" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J51" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K51" s="1">
+        <f>K13+K21+K30+K39</f>
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="52" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J52" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K52" s="1">
+        <f>K4+K14+K22+K31+K40</f>
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="53" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J53" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K53" s="1">
+        <f>K5+K15+K23+K24+K32+K33+K41</f>
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="54" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="K54">
+        <f>SUM(K50:K53)</f>
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="47">
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C21:C26"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B72F34B-8139-4D0E-8882-03145DDD5E1F}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:O54"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="2" customWidth="1"/>
+    <col min="2" max="2" width="10.90625" style="2"/>
+    <col min="3" max="4" width="12.6328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.7265625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="4.36328125" customWidth="1"/>
+    <col min="10" max="10" width="15.7265625" customWidth="1"/>
+    <col min="13" max="14" width="10.90625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B1" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B2" s="4"/>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="1">
+        <f>2.5+2.5+2.5+2.5+2</f>
+        <v>12</v>
+      </c>
+      <c r="M3" s="9">
+        <f>K3</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="20"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="50"/>
+      <c r="I4" s="1"/>
+      <c r="J4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4">
+        <f>2.5+2.5+2.5</f>
+        <v>7.5</v>
+      </c>
+      <c r="N4" s="2">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="20"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5">
+        <f>2.5+2</f>
+        <v>4.5</v>
+      </c>
+      <c r="M5" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="N5" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="19"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="19"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="5"/>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B10" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B11" s="4"/>
+      <c r="C11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" s="1">
+        <f>3+2.5+3+2</f>
+        <v>10.5</v>
+      </c>
+      <c r="M12" s="2">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="36"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="19"/>
+      <c r="J13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" s="1">
+        <v>3</v>
+      </c>
+      <c r="M13" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="26"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14">
+        <f>2+2.5+2+2</f>
+        <v>8.5</v>
+      </c>
+      <c r="N14" s="2">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="44"/>
+      <c r="D15" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="46"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="47"/>
+      <c r="J15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="N15" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="44"/>
+      <c r="G16" s="47"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="6"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B19" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B20" s="4"/>
+      <c r="C20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K21" s="1">
+        <f>2.5+3</f>
+        <v>5.5</v>
+      </c>
+      <c r="M21" s="2">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="15"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="20"/>
+      <c r="I22" s="1"/>
+      <c r="J22" t="s">
+        <v>12</v>
+      </c>
+      <c r="K22">
+        <f>2.5+2</f>
+        <v>4.5</v>
+      </c>
+      <c r="N22" s="2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="16"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K23" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="M23" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="O23" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="16"/>
+      <c r="D24" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="25"/>
+      <c r="G24" s="19"/>
+      <c r="J24" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24">
+        <v>4.5</v>
+      </c>
+      <c r="N24" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O24" s="1"/>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B25" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="16"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="19"/>
+      <c r="O25" s="1"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="17"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="6"/>
+      <c r="O26" s="1"/>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="O27" s="1"/>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B28" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="O28" s="1"/>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B29" s="4"/>
+      <c r="C29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O29" s="1"/>
+    </row>
+    <row r="30" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K30" s="1">
+        <f>3+2.5+2+3</f>
+        <v>10.5</v>
+      </c>
+      <c r="M30" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="O30" s="1"/>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="31"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="20"/>
+      <c r="J31" t="s">
+        <v>12</v>
+      </c>
+      <c r="K31">
+        <f>2+2.5+2</f>
+        <v>6.5</v>
+      </c>
+      <c r="N31" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="O31" s="1"/>
+    </row>
+    <row r="32" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="31"/>
+      <c r="E32" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K32" s="1">
+        <v>2</v>
+      </c>
+      <c r="M32" s="10">
+        <v>2</v>
+      </c>
+      <c r="O32" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="37"/>
+      <c r="D33" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="39"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="19"/>
+      <c r="J33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K33" s="1">
+        <v>5</v>
+      </c>
+      <c r="N33" s="2">
+        <v>5</v>
+      </c>
+      <c r="O33" s="1"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B34" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="19"/>
+      <c r="O34" s="1"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="43"/>
+      <c r="G35" s="6"/>
+      <c r="O35" s="1"/>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="O36" s="1"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B37" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O37" s="1"/>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B38" s="4"/>
+      <c r="C38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O38" s="1"/>
+    </row>
+    <row r="39" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K39" s="1">
+        <f>3+2.5</f>
+        <v>5.5</v>
+      </c>
+      <c r="M39" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="O39" s="1"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="19"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="22"/>
+      <c r="I40" s="1"/>
+      <c r="J40" t="s">
+        <v>12</v>
+      </c>
+      <c r="K40">
+        <v>2.5</v>
+      </c>
+      <c r="N40" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="O40" s="1"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="31"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="28"/>
+      <c r="G41" s="22"/>
+      <c r="I41" s="1"/>
+      <c r="J41" t="s">
+        <v>15</v>
+      </c>
+      <c r="K41">
+        <v>12</v>
+      </c>
+      <c r="M41" s="10">
+        <f>4.5</f>
+        <v>4.5</v>
+      </c>
+      <c r="N41" s="2">
+        <f>2+2.5+5</f>
+        <v>9.5</v>
+      </c>
+      <c r="O41" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="25"/>
+      <c r="D42" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="28"/>
+      <c r="G42" s="22"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" s="25"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="23"/>
+      <c r="K43" s="1">
+        <f>SUM(K3:K41)</f>
+        <v>111</v>
+      </c>
+      <c r="L43" s="1"/>
+      <c r="M43" s="9">
+        <f>SUM(M3:M41)</f>
+        <v>59.5</v>
+      </c>
+      <c r="N43" s="9">
+        <f>SUM(N3:N41)</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="26"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="29"/>
       <c r="G44" s="6"/>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.35">
@@ -4045,895 +4931,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B72F34B-8139-4D0E-8882-03145DDD5E1F}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B1:O54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="10.90625" style="2"/>
-    <col min="3" max="4" width="12.6328125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.7265625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.1796875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="4.36328125" customWidth="1"/>
-    <col min="10" max="10" width="15.7265625" customWidth="1"/>
-    <col min="13" max="14" width="10.90625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B1" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B2" s="4"/>
-      <c r="C2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="1">
-        <f>2.5+2.5+2.5+2.5+2</f>
-        <v>12</v>
-      </c>
-      <c r="M3" s="9">
-        <f>K3</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="50"/>
-      <c r="I4" s="1"/>
-      <c r="J4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K4">
-        <f>2.5+2.5+2.5</f>
-        <v>7.5</v>
-      </c>
-      <c r="N4" s="2">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5">
-        <f>2.5+2</f>
-        <v>4.5</v>
-      </c>
-      <c r="M5" s="10">
-        <v>1.5</v>
-      </c>
-      <c r="N5" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="14"/>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="14"/>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="5"/>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B10" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B11" s="4"/>
-      <c r="C11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K12" s="1">
-        <f>3+2.5+3+2</f>
-        <v>10.5</v>
-      </c>
-      <c r="M12" s="2">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B13" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="14"/>
-      <c r="J13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="1">
-        <v>3</v>
-      </c>
-      <c r="M13" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B14" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="J14" t="s">
-        <v>12</v>
-      </c>
-      <c r="K14">
-        <f>2+2.5+2+2</f>
-        <v>8.5</v>
-      </c>
-      <c r="N14" s="2">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="44"/>
-      <c r="D15" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="46"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="47"/>
-      <c r="J15" t="s">
-        <v>15</v>
-      </c>
-      <c r="K15">
-        <v>2</v>
-      </c>
-      <c r="N15" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B16" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="44"/>
-      <c r="G16" s="47"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="6"/>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B19" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B20" s="4"/>
-      <c r="C20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="F21" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K21" s="1">
-        <f>2.5+3</f>
-        <v>5.5</v>
-      </c>
-      <c r="M21" s="2">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B22" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="41"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="31"/>
-      <c r="I22" s="1"/>
-      <c r="J22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K22">
-        <f>2.5+2</f>
-        <v>4.5</v>
-      </c>
-      <c r="N22" s="2">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="23" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="42"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K23" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="M23" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="O23" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" s="42"/>
-      <c r="D24" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="F24" s="25"/>
-      <c r="G24" s="14"/>
-      <c r="J24" t="s">
-        <v>31</v>
-      </c>
-      <c r="K24">
-        <v>4.5</v>
-      </c>
-      <c r="N24" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="O24" s="1"/>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B25" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="42"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="14"/>
-      <c r="O25" s="1"/>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="43"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="6"/>
-      <c r="O26" s="1"/>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="O27" s="1"/>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B28" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="O28" s="1"/>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B29" s="4"/>
-      <c r="C29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="O29" s="1"/>
-    </row>
-    <row r="30" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="F30" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K30" s="1">
-        <f>3+2.5+2+3</f>
-        <v>10.5</v>
-      </c>
-      <c r="M30" s="2">
-        <v>10.5</v>
-      </c>
-      <c r="O30" s="1"/>
-    </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B31" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="31"/>
-      <c r="J31" t="s">
-        <v>12</v>
-      </c>
-      <c r="K31">
-        <f>2+2.5+2</f>
-        <v>6.5</v>
-      </c>
-      <c r="N31" s="2">
-        <v>6.5</v>
-      </c>
-      <c r="O31" s="1"/>
-    </row>
-    <row r="32" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="17"/>
-      <c r="E32" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K32" s="1">
-        <v>2</v>
-      </c>
-      <c r="M32" s="10">
-        <v>2</v>
-      </c>
-      <c r="O32" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" s="28"/>
-      <c r="D33" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="35"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="14"/>
-      <c r="J33" t="s">
-        <v>31</v>
-      </c>
-      <c r="K33" s="1">
-        <v>5</v>
-      </c>
-      <c r="N33" s="2">
-        <v>5</v>
-      </c>
-      <c r="O33" s="1"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B34" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="14"/>
-      <c r="O34" s="1"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="6"/>
-      <c r="O35" s="1"/>
-    </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="O36" s="1"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B37" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O37" s="1"/>
-    </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B38" s="4"/>
-      <c r="C38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="O38" s="1"/>
-    </row>
-    <row r="39" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="G39" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K39" s="1">
-        <f>3+2.5</f>
-        <v>5.5</v>
-      </c>
-      <c r="M39" s="2">
-        <v>5.5</v>
-      </c>
-      <c r="O39" s="1"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B40" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="14"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="22"/>
-      <c r="I40" s="1"/>
-      <c r="J40" t="s">
-        <v>12</v>
-      </c>
-      <c r="K40">
-        <v>2.5</v>
-      </c>
-      <c r="N40" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="O40" s="1"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41" s="17"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="22"/>
-      <c r="I41" s="1"/>
-      <c r="J41" t="s">
-        <v>15</v>
-      </c>
-      <c r="K41">
-        <v>12</v>
-      </c>
-      <c r="M41" s="10">
-        <f>4.5</f>
-        <v>4.5</v>
-      </c>
-      <c r="N41" s="2">
-        <f>2+2.5+5</f>
-        <v>9.5</v>
-      </c>
-      <c r="O41" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C42" s="25"/>
-      <c r="D42" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="19"/>
-      <c r="G42" s="22"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C43" s="25"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="23"/>
-      <c r="K43" s="1">
-        <f>SUM(K3:K41)</f>
-        <v>111</v>
-      </c>
-      <c r="L43" s="1"/>
-      <c r="M43" s="9">
-        <f>SUM(M3:M41)</f>
-        <v>59.5</v>
-      </c>
-      <c r="N43" s="9">
-        <f>SUM(N3:N41)</f>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C44" s="26"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="6"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K46">
-        <f>5*4*5</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K47">
-        <f>4*5</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K48">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="49" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="K49">
-        <f>120-5-4</f>
-        <v>111</v>
-      </c>
-    </row>
-    <row r="50" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J50" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K50" s="1">
-        <f>K3+K12</f>
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="51" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J51" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K51" s="1">
-        <f>K13+K21+K30+K39</f>
-        <v>24.5</v>
-      </c>
-    </row>
-    <row r="52" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J52" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K52" s="1">
-        <f>K4+K14+K22+K31+K40</f>
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="53" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J53" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K53" s="1">
-        <f>K5+K15+K23+K24+K32+K33+K41</f>
-        <v>34.5</v>
-      </c>
-    </row>
-    <row r="54" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="K54">
-        <f>SUM(K50:K53)</f>
-        <v>111</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="47">
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C21:C26"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Horarios/HorarioWAN_2026.xlsx
+++ b/Horarios/HorarioWAN_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecmx-my.sharepoint.com/personal/lperezf_tec_mx/Documents/Documents/GitLiz/WAN/Horarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{FC23BDE9-CBF9-4CD9-B661-15FDB57BE38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6ECF9B62-7998-4FB7-B4A0-165D1B3F8DC8}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="8_{FC23BDE9-CBF9-4CD9-B661-15FDB57BE38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89C49A76-0998-4EA9-B622-0889C0661721}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
   </bookViews>
@@ -644,6 +644,96 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -656,66 +746,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -733,36 +763,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1092,7 +1092,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:I44"/>
+  <dimension ref="B1:G44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -1103,12 +1103,12 @@
     <col min="8" max="8" width="4.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B1" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B2" s="4"/>
       <c r="C2" s="3" t="s">
         <v>6</v>
@@ -1126,94 +1126,92 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="50" t="s">
+      <c r="D3" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="51" t="s">
+      <c r="F3" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="52"/>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="C4" s="27"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="15"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="51" t="s">
+      <c r="C5" s="27"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="14" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="C6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="50" t="s">
+      <c r="E6" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="53"/>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="G6" s="16"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="52"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="15"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
       <c r="G8" s="5"/>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="8" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="4"/>
       <c r="C11" s="3" t="s">
         <v>6</v>
@@ -1231,93 +1229,92 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="45" t="s">
+      <c r="C12" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="19" t="s">
+      <c r="F12" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="I12" s="1"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="36"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="19"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="C13" s="24"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="30"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="45" t="s">
+      <c r="C14" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="33" t="s">
+      <c r="D14" s="22"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="47" t="s">
+      <c r="G14" s="32" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="44"/>
-      <c r="D15" s="45" t="s">
+      <c r="C15" s="21"/>
+      <c r="D15" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="46"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="47"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="E15" s="29"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="32"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="44"/>
-      <c r="G16" s="47"/>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="21"/>
+      <c r="G16" s="32"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="26"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="22"/>
       <c r="G17" s="6"/>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B19" s="8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B20" s="4"/>
       <c r="C20" s="3" t="s">
         <v>6</v>
@@ -1335,92 +1332,90 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="D21" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="20" t="s">
+      <c r="F21" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="I21" s="1"/>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="18"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="20"/>
-      <c r="I22" s="1"/>
-    </row>
-    <row r="23" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C22" s="21"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="27"/>
+    </row>
+    <row r="23" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="24" t="s">
+      <c r="C23" s="22"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="19" t="s">
+      <c r="G23" s="30" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="D24" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="16"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="19"/>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="E24" s="46"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="30"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="19"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="19"/>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="C25" s="42"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="30"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="26"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="22"/>
       <c r="G26" s="6"/>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B28" s="8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B29" s="4"/>
       <c r="C29" s="3" t="s">
         <v>6</v>
@@ -1438,93 +1433,92 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="33" t="s">
+      <c r="C30" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="20" t="s">
+      <c r="F30" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="I30" s="1"/>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B31" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="31"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="20"/>
-    </row>
-    <row r="32" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C31" s="41"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="27"/>
+    </row>
+    <row r="32" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="33" t="s">
+      <c r="C32" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="31"/>
-      <c r="E32" s="38" t="s">
+      <c r="D32" s="41"/>
+      <c r="E32" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="41" t="s">
+      <c r="F32" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="19" t="s">
+      <c r="G32" s="30" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B33" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="37"/>
-      <c r="D33" s="33" t="s">
+      <c r="C33" s="42"/>
+      <c r="D33" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="39"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="19"/>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="E33" s="49"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="30"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="37"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="19"/>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="30"/>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="43"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="50"/>
+      <c r="F35" s="53"/>
       <c r="G35" s="6"/>
     </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B37" s="8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B38" s="4"/>
       <c r="C38" s="3" t="s">
         <v>6</v>
@@ -1542,93 +1536,110 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="18" t="s">
+      <c r="D39" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="27" t="s">
+      <c r="F39" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="21" t="s">
+      <c r="G39" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="I39" s="1"/>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B40" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="19"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="22"/>
-      <c r="I40" s="1"/>
-    </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="C40" s="30"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="35"/>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="24" t="s">
+      <c r="C41" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="31"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="22"/>
-      <c r="I41" s="1"/>
-    </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="D41" s="41"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="38"/>
+      <c r="G41" s="35"/>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="25"/>
-      <c r="D42" s="33" t="s">
+      <c r="C42" s="26"/>
+      <c r="D42" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="19" t="s">
+      <c r="E42" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="28"/>
-      <c r="G42" s="22"/>
-    </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="F42" s="38"/>
+      <c r="G42" s="35"/>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C43" s="25"/>
-      <c r="D43" s="37"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="23"/>
-    </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="C43" s="26"/>
+      <c r="D43" s="42"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="36"/>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="26"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="29"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="39"/>
       <c r="G44" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="F21:F22"/>
     <mergeCell ref="F23:F26"/>
@@ -1640,36 +1651,16 @@
     <mergeCell ref="D12:D14"/>
     <mergeCell ref="E12:E15"/>
     <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="D42:D44"/>
     <mergeCell ref="E21:E26"/>
     <mergeCell ref="C21:C23"/>
     <mergeCell ref="C24:C26"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="D33:D35"/>
     <mergeCell ref="D24:D26"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1719,19 +1710,19 @@
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="50" t="s">
+      <c r="D3" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="50" t="s">
+      <c r="F3" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="17" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1739,21 +1730,21 @@
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="50"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="17"/>
     </row>
     <row r="5" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="19" t="s">
+      <c r="C5" s="27"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="30" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1761,38 +1752,38 @@
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="C6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="50" t="s">
+      <c r="E6" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="19"/>
+      <c r="G6" s="30"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="19"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="30"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
@@ -1822,19 +1813,19 @@
       <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="45" t="s">
+      <c r="C12" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="19" t="s">
+      <c r="F12" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="30" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1842,25 +1833,25 @@
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="36"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="19"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="30"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="45" t="s">
+      <c r="C14" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="33" t="s">
+      <c r="D14" s="22"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="47" t="s">
+      <c r="G14" s="32" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1868,34 +1859,34 @@
       <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="44"/>
-      <c r="D15" s="45" t="s">
+      <c r="C15" s="21"/>
+      <c r="D15" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="46"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="47"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="32"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="44"/>
-      <c r="G16" s="47"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="21"/>
+      <c r="G16" s="32"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="26"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="22"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.35">
@@ -1925,19 +1916,19 @@
       <c r="B21" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="D21" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="20" t="s">
+      <c r="F21" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="27" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1945,23 +1936,23 @@
       <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="18"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="20"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="27"/>
     </row>
     <row r="23" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="24" t="s">
+      <c r="C23" s="22"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="19" t="s">
+      <c r="G23" s="30" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1969,34 +1960,34 @@
       <c r="B24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="D24" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="16"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="19"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="30"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="19"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="19"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="30"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="26"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="22"/>
       <c r="G26" s="6"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
@@ -2026,19 +2017,19 @@
       <c r="B30" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="33" t="s">
+      <c r="C30" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="20" t="s">
+      <c r="F30" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="27" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2046,27 +2037,27 @@
       <c r="B31" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="31"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="20"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="27"/>
     </row>
     <row r="32" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="33" t="s">
+      <c r="C32" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="31"/>
-      <c r="E32" s="38" t="s">
+      <c r="D32" s="41"/>
+      <c r="E32" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="41" t="s">
+      <c r="F32" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="19" t="s">
+      <c r="G32" s="30" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2074,32 +2065,32 @@
       <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="37"/>
-      <c r="D33" s="33" t="s">
+      <c r="C33" s="42"/>
+      <c r="D33" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="39"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="19"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="30"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="37"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="19"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="30"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="43"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="50"/>
+      <c r="F35" s="53"/>
       <c r="G35" s="6"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.35">
@@ -2129,19 +2120,19 @@
       <c r="B39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="18" t="s">
+      <c r="D39" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="27" t="s">
+      <c r="F39" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="21" t="s">
+      <c r="G39" s="34" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2149,68 +2140,83 @@
       <c r="B40" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="19"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="22"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="35"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="24" t="s">
+      <c r="C41" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="31"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="22"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="38"/>
+      <c r="G41" s="35"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="25"/>
-      <c r="D42" s="33" t="s">
+      <c r="C42" s="26"/>
+      <c r="D42" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="19" t="s">
+      <c r="E42" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="28"/>
-      <c r="G42" s="22"/>
+      <c r="F42" s="38"/>
+      <c r="G42" s="35"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="25"/>
-      <c r="D43" s="37"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="23"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="42"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="36"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="26"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="29"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="39"/>
       <c r="G44" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E26"/>
+    <mergeCell ref="C24:C26"/>
     <mergeCell ref="G21:G22"/>
     <mergeCell ref="G23:G25"/>
     <mergeCell ref="C30:C31"/>
@@ -2227,29 +2233,14 @@
     <mergeCell ref="F21:F22"/>
     <mergeCell ref="F23:F26"/>
     <mergeCell ref="D24:D26"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E26"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E42:E44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2312,19 +2303,19 @@
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="50" t="s">
+      <c r="D3" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="50" t="s">
+      <c r="F3" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="17" t="s">
         <v>18</v>
       </c>
       <c r="I3" s="1"/>
@@ -2344,11 +2335,11 @@
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="50"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="17"/>
       <c r="I4" s="1"/>
       <c r="J4" t="s">
         <v>12</v>
@@ -2365,11 +2356,11 @@
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="19" t="s">
+      <c r="C5" s="27"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="30" t="s">
         <v>22</v>
       </c>
       <c r="J5" t="s">
@@ -2393,38 +2384,38 @@
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="C6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="50" t="s">
+      <c r="E6" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="19"/>
+      <c r="G6" s="30"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="19"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="30"/>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.35">
@@ -2454,19 +2445,19 @@
       <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="45" t="s">
+      <c r="C12" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="19" t="s">
+      <c r="F12" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="30" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="1"/>
@@ -2485,11 +2476,11 @@
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="36"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="19"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="30"/>
       <c r="J13" s="1" t="s">
         <v>14</v>
       </c>
@@ -2504,15 +2495,15 @@
       <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="45" t="s">
+      <c r="C14" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="33" t="s">
+      <c r="D14" s="22"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="47" t="s">
+      <c r="G14" s="32" t="s">
         <v>23</v>
       </c>
       <c r="J14" t="s">
@@ -2530,13 +2521,13 @@
       <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="44"/>
-      <c r="D15" s="45" t="s">
+      <c r="C15" s="21"/>
+      <c r="D15" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="46"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="47"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="32"/>
       <c r="J15" t="s">
         <v>15</v>
       </c>
@@ -2551,13 +2542,13 @@
       <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="44"/>
-      <c r="G16" s="47"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="21"/>
+      <c r="G16" s="32"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
@@ -2565,10 +2556,10 @@
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="26"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="22"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.35">
@@ -2598,19 +2589,19 @@
       <c r="B21" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="18" t="s">
+      <c r="C21" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="20" t="s">
+      <c r="F21" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="27" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="1"/>
@@ -2629,11 +2620,11 @@
       <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="44"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="20"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="27"/>
       <c r="I22" s="1"/>
       <c r="J22" t="s">
         <v>12</v>
@@ -2650,15 +2641,15 @@
       <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="26"/>
-      <c r="D23" s="24" t="s">
+      <c r="C23" s="22"/>
+      <c r="D23" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="18"/>
-      <c r="F23" s="33" t="s">
+      <c r="E23" s="33"/>
+      <c r="F23" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="19" t="s">
+      <c r="G23" s="30" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -2678,15 +2669,15 @@
       <c r="B24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="33" t="s">
+      <c r="C24" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="25"/>
-      <c r="E24" s="19" t="s">
+      <c r="D24" s="26"/>
+      <c r="E24" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="37"/>
-      <c r="G24" s="19"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="30"/>
       <c r="J24" t="s">
         <v>31</v>
       </c>
@@ -2702,21 +2693,21 @@
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="37"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="19"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="30"/>
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="34"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="34"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="43"/>
       <c r="G26" s="6"/>
       <c r="P26" s="1"/>
     </row>
@@ -2752,19 +2743,19 @@
       <c r="B30" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="33" t="s">
+      <c r="C30" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="20" t="s">
+      <c r="F30" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="27" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="1"/>
@@ -2784,11 +2775,11 @@
       <c r="B31" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="32"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="20"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="27"/>
       <c r="J31" t="s">
         <v>12</v>
       </c>
@@ -2805,15 +2796,15 @@
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="38" t="s">
+      <c r="C32" s="41"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="41" t="s">
+      <c r="F32" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="19" t="s">
+      <c r="G32" s="30" t="s">
         <v>22</v>
       </c>
       <c r="J32" s="1" t="s">
@@ -2833,15 +2824,15 @@
       <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="33" t="s">
+      <c r="C33" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="33" t="s">
+      <c r="D33" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="39"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="19"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="30"/>
       <c r="J33" t="s">
         <v>31</v>
       </c>
@@ -2857,21 +2848,21 @@
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="37"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="19"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="30"/>
       <c r="P34" s="1"/>
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="43"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="50"/>
+      <c r="F35" s="53"/>
       <c r="G35" s="6"/>
       <c r="P35" s="1"/>
     </row>
@@ -2907,19 +2898,19 @@
       <c r="B39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="19" t="s">
+      <c r="D39" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="F39" s="19" t="s">
+      <c r="E39" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="G39" s="27" t="s">
+      <c r="G39" s="37" t="s">
         <v>57</v>
       </c>
       <c r="I39" s="1"/>
@@ -2938,11 +2929,11 @@
       <c r="B40" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="32"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="28"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="38"/>
       <c r="I40" s="1"/>
       <c r="J40" t="s">
         <v>12</v>
@@ -2959,13 +2950,13 @@
       <c r="B41" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="24" t="s">
+      <c r="C41" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="19"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="28"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="41"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="38"/>
       <c r="I41" s="1"/>
       <c r="J41" t="s">
         <v>15</v>
@@ -2988,27 +2979,27 @@
       <c r="B42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="25"/>
-      <c r="D42" s="27" t="s">
+      <c r="C42" s="26"/>
+      <c r="D42" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="E42" s="27" t="s">
+      <c r="E42" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="27" t="s">
+      <c r="F42" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="G42" s="28"/>
+      <c r="G42" s="38"/>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="25"/>
+      <c r="C43" s="26"/>
       <c r="D43" s="54"/>
       <c r="E43" s="54"/>
       <c r="F43" s="54"/>
-      <c r="G43" s="29"/>
+      <c r="G43" s="39"/>
       <c r="K43" s="1">
         <f>SUM(K3:K41)</f>
         <v>120</v>
@@ -3030,7 +3021,7 @@
       <c r="B44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="26"/>
+      <c r="C44" s="22"/>
       <c r="D44" s="55"/>
       <c r="E44" s="55"/>
       <c r="F44" s="55"/>
@@ -3097,11 +3088,34 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="D23:D26"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
     <mergeCell ref="G21:G22"/>
     <mergeCell ref="G23:G25"/>
     <mergeCell ref="G39:G43"/>
@@ -3118,34 +3132,11 @@
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="D42:D44"/>
     <mergeCell ref="F39:F41"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="D23:D26"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="F42:F44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3204,19 +3195,19 @@
       <c r="B3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="50" t="s">
+      <c r="D3" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="51" t="s">
+      <c r="F3" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="14" t="s">
         <v>62</v>
       </c>
       <c r="I3" s="1"/>
@@ -3236,11 +3227,11 @@
       <c r="B4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="52"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="15"/>
       <c r="I4" s="1"/>
       <c r="J4" t="s">
         <v>12</v>
@@ -3257,11 +3248,11 @@
       <c r="B5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="51" t="s">
+      <c r="C5" s="27"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="14" t="s">
         <v>63</v>
       </c>
       <c r="J5" t="s">
@@ -3285,38 +3276,38 @@
       <c r="B6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="C6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="50" t="s">
+      <c r="E6" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="53"/>
+      <c r="G6" s="16"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="52"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="15"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.35">
@@ -3346,19 +3337,19 @@
       <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="45" t="s">
+      <c r="C12" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="19" t="s">
+      <c r="F12" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="30" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="1"/>
@@ -3377,11 +3368,11 @@
       <c r="B13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="36"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="19"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="30"/>
       <c r="J13" s="1" t="s">
         <v>14</v>
       </c>
@@ -3396,15 +3387,15 @@
       <c r="B14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="45" t="s">
+      <c r="C14" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="33" t="s">
+      <c r="D14" s="22"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="47" t="s">
+      <c r="G14" s="32" t="s">
         <v>23</v>
       </c>
       <c r="J14" t="s">
@@ -3422,13 +3413,13 @@
       <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="44"/>
-      <c r="D15" s="45" t="s">
+      <c r="C15" s="21"/>
+      <c r="D15" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="46"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="47"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="32"/>
       <c r="J15" t="s">
         <v>15</v>
       </c>
@@ -3443,13 +3434,13 @@
       <c r="B16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="44"/>
-      <c r="G16" s="47"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="21"/>
+      <c r="G16" s="32"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
@@ -3457,10 +3448,10 @@
       <c r="B17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="26"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="22"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.35">
@@ -3490,19 +3481,19 @@
       <c r="B21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="18" t="s">
+      <c r="D21" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="20" t="s">
+      <c r="F21" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="27" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="1"/>
@@ -3521,11 +3512,11 @@
       <c r="B22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="20"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="27"/>
       <c r="I22" s="1"/>
       <c r="J22" t="s">
         <v>12</v>
@@ -3542,13 +3533,13 @@
       <c r="B23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="16"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="24" t="s">
+      <c r="C23" s="46"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="19" t="s">
+      <c r="G23" s="30" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -3568,15 +3559,15 @@
       <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="16"/>
-      <c r="D24" s="33" t="s">
+      <c r="C24" s="46"/>
+      <c r="D24" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="19" t="s">
+      <c r="E24" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="25"/>
-      <c r="G24" s="19"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="30"/>
       <c r="J24" t="s">
         <v>31</v>
       </c>
@@ -3592,21 +3583,21 @@
       <c r="B25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="19"/>
+      <c r="C25" s="46"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="30"/>
       <c r="O25" s="1"/>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="26"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="22"/>
       <c r="G26" s="6"/>
       <c r="O26" s="1"/>
     </row>
@@ -3642,19 +3633,19 @@
       <c r="B30" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="33" t="s">
+      <c r="C30" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="20" t="s">
+      <c r="F30" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="27" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="1"/>
@@ -3674,11 +3665,11 @@
       <c r="B31" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="31"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="20"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="27"/>
       <c r="J31" t="s">
         <v>12</v>
       </c>
@@ -3695,17 +3686,17 @@
       <c r="B32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="33" t="s">
+      <c r="C32" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="31"/>
-      <c r="E32" s="38" t="s">
+      <c r="D32" s="41"/>
+      <c r="E32" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="41" t="s">
+      <c r="F32" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="19" t="s">
+      <c r="G32" s="30" t="s">
         <v>22</v>
       </c>
       <c r="J32" s="1" t="s">
@@ -3725,13 +3716,13 @@
       <c r="B33" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="37"/>
-      <c r="D33" s="33" t="s">
+      <c r="C33" s="42"/>
+      <c r="D33" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="39"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="19"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="30"/>
       <c r="J33" t="s">
         <v>31</v>
       </c>
@@ -3747,21 +3738,21 @@
       <c r="B34" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="37"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="19"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="30"/>
       <c r="O34" s="1"/>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="43"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="50"/>
+      <c r="F35" s="53"/>
       <c r="G35" s="6"/>
       <c r="O35" s="1"/>
     </row>
@@ -3797,19 +3788,19 @@
       <c r="B39" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="18" t="s">
+      <c r="D39" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="27" t="s">
+      <c r="F39" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="21" t="s">
+      <c r="G39" s="34" t="s">
         <v>16</v>
       </c>
       <c r="I39" s="1"/>
@@ -3829,11 +3820,11 @@
       <c r="B40" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="19"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="22"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="35"/>
       <c r="I40" s="1"/>
       <c r="J40" t="s">
         <v>12</v>
@@ -3850,13 +3841,13 @@
       <c r="B41" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="24" t="s">
+      <c r="C41" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="31"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="22"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="38"/>
+      <c r="G41" s="35"/>
       <c r="I41" s="1"/>
       <c r="J41" t="s">
         <v>15</v>
@@ -3879,25 +3870,25 @@
       <c r="B42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="25"/>
-      <c r="D42" s="33" t="s">
+      <c r="C42" s="26"/>
+      <c r="D42" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="19" t="s">
+      <c r="E42" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="28"/>
-      <c r="G42" s="22"/>
+      <c r="F42" s="38"/>
+      <c r="G42" s="35"/>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C43" s="25"/>
-      <c r="D43" s="37"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="23"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="42"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="36"/>
       <c r="K43" s="1">
         <f>SUM(K3:K41)</f>
         <v>111</v>
@@ -3916,10 +3907,901 @@
       <c r="B44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="26"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="29"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="39"/>
+      <c r="G44" s="6"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K46">
+        <f>5*4*5</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K47">
+        <f>4*5</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K48">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="K49">
+        <f>120-5-4</f>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J50" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K50" s="1">
+        <f>K3+K12</f>
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="51" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J51" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K51" s="1">
+        <f>K13+K21+K30+K39</f>
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="52" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J52" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K52" s="1">
+        <f>K4+K14+K22+K31+K40</f>
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="53" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J53" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K53" s="1">
+        <f>K5+K15+K23+K24+K32+K33+K41</f>
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="54" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="K54">
+        <f>SUM(K50:K53)</f>
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="47">
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="C21:C26"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B72F34B-8139-4D0E-8882-03145DDD5E1F}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:O54"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="2" customWidth="1"/>
+    <col min="2" max="2" width="10.90625" style="2"/>
+    <col min="3" max="4" width="12.6328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.7265625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="4.36328125" customWidth="1"/>
+    <col min="10" max="10" width="15.7265625" customWidth="1"/>
+    <col min="13" max="14" width="10.90625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B1" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B2" s="4"/>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="1">
+        <f>2.5+2.5+2.5+2.5+2</f>
+        <v>12</v>
+      </c>
+      <c r="M3" s="9">
+        <f>K3</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="27"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="17"/>
+      <c r="I4" s="1"/>
+      <c r="J4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4">
+        <f>2.5+2.5+2.5</f>
+        <v>7.5</v>
+      </c>
+      <c r="N4" s="2">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5">
+        <f>2.5+2</f>
+        <v>4.5</v>
+      </c>
+      <c r="M5" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="N5" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="30"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="30"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="5"/>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B10" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B11" s="4"/>
+      <c r="C11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" s="1">
+        <f>3+2.5+3+2</f>
+        <v>10.5</v>
+      </c>
+      <c r="M12" s="2">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="24"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="30"/>
+      <c r="J13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" s="1">
+        <v>3</v>
+      </c>
+      <c r="M13" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="22"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14">
+        <f>2+2.5+2+2</f>
+        <v>8.5</v>
+      </c>
+      <c r="N14" s="2">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="21"/>
+      <c r="D15" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="29"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="32"/>
+      <c r="J15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="N15" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="21"/>
+      <c r="G16" s="32"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="6"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B19" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B20" s="4"/>
+      <c r="C20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="44" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K21" s="1">
+        <f>2.5+3</f>
+        <v>5.5</v>
+      </c>
+      <c r="M21" s="2">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="45"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="27"/>
+      <c r="I22" s="1"/>
+      <c r="J22" t="s">
+        <v>12</v>
+      </c>
+      <c r="K22">
+        <f>2.5+2</f>
+        <v>4.5</v>
+      </c>
+      <c r="N22" s="2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="46"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K23" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="M23" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="O23" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="46"/>
+      <c r="D24" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="26"/>
+      <c r="G24" s="30"/>
+      <c r="J24" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24">
+        <v>4.5</v>
+      </c>
+      <c r="N24" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O24" s="1"/>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B25" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="46"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="30"/>
+      <c r="O25" s="1"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="47"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="6"/>
+      <c r="O26" s="1"/>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="O27" s="1"/>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B28" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="O28" s="1"/>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B29" s="4"/>
+      <c r="C29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O29" s="1"/>
+    </row>
+    <row r="30" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K30" s="1">
+        <f>3+2.5+2+3</f>
+        <v>10.5</v>
+      </c>
+      <c r="M30" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="O30" s="1"/>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="41"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="27"/>
+      <c r="J31" t="s">
+        <v>12</v>
+      </c>
+      <c r="K31">
+        <f>2+2.5+2</f>
+        <v>6.5</v>
+      </c>
+      <c r="N31" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="O31" s="1"/>
+    </row>
+    <row r="32" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="41"/>
+      <c r="E32" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K32" s="1">
+        <v>2</v>
+      </c>
+      <c r="M32" s="10">
+        <v>2</v>
+      </c>
+      <c r="O32" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="42"/>
+      <c r="D33" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="49"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="30"/>
+      <c r="J33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K33" s="1">
+        <v>5</v>
+      </c>
+      <c r="N33" s="2">
+        <v>5</v>
+      </c>
+      <c r="O33" s="1"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B34" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="30"/>
+      <c r="O34" s="1"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="43"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="50"/>
+      <c r="F35" s="53"/>
+      <c r="G35" s="6"/>
+      <c r="O35" s="1"/>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="O36" s="1"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B37" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O37" s="1"/>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B38" s="4"/>
+      <c r="C38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O38" s="1"/>
+    </row>
+    <row r="39" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K39" s="1">
+        <f>3+2.5</f>
+        <v>5.5</v>
+      </c>
+      <c r="M39" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="O39" s="1"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="30"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="35"/>
+      <c r="I40" s="1"/>
+      <c r="J40" t="s">
+        <v>12</v>
+      </c>
+      <c r="K40">
+        <v>2.5</v>
+      </c>
+      <c r="N40" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="O40" s="1"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="41"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="38"/>
+      <c r="G41" s="35"/>
+      <c r="I41" s="1"/>
+      <c r="J41" t="s">
+        <v>15</v>
+      </c>
+      <c r="K41">
+        <v>12</v>
+      </c>
+      <c r="M41" s="10">
+        <f>4.5</f>
+        <v>4.5</v>
+      </c>
+      <c r="N41" s="2">
+        <f>2+2.5+5</f>
+        <v>9.5</v>
+      </c>
+      <c r="O41" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="26"/>
+      <c r="D42" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="38"/>
+      <c r="G42" s="35"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" s="26"/>
+      <c r="D43" s="42"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="36"/>
+      <c r="K43" s="1">
+        <f>SUM(K3:K41)</f>
+        <v>111</v>
+      </c>
+      <c r="L43" s="1"/>
+      <c r="M43" s="9">
+        <f>SUM(M3:M41)</f>
+        <v>59.5</v>
+      </c>
+      <c r="N43" s="9">
+        <f>SUM(N3:N41)</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="22"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="39"/>
       <c r="G44" s="6"/>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.35">
@@ -4040,895 +4922,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B72F34B-8139-4D0E-8882-03145DDD5E1F}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B1:O54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="10.90625" style="2"/>
-    <col min="3" max="4" width="12.6328125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.7265625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.1796875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="4.36328125" customWidth="1"/>
-    <col min="10" max="10" width="15.7265625" customWidth="1"/>
-    <col min="13" max="14" width="10.90625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B1" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B2" s="4"/>
-      <c r="C2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="1">
-        <f>2.5+2.5+2.5+2.5+2</f>
-        <v>12</v>
-      </c>
-      <c r="M3" s="9">
-        <f>K3</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="50"/>
-      <c r="I4" s="1"/>
-      <c r="J4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K4">
-        <f>2.5+2.5+2.5</f>
-        <v>7.5</v>
-      </c>
-      <c r="N4" s="2">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5">
-        <f>2.5+2</f>
-        <v>4.5</v>
-      </c>
-      <c r="M5" s="10">
-        <v>1.5</v>
-      </c>
-      <c r="N5" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="19"/>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="19"/>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="5"/>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B10" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B11" s="4"/>
-      <c r="C11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K12" s="1">
-        <f>3+2.5+3+2</f>
-        <v>10.5</v>
-      </c>
-      <c r="M12" s="2">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B13" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="36"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="19"/>
-      <c r="J13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="1">
-        <v>3</v>
-      </c>
-      <c r="M13" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B14" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="J14" t="s">
-        <v>12</v>
-      </c>
-      <c r="K14">
-        <f>2+2.5+2+2</f>
-        <v>8.5</v>
-      </c>
-      <c r="N14" s="2">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="44"/>
-      <c r="D15" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="46"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="47"/>
-      <c r="J15" t="s">
-        <v>15</v>
-      </c>
-      <c r="K15">
-        <v>2</v>
-      </c>
-      <c r="N15" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B16" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="44"/>
-      <c r="G16" s="47"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="6"/>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B19" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B20" s="4"/>
-      <c r="C20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="F21" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K21" s="1">
-        <f>2.5+3</f>
-        <v>5.5</v>
-      </c>
-      <c r="M21" s="2">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B22" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="20"/>
-      <c r="I22" s="1"/>
-      <c r="J22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K22">
-        <f>2.5+2</f>
-        <v>4.5</v>
-      </c>
-      <c r="N22" s="2">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="23" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="16"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K23" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="M23" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="O23" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" s="16"/>
-      <c r="D24" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="F24" s="25"/>
-      <c r="G24" s="19"/>
-      <c r="J24" t="s">
-        <v>31</v>
-      </c>
-      <c r="K24">
-        <v>4.5</v>
-      </c>
-      <c r="N24" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="O24" s="1"/>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B25" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="19"/>
-      <c r="O25" s="1"/>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="6"/>
-      <c r="O26" s="1"/>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="O27" s="1"/>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B28" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="O28" s="1"/>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B29" s="4"/>
-      <c r="C29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="O29" s="1"/>
-    </row>
-    <row r="30" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="F30" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K30" s="1">
-        <f>3+2.5+2+3</f>
-        <v>10.5</v>
-      </c>
-      <c r="M30" s="2">
-        <v>10.5</v>
-      </c>
-      <c r="O30" s="1"/>
-    </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B31" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" s="31"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="20"/>
-      <c r="J31" t="s">
-        <v>12</v>
-      </c>
-      <c r="K31">
-        <f>2+2.5+2</f>
-        <v>6.5</v>
-      </c>
-      <c r="N31" s="2">
-        <v>6.5</v>
-      </c>
-      <c r="O31" s="1"/>
-    </row>
-    <row r="32" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="31"/>
-      <c r="E32" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="41" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K32" s="1">
-        <v>2</v>
-      </c>
-      <c r="M32" s="10">
-        <v>2</v>
-      </c>
-      <c r="O32" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" s="37"/>
-      <c r="D33" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="39"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="19"/>
-      <c r="J33" t="s">
-        <v>31</v>
-      </c>
-      <c r="K33" s="1">
-        <v>5</v>
-      </c>
-      <c r="N33" s="2">
-        <v>5</v>
-      </c>
-      <c r="O33" s="1"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B34" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C34" s="37"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="19"/>
-      <c r="O34" s="1"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="6"/>
-      <c r="O35" s="1"/>
-    </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="O36" s="1"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B37" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O37" s="1"/>
-    </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B38" s="4"/>
-      <c r="C38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="O38" s="1"/>
-    </row>
-    <row r="39" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C39" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="G39" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K39" s="1">
-        <f>3+2.5</f>
-        <v>5.5</v>
-      </c>
-      <c r="M39" s="2">
-        <v>5.5</v>
-      </c>
-      <c r="O39" s="1"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B40" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="19"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="22"/>
-      <c r="I40" s="1"/>
-      <c r="J40" t="s">
-        <v>12</v>
-      </c>
-      <c r="K40">
-        <v>2.5</v>
-      </c>
-      <c r="N40" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="O40" s="1"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41" s="31"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="22"/>
-      <c r="I41" s="1"/>
-      <c r="J41" t="s">
-        <v>15</v>
-      </c>
-      <c r="K41">
-        <v>12</v>
-      </c>
-      <c r="M41" s="10">
-        <f>4.5</f>
-        <v>4.5</v>
-      </c>
-      <c r="N41" s="2">
-        <f>2+2.5+5</f>
-        <v>9.5</v>
-      </c>
-      <c r="O41" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C42" s="25"/>
-      <c r="D42" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="28"/>
-      <c r="G42" s="22"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C43" s="25"/>
-      <c r="D43" s="37"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="23"/>
-      <c r="K43" s="1">
-        <f>SUM(K3:K41)</f>
-        <v>111</v>
-      </c>
-      <c r="L43" s="1"/>
-      <c r="M43" s="9">
-        <f>SUM(M3:M41)</f>
-        <v>59.5</v>
-      </c>
-      <c r="N43" s="9">
-        <f>SUM(N3:N41)</f>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C44" s="26"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="29"/>
-      <c r="G44" s="6"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K46">
-        <f>5*4*5</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K47">
-        <f>4*5</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K48">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="49" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="K49">
-        <f>120-5-4</f>
-        <v>111</v>
-      </c>
-    </row>
-    <row r="50" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J50" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K50" s="1">
-        <f>K3+K12</f>
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="51" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J51" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K51" s="1">
-        <f>K13+K21+K30+K39</f>
-        <v>24.5</v>
-      </c>
-    </row>
-    <row r="52" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J52" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K52" s="1">
-        <f>K4+K14+K22+K31+K40</f>
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="53" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J53" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K53" s="1">
-        <f>K5+K15+K23+K24+K32+K33+K41</f>
-        <v>34.5</v>
-      </c>
-    </row>
-    <row r="54" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="K54">
-        <f>SUM(K50:K53)</f>
-        <v>111</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="47">
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="C21:C26"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Horarios/HorarioWAN_2026.xlsx
+++ b/Horarios/HorarioWAN_2026.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="22" documentId="8_{FC23BDE9-CBF9-4CD9-B661-15FDB57BE38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89C49A76-0998-4EA9-B622-0889C0661721}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
   </bookViews>
   <sheets>
     <sheet name="WAN_201" sheetId="5" r:id="rId1"/>
@@ -644,6 +644,117 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -652,117 +763,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1130,19 +1130,19 @@
       <c r="B3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="17" t="s">
+      <c r="D3" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="14" t="s">
+      <c r="F3" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="51" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1150,21 +1150,21 @@
       <c r="B4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="15"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="52"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="14" t="s">
+      <c r="C5" s="14"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="51" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1172,38 +1172,38 @@
       <c r="B6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="17" t="s">
+      <c r="E6" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="16"/>
+      <c r="G6" s="53"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="15"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="52"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
@@ -1233,19 +1233,19 @@
       <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="28" t="s">
+      <c r="C12" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="30" t="s">
+      <c r="F12" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="15" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1253,25 +1253,25 @@
       <c r="B13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="24"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="30"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="15"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="31" t="s">
+      <c r="D14" s="36"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="42" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1279,34 +1279,34 @@
       <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="28" t="s">
+      <c r="C15" s="41"/>
+      <c r="D15" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="32"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="42"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="21"/>
-      <c r="G16" s="32"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="41"/>
+      <c r="G16" s="42"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="22"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="36"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.35">
@@ -1336,19 +1336,19 @@
       <c r="B21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="33" t="s">
+      <c r="C21" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="44" t="s">
+      <c r="E21" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="27" t="s">
+      <c r="F21" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="14" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1356,23 +1356,23 @@
       <c r="B22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="21"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="27"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="14"/>
     </row>
     <row r="23" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="25" t="s">
+      <c r="C23" s="36"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="30" t="s">
+      <c r="G23" s="15" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1380,34 +1380,34 @@
       <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="31" t="s">
+      <c r="C24" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="30" t="s">
+      <c r="D24" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E24" s="46"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="30"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="15"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="42"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="30"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="15"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="43"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="22"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="36"/>
       <c r="G26" s="6"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
@@ -1437,19 +1437,19 @@
       <c r="B30" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="31" t="s">
+      <c r="C30" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="27" t="s">
+      <c r="F30" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1457,27 +1457,27 @@
       <c r="B31" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="41"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="27"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="14"/>
     </row>
     <row r="32" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="31" t="s">
+      <c r="C32" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="41"/>
-      <c r="E32" s="48" t="s">
+      <c r="D32" s="17"/>
+      <c r="E32" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="51" t="s">
+      <c r="F32" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="30" t="s">
+      <c r="G32" s="15" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1485,32 +1485,32 @@
       <c r="B33" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="42"/>
-      <c r="D33" s="31" t="s">
+      <c r="C33" s="23"/>
+      <c r="D33" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="49"/>
-      <c r="F33" s="52"/>
-      <c r="G33" s="30"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="15"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="30"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="15"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="43"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="53"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="29"/>
       <c r="G35" s="6"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.35">
@@ -1540,19 +1540,19 @@
       <c r="B39" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="30" t="s">
+      <c r="C39" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="33" t="s">
+      <c r="D39" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="30" t="s">
         <v>13</v>
       </c>
       <c r="F39" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="34" t="s">
+      <c r="G39" s="31" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1560,60 +1560,91 @@
       <c r="B40" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="30"/>
-      <c r="D40" s="40"/>
-      <c r="E40" s="33"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="30"/>
       <c r="F40" s="38"/>
-      <c r="G40" s="35"/>
+      <c r="G40" s="32"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="25" t="s">
+      <c r="C41" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="41"/>
-      <c r="E41" s="33"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="30"/>
       <c r="F41" s="38"/>
-      <c r="G41" s="35"/>
+      <c r="G41" s="32"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="26"/>
-      <c r="D42" s="31" t="s">
+      <c r="C42" s="35"/>
+      <c r="D42" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="30" t="s">
+      <c r="E42" s="15" t="s">
         <v>13</v>
       </c>
       <c r="F42" s="38"/>
-      <c r="G42" s="35"/>
+      <c r="G42" s="32"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C43" s="26"/>
-      <c r="D43" s="42"/>
-      <c r="E43" s="30"/>
+      <c r="C43" s="35"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="15"/>
       <c r="F43" s="38"/>
-      <c r="G43" s="36"/>
+      <c r="G43" s="33"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="22"/>
-      <c r="D44" s="43"/>
-      <c r="E44" s="30"/>
+      <c r="C44" s="36"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="15"/>
       <c r="F44" s="39"/>
       <c r="G44" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="D42:D44"/>
     <mergeCell ref="G21:G22"/>
     <mergeCell ref="G23:G25"/>
     <mergeCell ref="G30:G31"/>
@@ -1626,44 +1657,13 @@
     <mergeCell ref="E32:E35"/>
     <mergeCell ref="F32:F35"/>
     <mergeCell ref="D33:D35"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="F21:F22"/>
     <mergeCell ref="F23:F26"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
     <mergeCell ref="E21:E26"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="94" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1710,19 +1710,19 @@
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="17" t="s">
+      <c r="D3" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="17" t="s">
+      <c r="F3" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="45" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1730,21 +1730,21 @@
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="17"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="45"/>
     </row>
     <row r="5" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="30" t="s">
+      <c r="C5" s="14"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="15" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1752,38 +1752,38 @@
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="17" t="s">
+      <c r="E6" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="30"/>
+      <c r="G6" s="15"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="30"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="15"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
@@ -1813,19 +1813,19 @@
       <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="28" t="s">
+      <c r="C12" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="30" t="s">
+      <c r="F12" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="15" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1833,25 +1833,25 @@
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="24"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="30"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="15"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="31" t="s">
+      <c r="D14" s="36"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="42" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1859,34 +1859,34 @@
       <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="28" t="s">
+      <c r="C15" s="41"/>
+      <c r="D15" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="32"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="42"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="21"/>
-      <c r="G16" s="32"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="41"/>
+      <c r="G16" s="42"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="22"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="36"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.35">
@@ -1916,19 +1916,19 @@
       <c r="B21" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="33" t="s">
+      <c r="C21" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="44" t="s">
+      <c r="E21" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="27" t="s">
+      <c r="F21" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="14" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1936,23 +1936,23 @@
       <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="21"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="27"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="14"/>
     </row>
     <row r="23" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="25" t="s">
+      <c r="C23" s="36"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="30" t="s">
+      <c r="G23" s="15" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1960,34 +1960,34 @@
       <c r="B24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="31" t="s">
+      <c r="C24" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="30" t="s">
+      <c r="D24" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E24" s="46"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="30"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="15"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="42"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="30"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="15"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="43"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="22"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="36"/>
       <c r="G26" s="6"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
@@ -2017,19 +2017,19 @@
       <c r="B30" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="31" t="s">
+      <c r="C30" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="27" t="s">
+      <c r="F30" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2037,27 +2037,27 @@
       <c r="B31" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="41"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="27"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="14"/>
     </row>
     <row r="32" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="31" t="s">
+      <c r="C32" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="41"/>
-      <c r="E32" s="48" t="s">
+      <c r="D32" s="17"/>
+      <c r="E32" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="51" t="s">
+      <c r="F32" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="30" t="s">
+      <c r="G32" s="15" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2065,32 +2065,32 @@
       <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="42"/>
-      <c r="D33" s="31" t="s">
+      <c r="C33" s="23"/>
+      <c r="D33" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="49"/>
-      <c r="F33" s="52"/>
-      <c r="G33" s="30"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="15"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="30"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="15"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="43"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="53"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="29"/>
       <c r="G35" s="6"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.35">
@@ -2120,19 +2120,19 @@
       <c r="B39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="30" t="s">
+      <c r="C39" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="33" t="s">
+      <c r="D39" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="30" t="s">
         <v>13</v>
       </c>
       <c r="F39" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="34" t="s">
+      <c r="G39" s="31" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2140,60 +2140,97 @@
       <c r="B40" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="30"/>
-      <c r="D40" s="40"/>
-      <c r="E40" s="33"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="30"/>
       <c r="F40" s="38"/>
-      <c r="G40" s="35"/>
+      <c r="G40" s="32"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="25" t="s">
+      <c r="C41" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="41"/>
-      <c r="E41" s="33"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="30"/>
       <c r="F41" s="38"/>
-      <c r="G41" s="35"/>
+      <c r="G41" s="32"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="26"/>
-      <c r="D42" s="31" t="s">
+      <c r="C42" s="35"/>
+      <c r="D42" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="30" t="s">
+      <c r="E42" s="15" t="s">
         <v>13</v>
       </c>
       <c r="F42" s="38"/>
-      <c r="G42" s="35"/>
+      <c r="G42" s="32"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="26"/>
-      <c r="D43" s="42"/>
-      <c r="E43" s="30"/>
+      <c r="C43" s="35"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="15"/>
       <c r="F43" s="38"/>
-      <c r="G43" s="36"/>
+      <c r="G43" s="33"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="22"/>
-      <c r="D44" s="43"/>
-      <c r="E44" s="30"/>
+      <c r="C44" s="36"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="15"/>
       <c r="F44" s="39"/>
       <c r="G44" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="E3:E5"/>
@@ -2204,46 +2241,9 @@
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="E6:E8"/>
     <mergeCell ref="F6:F8"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E26"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E42:E44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="95" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2303,19 +2303,19 @@
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="17" t="s">
+      <c r="D3" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="17" t="s">
+      <c r="F3" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="45" t="s">
         <v>18</v>
       </c>
       <c r="I3" s="1"/>
@@ -2335,11 +2335,11 @@
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="17"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="45"/>
       <c r="I4" s="1"/>
       <c r="J4" t="s">
         <v>12</v>
@@ -2356,11 +2356,11 @@
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="30" t="s">
+      <c r="C5" s="14"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="15" t="s">
         <v>22</v>
       </c>
       <c r="J5" t="s">
@@ -2384,38 +2384,38 @@
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="17" t="s">
+      <c r="E6" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="30"/>
+      <c r="G6" s="15"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="30"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="15"/>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.35">
@@ -2445,19 +2445,19 @@
       <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="28" t="s">
+      <c r="C12" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="30" t="s">
+      <c r="F12" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="15" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="1"/>
@@ -2476,11 +2476,11 @@
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="24"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="30"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="15"/>
       <c r="J13" s="1" t="s">
         <v>14</v>
       </c>
@@ -2495,15 +2495,15 @@
       <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="31" t="s">
+      <c r="D14" s="36"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="42" t="s">
         <v>23</v>
       </c>
       <c r="J14" t="s">
@@ -2521,13 +2521,13 @@
       <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="28" t="s">
+      <c r="C15" s="41"/>
+      <c r="D15" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="32"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="42"/>
       <c r="J15" t="s">
         <v>15</v>
       </c>
@@ -2542,13 +2542,13 @@
       <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="21"/>
-      <c r="G16" s="32"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="41"/>
+      <c r="G16" s="42"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
@@ -2556,10 +2556,10 @@
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="22"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="36"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.35">
@@ -2589,19 +2589,19 @@
       <c r="B21" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="33" t="s">
+      <c r="C21" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="27" t="s">
+      <c r="F21" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="14" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="1"/>
@@ -2620,11 +2620,11 @@
       <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="21"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="41"/>
-      <c r="G22" s="27"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="14"/>
       <c r="I22" s="1"/>
       <c r="J22" t="s">
         <v>12</v>
@@ -2641,15 +2641,15 @@
       <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="25" t="s">
+      <c r="C23" s="36"/>
+      <c r="D23" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="33"/>
-      <c r="F23" s="31" t="s">
+      <c r="E23" s="30"/>
+      <c r="F23" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="30" t="s">
+      <c r="G23" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -2669,15 +2669,15 @@
       <c r="B24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="31" t="s">
+      <c r="C24" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="26"/>
-      <c r="E24" s="30" t="s">
+      <c r="D24" s="35"/>
+      <c r="E24" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="42"/>
-      <c r="G24" s="30"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="15"/>
       <c r="J24" t="s">
         <v>31</v>
       </c>
@@ -2693,21 +2693,21 @@
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="42"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="30"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="15"/>
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="43"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="43"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="20"/>
       <c r="G26" s="6"/>
       <c r="P26" s="1"/>
     </row>
@@ -2743,19 +2743,19 @@
       <c r="B30" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="31" t="s">
+      <c r="C30" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="27" t="s">
+      <c r="F30" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="14" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="1"/>
@@ -2775,11 +2775,11 @@
       <c r="B31" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="40"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="27"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="14"/>
       <c r="J31" t="s">
         <v>12</v>
       </c>
@@ -2796,15 +2796,15 @@
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="41"/>
-      <c r="D32" s="41"/>
-      <c r="E32" s="48" t="s">
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="51" t="s">
+      <c r="F32" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="30" t="s">
+      <c r="G32" s="15" t="s">
         <v>22</v>
       </c>
       <c r="J32" s="1" t="s">
@@ -2824,15 +2824,15 @@
       <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="31" t="s">
+      <c r="C33" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="31" t="s">
+      <c r="D33" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="49"/>
-      <c r="F33" s="52"/>
-      <c r="G33" s="30"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="15"/>
       <c r="J33" t="s">
         <v>31</v>
       </c>
@@ -2848,21 +2848,21 @@
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="30"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="15"/>
       <c r="P34" s="1"/>
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="43"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="53"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="29"/>
       <c r="G35" s="6"/>
       <c r="P35" s="1"/>
     </row>
@@ -2898,16 +2898,16 @@
       <c r="B39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="30" t="s">
+      <c r="C39" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="30" t="s">
+      <c r="D39" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F39" s="30" t="s">
+      <c r="E39" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" s="15" t="s">
         <v>13</v>
       </c>
       <c r="G39" s="37" t="s">
@@ -2929,10 +2929,10 @@
       <c r="B40" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="40"/>
-      <c r="F40" s="30"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="15"/>
       <c r="G40" s="38"/>
       <c r="I40" s="1"/>
       <c r="J40" t="s">
@@ -2950,12 +2950,12 @@
       <c r="B41" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="25" t="s">
+      <c r="C41" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="30"/>
-      <c r="E41" s="41"/>
-      <c r="F41" s="30"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="15"/>
       <c r="G41" s="38"/>
       <c r="I41" s="1"/>
       <c r="J41" t="s">
@@ -2979,7 +2979,7 @@
       <c r="B42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="26"/>
+      <c r="C42" s="35"/>
       <c r="D42" s="37" t="s">
         <v>13</v>
       </c>
@@ -2995,7 +2995,7 @@
       <c r="B43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="26"/>
+      <c r="C43" s="35"/>
       <c r="D43" s="54"/>
       <c r="E43" s="54"/>
       <c r="F43" s="54"/>
@@ -3021,7 +3021,7 @@
       <c r="B44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="22"/>
+      <c r="C44" s="36"/>
       <c r="D44" s="55"/>
       <c r="E44" s="55"/>
       <c r="F44" s="55"/>
@@ -3088,34 +3088,11 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="D23:D26"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="F42:F44"/>
     <mergeCell ref="G21:G22"/>
     <mergeCell ref="G23:G25"/>
     <mergeCell ref="G39:G43"/>
@@ -3132,11 +3109,34 @@
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="D42:D44"/>
     <mergeCell ref="F39:F41"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="D23:D26"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="E24:E26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3195,19 +3195,19 @@
       <c r="B3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="17" t="s">
+      <c r="D3" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="14" t="s">
+      <c r="F3" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="51" t="s">
         <v>62</v>
       </c>
       <c r="I3" s="1"/>
@@ -3227,11 +3227,11 @@
       <c r="B4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="15"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="52"/>
       <c r="I4" s="1"/>
       <c r="J4" t="s">
         <v>12</v>
@@ -3248,11 +3248,11 @@
       <c r="B5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="14" t="s">
+      <c r="C5" s="14"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="51" t="s">
         <v>63</v>
       </c>
       <c r="J5" t="s">
@@ -3276,38 +3276,38 @@
       <c r="B6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="17" t="s">
+      <c r="E6" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="16"/>
+      <c r="G6" s="53"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="15"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="52"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.35">
@@ -3337,19 +3337,19 @@
       <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="28" t="s">
+      <c r="C12" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="30" t="s">
+      <c r="F12" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="15" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="1"/>
@@ -3368,11 +3368,11 @@
       <c r="B13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="24"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="30"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="15"/>
       <c r="J13" s="1" t="s">
         <v>14</v>
       </c>
@@ -3387,15 +3387,15 @@
       <c r="B14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="31" t="s">
+      <c r="D14" s="36"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="42" t="s">
         <v>23</v>
       </c>
       <c r="J14" t="s">
@@ -3413,13 +3413,13 @@
       <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="28" t="s">
+      <c r="C15" s="41"/>
+      <c r="D15" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="32"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="42"/>
       <c r="J15" t="s">
         <v>15</v>
       </c>
@@ -3434,13 +3434,13 @@
       <c r="B16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="21"/>
-      <c r="G16" s="32"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="41"/>
+      <c r="G16" s="42"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
@@ -3448,10 +3448,10 @@
       <c r="B17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="22"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="36"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.35">
@@ -3481,19 +3481,19 @@
       <c r="B21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="44" t="s">
+      <c r="C21" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="33" t="s">
+      <c r="D21" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="27" t="s">
+      <c r="F21" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="14" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="1"/>
@@ -3512,11 +3512,11 @@
       <c r="B22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="27"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="14"/>
       <c r="I22" s="1"/>
       <c r="J22" t="s">
         <v>12</v>
@@ -3533,13 +3533,13 @@
       <c r="B23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="46"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="25" t="s">
+      <c r="C23" s="49"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="30" t="s">
+      <c r="G23" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -3559,15 +3559,15 @@
       <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="46"/>
-      <c r="D24" s="31" t="s">
+      <c r="C24" s="49"/>
+      <c r="D24" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="30" t="s">
+      <c r="E24" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="26"/>
-      <c r="G24" s="30"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="15"/>
       <c r="J24" t="s">
         <v>31</v>
       </c>
@@ -3583,21 +3583,21 @@
       <c r="B25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="46"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="30"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="15"/>
       <c r="O25" s="1"/>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="47"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="22"/>
+      <c r="C26" s="50"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="36"/>
       <c r="G26" s="6"/>
       <c r="O26" s="1"/>
     </row>
@@ -3633,19 +3633,19 @@
       <c r="B30" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="31" t="s">
+      <c r="C30" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="27" t="s">
+      <c r="F30" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="14" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="1"/>
@@ -3665,11 +3665,11 @@
       <c r="B31" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="41"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="27"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="14"/>
       <c r="J31" t="s">
         <v>12</v>
       </c>
@@ -3686,17 +3686,17 @@
       <c r="B32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="31" t="s">
+      <c r="C32" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="41"/>
-      <c r="E32" s="48" t="s">
+      <c r="D32" s="17"/>
+      <c r="E32" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="51" t="s">
+      <c r="F32" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="30" t="s">
+      <c r="G32" s="15" t="s">
         <v>22</v>
       </c>
       <c r="J32" s="1" t="s">
@@ -3716,13 +3716,13 @@
       <c r="B33" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="42"/>
-      <c r="D33" s="31" t="s">
+      <c r="C33" s="23"/>
+      <c r="D33" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="49"/>
-      <c r="F33" s="52"/>
-      <c r="G33" s="30"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="15"/>
       <c r="J33" t="s">
         <v>31</v>
       </c>
@@ -3738,21 +3738,21 @@
       <c r="B34" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="30"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="15"/>
       <c r="O34" s="1"/>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="43"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="53"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="29"/>
       <c r="G35" s="6"/>
       <c r="O35" s="1"/>
     </row>
@@ -3788,19 +3788,19 @@
       <c r="B39" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="30" t="s">
+      <c r="C39" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="33" t="s">
+      <c r="D39" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="30" t="s">
         <v>13</v>
       </c>
       <c r="F39" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="34" t="s">
+      <c r="G39" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I39" s="1"/>
@@ -3820,11 +3820,11 @@
       <c r="B40" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="30"/>
-      <c r="D40" s="40"/>
-      <c r="E40" s="33"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="30"/>
       <c r="F40" s="38"/>
-      <c r="G40" s="35"/>
+      <c r="G40" s="32"/>
       <c r="I40" s="1"/>
       <c r="J40" t="s">
         <v>12</v>
@@ -3841,13 +3841,13 @@
       <c r="B41" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="25" t="s">
+      <c r="C41" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="41"/>
-      <c r="E41" s="33"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="30"/>
       <c r="F41" s="38"/>
-      <c r="G41" s="35"/>
+      <c r="G41" s="32"/>
       <c r="I41" s="1"/>
       <c r="J41" t="s">
         <v>15</v>
@@ -3870,25 +3870,25 @@
       <c r="B42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="26"/>
-      <c r="D42" s="31" t="s">
+      <c r="C42" s="35"/>
+      <c r="D42" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="30" t="s">
+      <c r="E42" s="15" t="s">
         <v>13</v>
       </c>
       <c r="F42" s="38"/>
-      <c r="G42" s="35"/>
+      <c r="G42" s="32"/>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C43" s="26"/>
-      <c r="D43" s="42"/>
-      <c r="E43" s="30"/>
+      <c r="C43" s="35"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="15"/>
       <c r="F43" s="38"/>
-      <c r="G43" s="36"/>
+      <c r="G43" s="33"/>
       <c r="K43" s="1">
         <f>SUM(K3:K41)</f>
         <v>111</v>
@@ -3907,9 +3907,900 @@
       <c r="B44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="22"/>
-      <c r="D44" s="43"/>
-      <c r="E44" s="30"/>
+      <c r="C44" s="36"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="39"/>
+      <c r="G44" s="6"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K46">
+        <f>5*4*5</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K47">
+        <f>4*5</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K48">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="K49">
+        <f>120-5-4</f>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J50" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K50" s="1">
+        <f>K3+K12</f>
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="51" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J51" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K51" s="1">
+        <f>K13+K21+K30+K39</f>
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="52" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J52" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K52" s="1">
+        <f>K4+K14+K22+K31+K40</f>
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="53" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J53" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K53" s="1">
+        <f>K5+K15+K23+K24+K32+K33+K41</f>
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="54" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="K54">
+        <f>SUM(K50:K53)</f>
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="47">
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C21:C26"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B72F34B-8139-4D0E-8882-03145DDD5E1F}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:O54"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="2" customWidth="1"/>
+    <col min="2" max="2" width="10.90625" style="2"/>
+    <col min="3" max="4" width="12.6328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.7265625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="4.36328125" customWidth="1"/>
+    <col min="10" max="10" width="15.7265625" customWidth="1"/>
+    <col min="13" max="14" width="10.90625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B1" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B2" s="4"/>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="1">
+        <f>2.5+2.5+2.5+2.5+2</f>
+        <v>12</v>
+      </c>
+      <c r="M3" s="9">
+        <f>K3</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="45"/>
+      <c r="I4" s="1"/>
+      <c r="J4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4">
+        <f>2.5+2.5+2.5</f>
+        <v>7.5</v>
+      </c>
+      <c r="N4" s="2">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5">
+        <f>2.5+2</f>
+        <v>4.5</v>
+      </c>
+      <c r="M5" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="N5" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="15"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="15"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="5"/>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B10" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B11" s="4"/>
+      <c r="C11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" s="1">
+        <f>3+2.5+3+2</f>
+        <v>10.5</v>
+      </c>
+      <c r="M12" s="2">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="22"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="15"/>
+      <c r="J13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" s="1">
+        <v>3</v>
+      </c>
+      <c r="M13" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="36"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14">
+        <f>2+2.5+2+2</f>
+        <v>8.5</v>
+      </c>
+      <c r="N14" s="2">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="41"/>
+      <c r="D15" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="46"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="42"/>
+      <c r="J15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="N15" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="41"/>
+      <c r="G16" s="42"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="6"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B19" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B20" s="4"/>
+      <c r="C20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K21" s="1">
+        <f>2.5+3</f>
+        <v>5.5</v>
+      </c>
+      <c r="M21" s="2">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="48"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="14"/>
+      <c r="I22" s="1"/>
+      <c r="J22" t="s">
+        <v>12</v>
+      </c>
+      <c r="K22">
+        <f>2.5+2</f>
+        <v>4.5</v>
+      </c>
+      <c r="N22" s="2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="49"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K23" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="M23" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="O23" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="49"/>
+      <c r="D24" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="35"/>
+      <c r="G24" s="15"/>
+      <c r="J24" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24">
+        <v>4.5</v>
+      </c>
+      <c r="N24" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O24" s="1"/>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B25" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="49"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="15"/>
+      <c r="O25" s="1"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="50"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="6"/>
+      <c r="O26" s="1"/>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="O27" s="1"/>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B28" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="O28" s="1"/>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B29" s="4"/>
+      <c r="C29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O29" s="1"/>
+    </row>
+    <row r="30" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K30" s="1">
+        <f>3+2.5+2+3</f>
+        <v>10.5</v>
+      </c>
+      <c r="M30" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="O30" s="1"/>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="17"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="14"/>
+      <c r="J31" t="s">
+        <v>12</v>
+      </c>
+      <c r="K31">
+        <f>2+2.5+2</f>
+        <v>6.5</v>
+      </c>
+      <c r="N31" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="O31" s="1"/>
+    </row>
+    <row r="32" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="17"/>
+      <c r="E32" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K32" s="1">
+        <v>2</v>
+      </c>
+      <c r="M32" s="10">
+        <v>2</v>
+      </c>
+      <c r="O32" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="23"/>
+      <c r="D33" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="25"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="15"/>
+      <c r="J33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K33" s="1">
+        <v>5</v>
+      </c>
+      <c r="N33" s="2">
+        <v>5</v>
+      </c>
+      <c r="O33" s="1"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B34" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="15"/>
+      <c r="O34" s="1"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="6"/>
+      <c r="O35" s="1"/>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="O36" s="1"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B37" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O37" s="1"/>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B38" s="4"/>
+      <c r="C38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O38" s="1"/>
+    </row>
+    <row r="39" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K39" s="1">
+        <f>3+2.5</f>
+        <v>5.5</v>
+      </c>
+      <c r="M39" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="O39" s="1"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="15"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="32"/>
+      <c r="I40" s="1"/>
+      <c r="J40" t="s">
+        <v>12</v>
+      </c>
+      <c r="K40">
+        <v>2.5</v>
+      </c>
+      <c r="N40" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="O40" s="1"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="17"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="38"/>
+      <c r="G41" s="32"/>
+      <c r="I41" s="1"/>
+      <c r="J41" t="s">
+        <v>15</v>
+      </c>
+      <c r="K41">
+        <v>12</v>
+      </c>
+      <c r="M41" s="10">
+        <f>4.5</f>
+        <v>4.5</v>
+      </c>
+      <c r="N41" s="2">
+        <f>2+2.5+5</f>
+        <v>9.5</v>
+      </c>
+      <c r="O41" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="35"/>
+      <c r="D42" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="38"/>
+      <c r="G42" s="32"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" s="35"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="33"/>
+      <c r="K43" s="1">
+        <f>SUM(K3:K41)</f>
+        <v>111</v>
+      </c>
+      <c r="L43" s="1"/>
+      <c r="M43" s="9">
+        <f>SUM(M3:M41)</f>
+        <v>59.5</v>
+      </c>
+      <c r="N43" s="9">
+        <f>SUM(N3:N41)</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="36"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="15"/>
       <c r="F44" s="39"/>
       <c r="G44" s="6"/>
     </row>
@@ -4031,895 +4922,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B72F34B-8139-4D0E-8882-03145DDD5E1F}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B1:O54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="10.90625" style="2"/>
-    <col min="3" max="4" width="12.6328125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.7265625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.1796875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="4.36328125" customWidth="1"/>
-    <col min="10" max="10" width="15.7265625" customWidth="1"/>
-    <col min="13" max="14" width="10.90625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B1" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B2" s="4"/>
-      <c r="C2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="1">
-        <f>2.5+2.5+2.5+2.5+2</f>
-        <v>12</v>
-      </c>
-      <c r="M3" s="9">
-        <f>K3</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="17"/>
-      <c r="I4" s="1"/>
-      <c r="J4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K4">
-        <f>2.5+2.5+2.5</f>
-        <v>7.5</v>
-      </c>
-      <c r="N4" s="2">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5">
-        <f>2.5+2</f>
-        <v>4.5</v>
-      </c>
-      <c r="M5" s="10">
-        <v>1.5</v>
-      </c>
-      <c r="N5" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="30"/>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="30"/>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="5"/>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B10" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B11" s="4"/>
-      <c r="C11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K12" s="1">
-        <f>3+2.5+3+2</f>
-        <v>10.5</v>
-      </c>
-      <c r="M12" s="2">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B13" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="24"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="30"/>
-      <c r="J13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="1">
-        <v>3</v>
-      </c>
-      <c r="M13" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B14" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="J14" t="s">
-        <v>12</v>
-      </c>
-      <c r="K14">
-        <f>2+2.5+2+2</f>
-        <v>8.5</v>
-      </c>
-      <c r="N14" s="2">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="32"/>
-      <c r="J15" t="s">
-        <v>15</v>
-      </c>
-      <c r="K15">
-        <v>2</v>
-      </c>
-      <c r="N15" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B16" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="21"/>
-      <c r="G16" s="32"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="6"/>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B19" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B20" s="4"/>
-      <c r="C20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" s="44" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F21" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K21" s="1">
-        <f>2.5+3</f>
-        <v>5.5</v>
-      </c>
-      <c r="M21" s="2">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B22" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="27"/>
-      <c r="I22" s="1"/>
-      <c r="J22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K22">
-        <f>2.5+2</f>
-        <v>4.5</v>
-      </c>
-      <c r="N22" s="2">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="23" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="46"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K23" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="M23" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="O23" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" s="46"/>
-      <c r="D24" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="F24" s="26"/>
-      <c r="G24" s="30"/>
-      <c r="J24" t="s">
-        <v>31</v>
-      </c>
-      <c r="K24">
-        <v>4.5</v>
-      </c>
-      <c r="N24" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="O24" s="1"/>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B25" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="46"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="30"/>
-      <c r="O25" s="1"/>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="47"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="6"/>
-      <c r="O26" s="1"/>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="O27" s="1"/>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B28" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="O28" s="1"/>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B29" s="4"/>
-      <c r="C29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="O29" s="1"/>
-    </row>
-    <row r="30" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="F30" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K30" s="1">
-        <f>3+2.5+2+3</f>
-        <v>10.5</v>
-      </c>
-      <c r="M30" s="2">
-        <v>10.5</v>
-      </c>
-      <c r="O30" s="1"/>
-    </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B31" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" s="41"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="27"/>
-      <c r="J31" t="s">
-        <v>12</v>
-      </c>
-      <c r="K31">
-        <f>2+2.5+2</f>
-        <v>6.5</v>
-      </c>
-      <c r="N31" s="2">
-        <v>6.5</v>
-      </c>
-      <c r="O31" s="1"/>
-    </row>
-    <row r="32" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="41"/>
-      <c r="E32" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="51" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K32" s="1">
-        <v>2</v>
-      </c>
-      <c r="M32" s="10">
-        <v>2</v>
-      </c>
-      <c r="O32" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" s="42"/>
-      <c r="D33" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="49"/>
-      <c r="F33" s="52"/>
-      <c r="G33" s="30"/>
-      <c r="J33" t="s">
-        <v>31</v>
-      </c>
-      <c r="K33" s="1">
-        <v>5</v>
-      </c>
-      <c r="N33" s="2">
-        <v>5</v>
-      </c>
-      <c r="O33" s="1"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B34" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="30"/>
-      <c r="O34" s="1"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="43"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="53"/>
-      <c r="G35" s="6"/>
-      <c r="O35" s="1"/>
-    </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="O36" s="1"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B37" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O37" s="1"/>
-    </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B38" s="4"/>
-      <c r="C38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="O38" s="1"/>
-    </row>
-    <row r="39" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C39" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="G39" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K39" s="1">
-        <f>3+2.5</f>
-        <v>5.5</v>
-      </c>
-      <c r="M39" s="2">
-        <v>5.5</v>
-      </c>
-      <c r="O39" s="1"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B40" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="30"/>
-      <c r="D40" s="40"/>
-      <c r="E40" s="33"/>
-      <c r="F40" s="38"/>
-      <c r="G40" s="35"/>
-      <c r="I40" s="1"/>
-      <c r="J40" t="s">
-        <v>12</v>
-      </c>
-      <c r="K40">
-        <v>2.5</v>
-      </c>
-      <c r="N40" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="O40" s="1"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41" s="41"/>
-      <c r="E41" s="33"/>
-      <c r="F41" s="38"/>
-      <c r="G41" s="35"/>
-      <c r="I41" s="1"/>
-      <c r="J41" t="s">
-        <v>15</v>
-      </c>
-      <c r="K41">
-        <v>12</v>
-      </c>
-      <c r="M41" s="10">
-        <f>4.5</f>
-        <v>4.5</v>
-      </c>
-      <c r="N41" s="2">
-        <f>2+2.5+5</f>
-        <v>9.5</v>
-      </c>
-      <c r="O41" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C42" s="26"/>
-      <c r="D42" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="38"/>
-      <c r="G42" s="35"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C43" s="26"/>
-      <c r="D43" s="42"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="36"/>
-      <c r="K43" s="1">
-        <f>SUM(K3:K41)</f>
-        <v>111</v>
-      </c>
-      <c r="L43" s="1"/>
-      <c r="M43" s="9">
-        <f>SUM(M3:M41)</f>
-        <v>59.5</v>
-      </c>
-      <c r="N43" s="9">
-        <f>SUM(N3:N41)</f>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C44" s="22"/>
-      <c r="D44" s="43"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="39"/>
-      <c r="G44" s="6"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K46">
-        <f>5*4*5</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K47">
-        <f>4*5</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K48">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="49" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="K49">
-        <f>120-5-4</f>
-        <v>111</v>
-      </c>
-    </row>
-    <row r="50" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J50" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K50" s="1">
-        <f>K3+K12</f>
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="51" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J51" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K51" s="1">
-        <f>K13+K21+K30+K39</f>
-        <v>24.5</v>
-      </c>
-    </row>
-    <row r="52" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J52" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K52" s="1">
-        <f>K4+K14+K22+K31+K40</f>
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="53" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J53" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K53" s="1">
-        <f>K5+K15+K23+K24+K32+K33+K41</f>
-        <v>34.5</v>
-      </c>
-    </row>
-    <row r="54" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="K54">
-        <f>SUM(K50:K53)</f>
-        <v>111</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="47">
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C21:C26"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Horarios/HorarioWAN_2026.xlsx
+++ b/Horarios/HorarioWAN_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecmx-my.sharepoint.com/personal/lperezf_tec_mx/Documents/Documents/GitLiz/WAN/Horarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{FC23BDE9-CBF9-4CD9-B661-15FDB57BE38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89C49A76-0998-4EA9-B622-0889C0661721}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="8_{FC23BDE9-CBF9-4CD9-B661-15FDB57BE38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0A94BC4-B2ED-4228-83E2-869E24004626}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
   </bookViews>
@@ -644,36 +644,66 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -692,45 +722,30 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -738,21 +753,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1130,16 +1130,16 @@
       <c r="B3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="45" t="s">
+      <c r="D3" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="43" t="s">
+      <c r="F3" s="48" t="s">
         <v>19</v>
       </c>
       <c r="G3" s="51" t="s">
@@ -1150,20 +1150,20 @@
       <c r="B4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
       <c r="G4" s="52"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
       <c r="G5" s="51" t="s">
         <v>63</v>
       </c>
@@ -1172,16 +1172,16 @@
       <c r="B6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="45" t="s">
+      <c r="C6" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="45" t="s">
+      <c r="D6" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="45" t="s">
+      <c r="E6" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="50" t="s">
         <v>18</v>
       </c>
       <c r="G6" s="53"/>
@@ -1190,20 +1190,20 @@
       <c r="B7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
       <c r="G7" s="52"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
@@ -1233,19 +1233,19 @@
       <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="40" t="s">
+      <c r="C12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="15" t="s">
+      <c r="F12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1253,25 +1253,25 @@
       <c r="B13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="15"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="14"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="36"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="19" t="s">
+      <c r="D14" s="26"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="42" t="s">
+      <c r="G14" s="46" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1279,34 +1279,34 @@
       <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="40" t="s">
+      <c r="C15" s="40"/>
+      <c r="D15" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="46"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="42"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="46"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="41"/>
-      <c r="G16" s="42"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="40"/>
+      <c r="G16" s="46"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="36"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="26"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.35">
@@ -1336,19 +1336,19 @@
       <c r="B21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="15" t="s">
         <v>19</v>
       </c>
       <c r="D21" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="47" t="s">
+      <c r="E21" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="14" t="s">
+      <c r="F21" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="31" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1356,23 +1356,23 @@
       <c r="B22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="41"/>
+      <c r="C22" s="40"/>
       <c r="D22" s="30"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="14"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="31"/>
     </row>
     <row r="23" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="36"/>
+      <c r="C23" s="26"/>
       <c r="D23" s="30"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="34" t="s">
+      <c r="E23" s="43"/>
+      <c r="F23" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="14" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1380,34 +1380,34 @@
       <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E24" s="49"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="15"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="14"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="23"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="15"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="14"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="20"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="50"/>
-      <c r="F26" s="36"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="26"/>
       <c r="G26" s="6"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
@@ -1437,19 +1437,19 @@
       <c r="B30" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="19" t="s">
+      <c r="C30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="14" t="s">
+      <c r="F30" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="31" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1458,26 +1458,26 @@
         <v>35</v>
       </c>
       <c r="C31" s="17"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="14"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="31"/>
     </row>
     <row r="32" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="19" t="s">
+      <c r="C32" s="27" t="s">
         <v>20</v>
       </c>
       <c r="D32" s="17"/>
-      <c r="E32" s="24" t="s">
+      <c r="E32" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="27" t="s">
+      <c r="F32" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1485,32 +1485,32 @@
       <c r="B33" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="23"/>
-      <c r="D33" s="19" t="s">
+      <c r="C33" s="28"/>
+      <c r="D33" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="25"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="15"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="14"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="15"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="14"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="39"/>
       <c r="G35" s="6"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.35">
@@ -1540,19 +1540,19 @@
       <c r="B39" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="30" t="s">
+      <c r="D39" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="37" t="s">
+      <c r="E39" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="31" t="s">
+      <c r="G39" s="21" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1560,60 +1560,91 @@
       <c r="B40" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="15"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="38"/>
-      <c r="G40" s="32"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="22"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="34" t="s">
+      <c r="C41" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="17"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="38"/>
-      <c r="G41" s="32"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="22"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="35"/>
-      <c r="D42" s="19" t="s">
+      <c r="C42" s="25"/>
+      <c r="D42" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="38"/>
-      <c r="G42" s="32"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="22"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C43" s="35"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="33"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="23"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="36"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="39"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="20"/>
       <c r="G44" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="E21:E26"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
     <mergeCell ref="C21:C23"/>
     <mergeCell ref="C24:C26"/>
     <mergeCell ref="D24:D26"/>
@@ -1630,37 +1661,6 @@
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="D12:D14"/>
     <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="E21:E26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="94" orientation="portrait" r:id="rId1"/>
@@ -1710,19 +1710,19 @@
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="45" t="s">
+      <c r="D3" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="45" t="s">
+      <c r="F3" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="50" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1730,21 +1730,21 @@
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="45"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="50"/>
     </row>
     <row r="5" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="15" t="s">
+      <c r="C5" s="31"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1752,38 +1752,38 @@
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="45" t="s">
+      <c r="C6" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="45" t="s">
+      <c r="D6" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="45" t="s">
+      <c r="E6" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="15"/>
+      <c r="G6" s="14"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="15"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="14"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
@@ -1813,19 +1813,19 @@
       <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="40" t="s">
+      <c r="C12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="15" t="s">
+      <c r="F12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1833,25 +1833,25 @@
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="15"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="14"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="36"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="19" t="s">
+      <c r="D14" s="26"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="42" t="s">
+      <c r="G14" s="46" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1859,34 +1859,34 @@
       <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="40" t="s">
+      <c r="C15" s="40"/>
+      <c r="D15" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="46"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="42"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="46"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="41"/>
-      <c r="G16" s="42"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="40"/>
+      <c r="G16" s="46"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="36"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="26"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.35">
@@ -1916,19 +1916,19 @@
       <c r="B21" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="15" t="s">
         <v>19</v>
       </c>
       <c r="D21" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="47" t="s">
+      <c r="E21" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="14" t="s">
+      <c r="F21" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="31" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1936,23 +1936,23 @@
       <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="41"/>
+      <c r="C22" s="40"/>
       <c r="D22" s="30"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="14"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="31"/>
     </row>
     <row r="23" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="36"/>
+      <c r="C23" s="26"/>
       <c r="D23" s="30"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="34" t="s">
+      <c r="E23" s="43"/>
+      <c r="F23" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="14" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1960,34 +1960,34 @@
       <c r="B24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E24" s="49"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="15"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="14"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="23"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="15"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="14"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="20"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="50"/>
-      <c r="F26" s="36"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="26"/>
       <c r="G26" s="6"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
@@ -2017,19 +2017,19 @@
       <c r="B30" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="19" t="s">
+      <c r="C30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="14" t="s">
+      <c r="F30" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="31" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2038,26 +2038,26 @@
         <v>1</v>
       </c>
       <c r="C31" s="17"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="14"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="31"/>
     </row>
     <row r="32" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="19" t="s">
+      <c r="C32" s="27" t="s">
         <v>20</v>
       </c>
       <c r="D32" s="17"/>
-      <c r="E32" s="24" t="s">
+      <c r="E32" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="27" t="s">
+      <c r="F32" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2065,32 +2065,32 @@
       <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="23"/>
-      <c r="D33" s="19" t="s">
+      <c r="C33" s="28"/>
+      <c r="D33" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="25"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="15"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="14"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="15"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="14"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="39"/>
       <c r="G35" s="6"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.35">
@@ -2120,19 +2120,19 @@
       <c r="B39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="30" t="s">
+      <c r="D39" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="37" t="s">
+      <c r="E39" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="31" t="s">
+      <c r="G39" s="21" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2140,87 +2140,70 @@
       <c r="B40" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="15"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="38"/>
-      <c r="G40" s="32"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="22"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="34" t="s">
+      <c r="C41" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="17"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="38"/>
-      <c r="G41" s="32"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="22"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="35"/>
-      <c r="D42" s="19" t="s">
+      <c r="C42" s="25"/>
+      <c r="D42" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="38"/>
-      <c r="G42" s="32"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="22"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="35"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="33"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="23"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="36"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="39"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="20"/>
       <c r="G44" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E26"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
     <mergeCell ref="F12:F13"/>
     <mergeCell ref="G12:G13"/>
     <mergeCell ref="C14:C17"/>
@@ -2231,16 +2214,33 @@
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="D12:D14"/>
     <mergeCell ref="E12:E15"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E42:E44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="95" orientation="portrait" r:id="rId1"/>
@@ -2303,19 +2303,19 @@
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="45" t="s">
+      <c r="D3" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="45" t="s">
+      <c r="F3" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="50" t="s">
         <v>18</v>
       </c>
       <c r="I3" s="1"/>
@@ -2335,11 +2335,11 @@
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="45"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="50"/>
       <c r="I4" s="1"/>
       <c r="J4" t="s">
         <v>12</v>
@@ -2356,11 +2356,11 @@
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="15" t="s">
+      <c r="C5" s="31"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="14" t="s">
         <v>22</v>
       </c>
       <c r="J5" t="s">
@@ -2384,38 +2384,38 @@
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="45" t="s">
+      <c r="C6" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="45" t="s">
+      <c r="D6" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="45" t="s">
+      <c r="E6" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="15"/>
+      <c r="G6" s="14"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="15"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="14"/>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.35">
@@ -2445,19 +2445,19 @@
       <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="40" t="s">
+      <c r="C12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="15" t="s">
+      <c r="F12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="1"/>
@@ -2476,11 +2476,11 @@
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="15"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="14"/>
       <c r="J13" s="1" t="s">
         <v>14</v>
       </c>
@@ -2495,15 +2495,15 @@
       <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="36"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="19" t="s">
+      <c r="D14" s="26"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="42" t="s">
+      <c r="G14" s="46" t="s">
         <v>23</v>
       </c>
       <c r="J14" t="s">
@@ -2521,13 +2521,13 @@
       <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="40" t="s">
+      <c r="C15" s="40"/>
+      <c r="D15" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="46"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="42"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="46"/>
       <c r="J15" t="s">
         <v>15</v>
       </c>
@@ -2542,13 +2542,13 @@
       <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="41"/>
-      <c r="G16" s="42"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="40"/>
+      <c r="G16" s="46"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
@@ -2556,10 +2556,10 @@
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="36"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="26"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.35">
@@ -2589,19 +2589,19 @@
       <c r="B21" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="21" t="s">
+      <c r="C21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="32" t="s">
         <v>19</v>
       </c>
       <c r="E21" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="14" t="s">
+      <c r="F21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="31" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="1"/>
@@ -2620,11 +2620,11 @@
       <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="41"/>
-      <c r="D22" s="22"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="33"/>
       <c r="E22" s="30"/>
       <c r="F22" s="17"/>
-      <c r="G22" s="14"/>
+      <c r="G22" s="31"/>
       <c r="I22" s="1"/>
       <c r="J22" t="s">
         <v>12</v>
@@ -2641,15 +2641,15 @@
       <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="36"/>
-      <c r="D23" s="34" t="s">
+      <c r="C23" s="26"/>
+      <c r="D23" s="24" t="s">
         <v>20</v>
       </c>
       <c r="E23" s="30"/>
-      <c r="F23" s="19" t="s">
+      <c r="F23" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="14" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -2669,15 +2669,15 @@
       <c r="B24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="35"/>
-      <c r="E24" s="15" t="s">
+      <c r="D24" s="25"/>
+      <c r="E24" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="23"/>
-      <c r="G24" s="15"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="14"/>
       <c r="J24" t="s">
         <v>31</v>
       </c>
@@ -2693,21 +2693,21 @@
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="23"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="15"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="14"/>
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="20"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="20"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="29"/>
       <c r="G26" s="6"/>
       <c r="P26" s="1"/>
     </row>
@@ -2743,19 +2743,19 @@
       <c r="B30" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="19" t="s">
+      <c r="C30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="14" t="s">
+      <c r="F30" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="1"/>
@@ -2775,11 +2775,11 @@
       <c r="B31" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="14"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="31"/>
       <c r="J31" t="s">
         <v>12</v>
       </c>
@@ -2798,13 +2798,13 @@
       </c>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
-      <c r="E32" s="24" t="s">
+      <c r="E32" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="27" t="s">
+      <c r="F32" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="14" t="s">
         <v>22</v>
       </c>
       <c r="J32" s="1" t="s">
@@ -2824,15 +2824,15 @@
       <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="C33" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="19" t="s">
+      <c r="D33" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="25"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="15"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="14"/>
       <c r="J33" t="s">
         <v>31</v>
       </c>
@@ -2848,21 +2848,21 @@
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="15"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="14"/>
       <c r="P34" s="1"/>
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="39"/>
       <c r="G35" s="6"/>
       <c r="P35" s="1"/>
     </row>
@@ -2898,19 +2898,19 @@
       <c r="B39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="15" t="s">
+      <c r="D39" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="F39" s="15" t="s">
+      <c r="E39" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G39" s="37" t="s">
+      <c r="G39" s="18" t="s">
         <v>57</v>
       </c>
       <c r="I39" s="1"/>
@@ -2929,11 +2929,11 @@
       <c r="B40" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="38"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="19"/>
       <c r="I40" s="1"/>
       <c r="J40" t="s">
         <v>12</v>
@@ -2950,13 +2950,13 @@
       <c r="B41" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="34" t="s">
+      <c r="C41" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="15"/>
+      <c r="D41" s="14"/>
       <c r="E41" s="17"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="38"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="19"/>
       <c r="I41" s="1"/>
       <c r="J41" t="s">
         <v>15</v>
@@ -2979,27 +2979,27 @@
       <c r="B42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="35"/>
-      <c r="D42" s="37" t="s">
+      <c r="C42" s="25"/>
+      <c r="D42" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E42" s="37" t="s">
+      <c r="E42" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="37" t="s">
+      <c r="F42" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="G42" s="38"/>
+      <c r="G42" s="19"/>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="35"/>
+      <c r="C43" s="25"/>
       <c r="D43" s="54"/>
       <c r="E43" s="54"/>
       <c r="F43" s="54"/>
-      <c r="G43" s="39"/>
+      <c r="G43" s="20"/>
       <c r="K43" s="1">
         <f>SUM(K3:K41)</f>
         <v>120</v>
@@ -3021,7 +3021,7 @@
       <c r="B44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="36"/>
+      <c r="C44" s="26"/>
       <c r="D44" s="55"/>
       <c r="E44" s="55"/>
       <c r="F44" s="55"/>
@@ -3088,11 +3088,34 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="D23:D26"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
     <mergeCell ref="G21:G22"/>
     <mergeCell ref="G23:G25"/>
     <mergeCell ref="G39:G43"/>
@@ -3109,34 +3132,11 @@
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="D42:D44"/>
     <mergeCell ref="F39:F41"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="D23:D26"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="F42:F44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3195,16 +3195,16 @@
       <c r="B3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="45" t="s">
+      <c r="D3" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="43" t="s">
+      <c r="F3" s="48" t="s">
         <v>19</v>
       </c>
       <c r="G3" s="51" t="s">
@@ -3227,10 +3227,10 @@
       <c r="B4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
       <c r="G4" s="52"/>
       <c r="I4" s="1"/>
       <c r="J4" t="s">
@@ -3248,10 +3248,10 @@
       <c r="B5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
       <c r="G5" s="51" t="s">
         <v>63</v>
       </c>
@@ -3276,16 +3276,16 @@
       <c r="B6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="45" t="s">
+      <c r="C6" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="45" t="s">
+      <c r="D6" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="45" t="s">
+      <c r="E6" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="50" t="s">
         <v>18</v>
       </c>
       <c r="G6" s="53"/>
@@ -3294,20 +3294,20 @@
       <c r="B7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
       <c r="G7" s="52"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.35">
@@ -3337,19 +3337,19 @@
       <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="40" t="s">
+      <c r="C12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="15" t="s">
+      <c r="F12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="1"/>
@@ -3368,11 +3368,11 @@
       <c r="B13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="15"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="14"/>
       <c r="J13" s="1" t="s">
         <v>14</v>
       </c>
@@ -3387,15 +3387,15 @@
       <c r="B14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="36"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="19" t="s">
+      <c r="D14" s="26"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="42" t="s">
+      <c r="G14" s="46" t="s">
         <v>23</v>
       </c>
       <c r="J14" t="s">
@@ -3413,13 +3413,13 @@
       <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="40" t="s">
+      <c r="C15" s="40"/>
+      <c r="D15" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="46"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="42"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="46"/>
       <c r="J15" t="s">
         <v>15</v>
       </c>
@@ -3434,13 +3434,13 @@
       <c r="B16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="41"/>
-      <c r="G16" s="42"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="40"/>
+      <c r="G16" s="46"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
@@ -3448,10 +3448,10 @@
       <c r="B17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="36"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="26"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.35">
@@ -3481,19 +3481,19 @@
       <c r="B21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="47" t="s">
+      <c r="C21" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="15" t="s">
         <v>19</v>
       </c>
       <c r="E21" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="14" t="s">
+      <c r="F21" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="31" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="1"/>
@@ -3512,11 +3512,11 @@
       <c r="B22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="48"/>
-      <c r="D22" s="41"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="40"/>
       <c r="E22" s="30"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="14"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="31"/>
       <c r="I22" s="1"/>
       <c r="J22" t="s">
         <v>12</v>
@@ -3533,13 +3533,13 @@
       <c r="B23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="49"/>
-      <c r="D23" s="36"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="26"/>
       <c r="E23" s="30"/>
-      <c r="F23" s="34" t="s">
+      <c r="F23" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="14" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -3559,15 +3559,15 @@
       <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="49"/>
-      <c r="D24" s="19" t="s">
+      <c r="C24" s="43"/>
+      <c r="D24" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="35"/>
-      <c r="G24" s="15"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="14"/>
       <c r="J24" t="s">
         <v>31</v>
       </c>
@@ -3583,21 +3583,21 @@
       <c r="B25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="49"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="15"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="14"/>
       <c r="O25" s="1"/>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="50"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="36"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="26"/>
       <c r="G26" s="6"/>
       <c r="O26" s="1"/>
     </row>
@@ -3633,19 +3633,19 @@
       <c r="B30" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="19" t="s">
+      <c r="C30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="14" t="s">
+      <c r="F30" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="1"/>
@@ -3666,10 +3666,10 @@
         <v>35</v>
       </c>
       <c r="C31" s="17"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="14"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="31"/>
       <c r="J31" t="s">
         <v>12</v>
       </c>
@@ -3686,17 +3686,17 @@
       <c r="B32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="19" t="s">
+      <c r="C32" s="27" t="s">
         <v>20</v>
       </c>
       <c r="D32" s="17"/>
-      <c r="E32" s="24" t="s">
+      <c r="E32" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="27" t="s">
+      <c r="F32" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="14" t="s">
         <v>22</v>
       </c>
       <c r="J32" s="1" t="s">
@@ -3716,13 +3716,13 @@
       <c r="B33" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="23"/>
-      <c r="D33" s="19" t="s">
+      <c r="C33" s="28"/>
+      <c r="D33" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="25"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="15"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="14"/>
       <c r="J33" t="s">
         <v>31</v>
       </c>
@@ -3738,21 +3738,21 @@
       <c r="B34" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="15"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="14"/>
       <c r="O34" s="1"/>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="39"/>
       <c r="G35" s="6"/>
       <c r="O35" s="1"/>
     </row>
@@ -3788,19 +3788,19 @@
       <c r="B39" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="16" t="s">
+      <c r="D39" s="15" t="s">
         <v>19</v>
       </c>
       <c r="E39" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="37" t="s">
+      <c r="F39" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="31" t="s">
+      <c r="G39" s="21" t="s">
         <v>16</v>
       </c>
       <c r="I39" s="1"/>
@@ -3820,11 +3820,11 @@
       <c r="B40" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="15"/>
-      <c r="D40" s="18"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="16"/>
       <c r="E40" s="30"/>
-      <c r="F40" s="38"/>
-      <c r="G40" s="32"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="22"/>
       <c r="I40" s="1"/>
       <c r="J40" t="s">
         <v>12</v>
@@ -3841,13 +3841,13 @@
       <c r="B41" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="34" t="s">
+      <c r="C41" s="24" t="s">
         <v>20</v>
       </c>
       <c r="D41" s="17"/>
       <c r="E41" s="30"/>
-      <c r="F41" s="38"/>
-      <c r="G41" s="32"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="22"/>
       <c r="I41" s="1"/>
       <c r="J41" t="s">
         <v>15</v>
@@ -3870,25 +3870,25 @@
       <c r="B42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="35"/>
-      <c r="D42" s="19" t="s">
+      <c r="C42" s="25"/>
+      <c r="D42" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="15" t="s">
+      <c r="E42" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="38"/>
-      <c r="G42" s="32"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="22"/>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C43" s="35"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="33"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="23"/>
       <c r="K43" s="1">
         <f>SUM(K3:K41)</f>
         <v>111</v>
@@ -3907,10 +3907,901 @@
       <c r="B44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="36"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="39"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="6"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K46">
+        <f>5*4*5</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K47">
+        <f>4*5</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K48">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="K49">
+        <f>120-5-4</f>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J50" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K50" s="1">
+        <f>K3+K12</f>
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="51" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J51" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K51" s="1">
+        <f>K13+K21+K30+K39</f>
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="52" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J52" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K52" s="1">
+        <f>K4+K14+K22+K31+K40</f>
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="53" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J53" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K53" s="1">
+        <f>K5+K15+K23+K24+K32+K33+K41</f>
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="54" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="K54">
+        <f>SUM(K50:K53)</f>
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="47">
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="C21:C26"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B72F34B-8139-4D0E-8882-03145DDD5E1F}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:O54"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="2" customWidth="1"/>
+    <col min="2" max="2" width="10.90625" style="2"/>
+    <col min="3" max="4" width="12.6328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.7265625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="4.36328125" customWidth="1"/>
+    <col min="10" max="10" width="15.7265625" customWidth="1"/>
+    <col min="13" max="14" width="10.90625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B1" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B2" s="4"/>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="1">
+        <f>2.5+2.5+2.5+2.5+2</f>
+        <v>12</v>
+      </c>
+      <c r="M3" s="9">
+        <f>K3</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="31"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="50"/>
+      <c r="I4" s="1"/>
+      <c r="J4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4">
+        <f>2.5+2.5+2.5</f>
+        <v>7.5</v>
+      </c>
+      <c r="N4" s="2">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="31"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5">
+        <f>2.5+2</f>
+        <v>4.5</v>
+      </c>
+      <c r="M5" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="N5" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="14"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="5"/>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B10" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B11" s="4"/>
+      <c r="C11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" s="1">
+        <f>3+2.5+3+2</f>
+        <v>10.5</v>
+      </c>
+      <c r="M12" s="2">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="33"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="14"/>
+      <c r="J13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" s="1">
+        <v>3</v>
+      </c>
+      <c r="M13" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="26"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14">
+        <f>2+2.5+2+2</f>
+        <v>8.5</v>
+      </c>
+      <c r="N14" s="2">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="40"/>
+      <c r="D15" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="47"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="46"/>
+      <c r="J15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="N15" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="40"/>
+      <c r="G16" s="46"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="6"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B19" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B20" s="4"/>
+      <c r="C20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K21" s="1">
+        <f>2.5+3</f>
+        <v>5.5</v>
+      </c>
+      <c r="M21" s="2">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="42"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="31"/>
+      <c r="I22" s="1"/>
+      <c r="J22" t="s">
+        <v>12</v>
+      </c>
+      <c r="K22">
+        <f>2.5+2</f>
+        <v>4.5</v>
+      </c>
+      <c r="N22" s="2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="43"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K23" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="M23" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="O23" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="43"/>
+      <c r="D24" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="25"/>
+      <c r="G24" s="14"/>
+      <c r="J24" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24">
+        <v>4.5</v>
+      </c>
+      <c r="N24" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O24" s="1"/>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B25" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="43"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="14"/>
+      <c r="O25" s="1"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="44"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="6"/>
+      <c r="O26" s="1"/>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="O27" s="1"/>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B28" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="O28" s="1"/>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B29" s="4"/>
+      <c r="C29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O29" s="1"/>
+    </row>
+    <row r="30" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K30" s="1">
+        <f>3+2.5+2+3</f>
+        <v>10.5</v>
+      </c>
+      <c r="M30" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="O30" s="1"/>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="17"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="31"/>
+      <c r="J31" t="s">
+        <v>12</v>
+      </c>
+      <c r="K31">
+        <f>2+2.5+2</f>
+        <v>6.5</v>
+      </c>
+      <c r="N31" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="O31" s="1"/>
+    </row>
+    <row r="32" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="17"/>
+      <c r="E32" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K32" s="1">
+        <v>2</v>
+      </c>
+      <c r="M32" s="10">
+        <v>2</v>
+      </c>
+      <c r="O32" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="28"/>
+      <c r="D33" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="35"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="14"/>
+      <c r="J33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K33" s="1">
+        <v>5</v>
+      </c>
+      <c r="N33" s="2">
+        <v>5</v>
+      </c>
+      <c r="O33" s="1"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B34" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="14"/>
+      <c r="O34" s="1"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="6"/>
+      <c r="O35" s="1"/>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="O36" s="1"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B37" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O37" s="1"/>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B38" s="4"/>
+      <c r="C38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O38" s="1"/>
+    </row>
+    <row r="39" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K39" s="1">
+        <f>3+2.5</f>
+        <v>5.5</v>
+      </c>
+      <c r="M39" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="O39" s="1"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="14"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="22"/>
+      <c r="I40" s="1"/>
+      <c r="J40" t="s">
+        <v>12</v>
+      </c>
+      <c r="K40">
+        <v>2.5</v>
+      </c>
+      <c r="N40" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="O40" s="1"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="17"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="22"/>
+      <c r="I41" s="1"/>
+      <c r="J41" t="s">
+        <v>15</v>
+      </c>
+      <c r="K41">
+        <v>12</v>
+      </c>
+      <c r="M41" s="10">
+        <f>4.5</f>
+        <v>4.5</v>
+      </c>
+      <c r="N41" s="2">
+        <f>2+2.5+5</f>
+        <v>9.5</v>
+      </c>
+      <c r="O41" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="25"/>
+      <c r="D42" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="19"/>
+      <c r="G42" s="22"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" s="25"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="23"/>
+      <c r="K43" s="1">
+        <f>SUM(K3:K41)</f>
+        <v>111</v>
+      </c>
+      <c r="L43" s="1"/>
+      <c r="M43" s="9">
+        <f>SUM(M3:M41)</f>
+        <v>59.5</v>
+      </c>
+      <c r="N43" s="9">
+        <f>SUM(N3:N41)</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="26"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="20"/>
       <c r="G44" s="6"/>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.35">
@@ -4031,895 +4922,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B72F34B-8139-4D0E-8882-03145DDD5E1F}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B1:O54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="10.90625" style="2"/>
-    <col min="3" max="4" width="12.6328125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.7265625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.1796875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="4.36328125" customWidth="1"/>
-    <col min="10" max="10" width="15.7265625" customWidth="1"/>
-    <col min="13" max="14" width="10.90625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B1" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B2" s="4"/>
-      <c r="C2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="1">
-        <f>2.5+2.5+2.5+2.5+2</f>
-        <v>12</v>
-      </c>
-      <c r="M3" s="9">
-        <f>K3</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="45"/>
-      <c r="I4" s="1"/>
-      <c r="J4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K4">
-        <f>2.5+2.5+2.5</f>
-        <v>7.5</v>
-      </c>
-      <c r="N4" s="2">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5">
-        <f>2.5+2</f>
-        <v>4.5</v>
-      </c>
-      <c r="M5" s="10">
-        <v>1.5</v>
-      </c>
-      <c r="N5" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="15"/>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="15"/>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="5"/>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B10" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B11" s="4"/>
-      <c r="C11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K12" s="1">
-        <f>3+2.5+3+2</f>
-        <v>10.5</v>
-      </c>
-      <c r="M12" s="2">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B13" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="15"/>
-      <c r="J13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="1">
-        <v>3</v>
-      </c>
-      <c r="M13" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B14" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="36"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="J14" t="s">
-        <v>12</v>
-      </c>
-      <c r="K14">
-        <f>2+2.5+2+2</f>
-        <v>8.5</v>
-      </c>
-      <c r="N14" s="2">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="46"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="42"/>
-      <c r="J15" t="s">
-        <v>15</v>
-      </c>
-      <c r="K15">
-        <v>2</v>
-      </c>
-      <c r="N15" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B16" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="41"/>
-      <c r="G16" s="42"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="6"/>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B19" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B20" s="4"/>
-      <c r="C20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" s="47" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="F21" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K21" s="1">
-        <f>2.5+3</f>
-        <v>5.5</v>
-      </c>
-      <c r="M21" s="2">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B22" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="48"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="14"/>
-      <c r="I22" s="1"/>
-      <c r="J22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K22">
-        <f>2.5+2</f>
-        <v>4.5</v>
-      </c>
-      <c r="N22" s="2">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="23" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="49"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K23" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="M23" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="O23" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" s="49"/>
-      <c r="D24" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F24" s="35"/>
-      <c r="G24" s="15"/>
-      <c r="J24" t="s">
-        <v>31</v>
-      </c>
-      <c r="K24">
-        <v>4.5</v>
-      </c>
-      <c r="N24" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="O24" s="1"/>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B25" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="49"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="15"/>
-      <c r="O25" s="1"/>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="50"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="6"/>
-      <c r="O26" s="1"/>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="O27" s="1"/>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B28" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="O28" s="1"/>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B29" s="4"/>
-      <c r="C29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="O29" s="1"/>
-    </row>
-    <row r="30" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="F30" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K30" s="1">
-        <f>3+2.5+2+3</f>
-        <v>10.5</v>
-      </c>
-      <c r="M30" s="2">
-        <v>10.5</v>
-      </c>
-      <c r="O30" s="1"/>
-    </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B31" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="14"/>
-      <c r="J31" t="s">
-        <v>12</v>
-      </c>
-      <c r="K31">
-        <f>2+2.5+2</f>
-        <v>6.5</v>
-      </c>
-      <c r="N31" s="2">
-        <v>6.5</v>
-      </c>
-      <c r="O31" s="1"/>
-    </row>
-    <row r="32" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="17"/>
-      <c r="E32" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K32" s="1">
-        <v>2</v>
-      </c>
-      <c r="M32" s="10">
-        <v>2</v>
-      </c>
-      <c r="O32" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" s="23"/>
-      <c r="D33" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="25"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="15"/>
-      <c r="J33" t="s">
-        <v>31</v>
-      </c>
-      <c r="K33" s="1">
-        <v>5</v>
-      </c>
-      <c r="N33" s="2">
-        <v>5</v>
-      </c>
-      <c r="O33" s="1"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B34" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="15"/>
-      <c r="O34" s="1"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="29"/>
-      <c r="G35" s="6"/>
-      <c r="O35" s="1"/>
-    </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="O36" s="1"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B37" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O37" s="1"/>
-    </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B38" s="4"/>
-      <c r="C38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="O38" s="1"/>
-    </row>
-    <row r="39" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="G39" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K39" s="1">
-        <f>3+2.5</f>
-        <v>5.5</v>
-      </c>
-      <c r="M39" s="2">
-        <v>5.5</v>
-      </c>
-      <c r="O39" s="1"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B40" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="15"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="38"/>
-      <c r="G40" s="32"/>
-      <c r="I40" s="1"/>
-      <c r="J40" t="s">
-        <v>12</v>
-      </c>
-      <c r="K40">
-        <v>2.5</v>
-      </c>
-      <c r="N40" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="O40" s="1"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41" s="17"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="38"/>
-      <c r="G41" s="32"/>
-      <c r="I41" s="1"/>
-      <c r="J41" t="s">
-        <v>15</v>
-      </c>
-      <c r="K41">
-        <v>12</v>
-      </c>
-      <c r="M41" s="10">
-        <f>4.5</f>
-        <v>4.5</v>
-      </c>
-      <c r="N41" s="2">
-        <f>2+2.5+5</f>
-        <v>9.5</v>
-      </c>
-      <c r="O41" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C42" s="35"/>
-      <c r="D42" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="38"/>
-      <c r="G42" s="32"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C43" s="35"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="33"/>
-      <c r="K43" s="1">
-        <f>SUM(K3:K41)</f>
-        <v>111</v>
-      </c>
-      <c r="L43" s="1"/>
-      <c r="M43" s="9">
-        <f>SUM(M3:M41)</f>
-        <v>59.5</v>
-      </c>
-      <c r="N43" s="9">
-        <f>SUM(N3:N41)</f>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C44" s="36"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="39"/>
-      <c r="G44" s="6"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K46">
-        <f>5*4*5</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K47">
-        <f>4*5</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K48">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="49" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="K49">
-        <f>120-5-4</f>
-        <v>111</v>
-      </c>
-    </row>
-    <row r="50" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J50" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K50" s="1">
-        <f>K3+K12</f>
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="51" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J51" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K51" s="1">
-        <f>K13+K21+K30+K39</f>
-        <v>24.5</v>
-      </c>
-    </row>
-    <row r="52" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J52" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K52" s="1">
-        <f>K4+K14+K22+K31+K40</f>
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="53" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J53" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K53" s="1">
-        <f>K5+K15+K23+K24+K32+K33+K41</f>
-        <v>34.5</v>
-      </c>
-    </row>
-    <row r="54" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="K54">
-        <f>SUM(K50:K53)</f>
-        <v>111</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="47">
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="C21:C26"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Horarios/HorarioWAN_2026.xlsx
+++ b/Horarios/HorarioWAN_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecmx-my.sharepoint.com/personal/lperezf_tec_mx/Documents/Documents/GitLiz/WAN/Horarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="8_{FC23BDE9-CBF9-4CD9-B661-15FDB57BE38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0A94BC4-B2ED-4228-83E2-869E24004626}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="8_{FC23BDE9-CBF9-4CD9-B661-15FDB57BE38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8EFF27F-1D38-4B85-B337-DA811DC210E5}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
   </bookViews>
@@ -644,16 +644,97 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -673,87 +754,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1130,16 +1130,16 @@
       <c r="B3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="50" t="s">
+      <c r="D3" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="48" t="s">
+      <c r="F3" s="15" t="s">
         <v>19</v>
       </c>
       <c r="G3" s="51" t="s">
@@ -1150,20 +1150,20 @@
       <c r="B4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
       <c r="G4" s="52"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
       <c r="G5" s="51" t="s">
         <v>63</v>
       </c>
@@ -1172,16 +1172,16 @@
       <c r="B6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="C6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="50" t="s">
+      <c r="E6" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G6" s="53"/>
@@ -1190,20 +1190,20 @@
       <c r="B7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
       <c r="G7" s="52"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
@@ -1233,19 +1233,19 @@
       <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="45" t="s">
+      <c r="C12" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="14" t="s">
+      <c r="F12" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="18" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1253,25 +1253,25 @@
       <c r="B13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="14"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="18"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="45" t="s">
+      <c r="C14" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="27" t="s">
+      <c r="D14" s="23"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="46" t="s">
+      <c r="G14" s="25" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1279,34 +1279,34 @@
       <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="45" t="s">
+      <c r="C15" s="22"/>
+      <c r="D15" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="47"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="46"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="25"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="46"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="22"/>
+      <c r="G16" s="25"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="26"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="23"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.35">
@@ -1336,19 +1336,19 @@
       <c r="B21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="30" t="s">
+      <c r="C21" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="41" t="s">
+      <c r="E21" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="31" t="s">
+      <c r="F21" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="14" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1356,23 +1356,23 @@
       <c r="B22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="40"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="31"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="14"/>
     </row>
     <row r="23" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="26"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="24" t="s">
+      <c r="C23" s="23"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="14" t="s">
+      <c r="G23" s="18" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1380,34 +1380,34 @@
       <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="27" t="s">
+      <c r="C24" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="E24" s="43"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="14"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="18"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="28"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="14"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="18"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="29"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="26"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="23"/>
       <c r="G26" s="6"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
@@ -1437,19 +1437,19 @@
       <c r="B30" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="27" t="s">
+      <c r="C30" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="31" t="s">
+      <c r="F30" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1457,27 +1457,27 @@
       <c r="B31" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="31"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="14"/>
     </row>
     <row r="32" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="27" t="s">
+      <c r="C32" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="17"/>
-      <c r="E32" s="34" t="s">
+      <c r="D32" s="34"/>
+      <c r="E32" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="37" t="s">
+      <c r="F32" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="14" t="s">
+      <c r="G32" s="18" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1485,32 +1485,32 @@
       <c r="B33" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="28"/>
-      <c r="D33" s="27" t="s">
+      <c r="C33" s="32"/>
+      <c r="D33" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="35"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="14"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="18"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="14"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="18"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="39"/>
+      <c r="C35" s="33"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="41"/>
       <c r="G35" s="6"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.35">
@@ -1540,19 +1540,19 @@
       <c r="B39" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="30" t="s">
+      <c r="D39" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F39" s="18" t="s">
+      <c r="E39" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F39" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="21" t="s">
+      <c r="G39" s="48" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1560,60 +1560,91 @@
       <c r="B40" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="14"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="22"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="46"/>
+      <c r="G40" s="49"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="24" t="s">
+      <c r="C41" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="30"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="22"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="46"/>
+      <c r="G41" s="49"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="25"/>
-      <c r="D42" s="14" t="s">
+      <c r="C42" s="44"/>
+      <c r="D42" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E42" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="F42" s="19"/>
-      <c r="G42" s="22"/>
+      <c r="E42" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F42" s="46"/>
+      <c r="G42" s="49"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C43" s="25"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="23"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="35"/>
+      <c r="F43" s="46"/>
+      <c r="G43" s="50"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="26"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="29"/>
-      <c r="F44" s="20"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="47"/>
       <c r="G44" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="D42:D44"/>
     <mergeCell ref="G21:G22"/>
     <mergeCell ref="G23:G25"/>
     <mergeCell ref="G30:G31"/>
@@ -1630,37 +1661,6 @@
     <mergeCell ref="F21:F22"/>
     <mergeCell ref="F23:F26"/>
     <mergeCell ref="E21:E26"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="94" orientation="portrait" r:id="rId1"/>
@@ -1710,19 +1710,19 @@
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="50" t="s">
+      <c r="D3" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="50" t="s">
+      <c r="F3" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="17" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1730,21 +1730,21 @@
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="50"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="17"/>
     </row>
     <row r="5" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="14" t="s">
+      <c r="C5" s="14"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="18" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1752,38 +1752,38 @@
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="C6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="50" t="s">
+      <c r="E6" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="14"/>
+      <c r="G6" s="18"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="14"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="18"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
@@ -1813,19 +1813,19 @@
       <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="45" t="s">
+      <c r="C12" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="14" t="s">
+      <c r="F12" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="18" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1833,25 +1833,25 @@
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="14"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="18"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="45" t="s">
+      <c r="C14" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="27" t="s">
+      <c r="D14" s="23"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="46" t="s">
+      <c r="G14" s="25" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1859,34 +1859,34 @@
       <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="45" t="s">
+      <c r="C15" s="22"/>
+      <c r="D15" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="47"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="46"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="25"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="46"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="22"/>
+      <c r="G16" s="25"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="26"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="23"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.35">
@@ -1916,19 +1916,19 @@
       <c r="B21" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="30" t="s">
+      <c r="C21" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="41" t="s">
+      <c r="E21" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="31" t="s">
+      <c r="F21" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="14" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1936,23 +1936,23 @@
       <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="40"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="31"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="14"/>
     </row>
     <row r="23" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="26"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="24" t="s">
+      <c r="C23" s="23"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="14" t="s">
+      <c r="G23" s="18" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1960,34 +1960,34 @@
       <c r="B24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="27" t="s">
+      <c r="C24" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="E24" s="43"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="14"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="18"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="28"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="14"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="18"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="29"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="26"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="23"/>
       <c r="G26" s="6"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
@@ -2017,19 +2017,19 @@
       <c r="B30" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="27" t="s">
+      <c r="C30" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="31" t="s">
+      <c r="F30" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2037,27 +2037,27 @@
       <c r="B31" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="31"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="14"/>
     </row>
     <row r="32" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="27" t="s">
+      <c r="C32" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="17"/>
-      <c r="E32" s="34" t="s">
+      <c r="D32" s="34"/>
+      <c r="E32" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="37" t="s">
+      <c r="F32" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="14" t="s">
+      <c r="G32" s="18" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2065,32 +2065,32 @@
       <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="28"/>
-      <c r="D33" s="27" t="s">
+      <c r="C33" s="32"/>
+      <c r="D33" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="35"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="14"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="18"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="14"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="18"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="39"/>
+      <c r="C35" s="33"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="41"/>
       <c r="G35" s="6"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.35">
@@ -2120,19 +2120,19 @@
       <c r="B39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="30" t="s">
+      <c r="D39" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F39" s="18" t="s">
+      <c r="E39" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F39" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="21" t="s">
+      <c r="G39" s="48" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2140,60 +2140,97 @@
       <c r="B40" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="14"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="22"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="46"/>
+      <c r="G40" s="49"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="24" t="s">
+      <c r="C41" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="30"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="22"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="46"/>
+      <c r="G41" s="49"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="25"/>
-      <c r="D42" s="14" t="s">
+      <c r="C42" s="44"/>
+      <c r="D42" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E42" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="F42" s="19"/>
-      <c r="G42" s="22"/>
+      <c r="E42" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F42" s="46"/>
+      <c r="G42" s="49"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="25"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="23"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="35"/>
+      <c r="F43" s="46"/>
+      <c r="G43" s="50"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="26"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="29"/>
-      <c r="F44" s="20"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="47"/>
       <c r="G44" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="E3:E5"/>
@@ -2204,43 +2241,6 @@
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="E6:E8"/>
     <mergeCell ref="F6:F8"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E26"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E42:E44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="95" orientation="portrait" r:id="rId1"/>
@@ -2303,19 +2303,19 @@
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="50" t="s">
+      <c r="D3" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="50" t="s">
+      <c r="F3" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="17" t="s">
         <v>18</v>
       </c>
       <c r="I3" s="1"/>
@@ -2335,11 +2335,11 @@
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="50"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="17"/>
       <c r="I4" s="1"/>
       <c r="J4" t="s">
         <v>12</v>
@@ -2356,11 +2356,11 @@
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="14" t="s">
+      <c r="C5" s="14"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="18" t="s">
         <v>22</v>
       </c>
       <c r="J5" t="s">
@@ -2384,38 +2384,38 @@
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="C6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="50" t="s">
+      <c r="E6" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="14"/>
+      <c r="G6" s="18"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="14"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="18"/>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.35">
@@ -2445,19 +2445,19 @@
       <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="45" t="s">
+      <c r="C12" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="14" t="s">
+      <c r="F12" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="18" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="1"/>
@@ -2476,11 +2476,11 @@
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="14"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="18"/>
       <c r="J13" s="1" t="s">
         <v>14</v>
       </c>
@@ -2495,15 +2495,15 @@
       <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="45" t="s">
+      <c r="C14" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="27" t="s">
+      <c r="D14" s="23"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="46" t="s">
+      <c r="G14" s="25" t="s">
         <v>23</v>
       </c>
       <c r="J14" t="s">
@@ -2521,13 +2521,13 @@
       <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="45" t="s">
+      <c r="C15" s="22"/>
+      <c r="D15" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="47"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="46"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="25"/>
       <c r="J15" t="s">
         <v>15</v>
       </c>
@@ -2542,13 +2542,13 @@
       <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="46"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="22"/>
+      <c r="G16" s="25"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
@@ -2556,10 +2556,10 @@
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="26"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="23"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.35">
@@ -2589,19 +2589,19 @@
       <c r="B21" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="30" t="s">
+      <c r="C21" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="31" t="s">
+      <c r="F21" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="14" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="1"/>
@@ -2620,11 +2620,11 @@
       <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="40"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="31"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="14"/>
       <c r="I22" s="1"/>
       <c r="J22" t="s">
         <v>12</v>
@@ -2641,15 +2641,15 @@
       <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="26"/>
-      <c r="D23" s="24" t="s">
+      <c r="C23" s="23"/>
+      <c r="D23" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="30"/>
-      <c r="F23" s="27" t="s">
+      <c r="E23" s="42"/>
+      <c r="F23" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="14" t="s">
+      <c r="G23" s="18" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -2669,15 +2669,15 @@
       <c r="B24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="27" t="s">
+      <c r="C24" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="25"/>
-      <c r="E24" s="14" t="s">
+      <c r="D24" s="44"/>
+      <c r="E24" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="28"/>
-      <c r="G24" s="14"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="18"/>
       <c r="J24" t="s">
         <v>31</v>
       </c>
@@ -2693,21 +2693,21 @@
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="28"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="14"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="18"/>
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="29"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="29"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="33"/>
       <c r="G26" s="6"/>
       <c r="P26" s="1"/>
     </row>
@@ -2743,19 +2743,19 @@
       <c r="B30" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="27" t="s">
+      <c r="C30" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="31" t="s">
+      <c r="F30" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="14" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="1"/>
@@ -2775,11 +2775,11 @@
       <c r="B31" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="31"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="14"/>
       <c r="J31" t="s">
         <v>12</v>
       </c>
@@ -2796,15 +2796,15 @@
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="34" t="s">
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="37" t="s">
+      <c r="F32" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="14" t="s">
+      <c r="G32" s="18" t="s">
         <v>22</v>
       </c>
       <c r="J32" s="1" t="s">
@@ -2824,15 +2824,15 @@
       <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="27" t="s">
+      <c r="C33" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="27" t="s">
+      <c r="D33" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="35"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="14"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="18"/>
       <c r="J33" t="s">
         <v>31</v>
       </c>
@@ -2848,21 +2848,21 @@
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="14"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="18"/>
       <c r="P34" s="1"/>
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="39"/>
+      <c r="C35" s="33"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="41"/>
       <c r="G35" s="6"/>
       <c r="P35" s="1"/>
     </row>
@@ -2898,19 +2898,19 @@
       <c r="B39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="D39" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F39" s="14" t="s">
+      <c r="E39" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="G39" s="18" t="s">
+      <c r="G39" s="45" t="s">
         <v>57</v>
       </c>
       <c r="I39" s="1"/>
@@ -2929,11 +2929,11 @@
       <c r="B40" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="19"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="46"/>
       <c r="I40" s="1"/>
       <c r="J40" t="s">
         <v>12</v>
@@ -2950,13 +2950,13 @@
       <c r="B41" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="24" t="s">
+      <c r="C41" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="14"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="19"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="46"/>
       <c r="I41" s="1"/>
       <c r="J41" t="s">
         <v>15</v>
@@ -2979,27 +2979,27 @@
       <c r="B42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="25"/>
-      <c r="D42" s="18" t="s">
+      <c r="C42" s="44"/>
+      <c r="D42" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="E42" s="18" t="s">
+      <c r="E42" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="18" t="s">
+      <c r="F42" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="G42" s="19"/>
+      <c r="G42" s="46"/>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="25"/>
+      <c r="C43" s="44"/>
       <c r="D43" s="54"/>
       <c r="E43" s="54"/>
       <c r="F43" s="54"/>
-      <c r="G43" s="20"/>
+      <c r="G43" s="47"/>
       <c r="K43" s="1">
         <f>SUM(K3:K41)</f>
         <v>120</v>
@@ -3021,7 +3021,7 @@
       <c r="B44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="26"/>
+      <c r="C44" s="23"/>
       <c r="D44" s="55"/>
       <c r="E44" s="55"/>
       <c r="F44" s="55"/>
@@ -3088,34 +3088,11 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="D23:D26"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="F42:F44"/>
     <mergeCell ref="G21:G22"/>
     <mergeCell ref="G23:G25"/>
     <mergeCell ref="G39:G43"/>
@@ -3132,11 +3109,34 @@
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="D42:D44"/>
     <mergeCell ref="F39:F41"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="D23:D26"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="E24:E26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3195,16 +3195,16 @@
       <c r="B3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="50" t="s">
+      <c r="D3" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="48" t="s">
+      <c r="F3" s="15" t="s">
         <v>19</v>
       </c>
       <c r="G3" s="51" t="s">
@@ -3227,10 +3227,10 @@
       <c r="B4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
       <c r="G4" s="52"/>
       <c r="I4" s="1"/>
       <c r="J4" t="s">
@@ -3248,10 +3248,10 @@
       <c r="B5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
       <c r="G5" s="51" t="s">
         <v>63</v>
       </c>
@@ -3276,16 +3276,16 @@
       <c r="B6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="C6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="50" t="s">
+      <c r="E6" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G6" s="53"/>
@@ -3294,20 +3294,20 @@
       <c r="B7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
       <c r="G7" s="52"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.35">
@@ -3337,19 +3337,19 @@
       <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="45" t="s">
+      <c r="C12" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="14" t="s">
+      <c r="F12" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="18" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="1"/>
@@ -3368,11 +3368,11 @@
       <c r="B13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="14"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="18"/>
       <c r="J13" s="1" t="s">
         <v>14</v>
       </c>
@@ -3387,15 +3387,15 @@
       <c r="B14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="45" t="s">
+      <c r="C14" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="27" t="s">
+      <c r="D14" s="23"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="46" t="s">
+      <c r="G14" s="25" t="s">
         <v>23</v>
       </c>
       <c r="J14" t="s">
@@ -3413,13 +3413,13 @@
       <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="45" t="s">
+      <c r="C15" s="22"/>
+      <c r="D15" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="47"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="46"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="25"/>
       <c r="J15" t="s">
         <v>15</v>
       </c>
@@ -3434,13 +3434,13 @@
       <c r="B16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="46"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="22"/>
+      <c r="G16" s="25"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
@@ -3448,10 +3448,10 @@
       <c r="B17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="26"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="23"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.35">
@@ -3481,19 +3481,19 @@
       <c r="B21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="41" t="s">
+      <c r="C21" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="30" t="s">
+      <c r="D21" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="31" t="s">
+      <c r="F21" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="14" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="1"/>
@@ -3512,11 +3512,11 @@
       <c r="B22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="42"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="31"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="14"/>
       <c r="I22" s="1"/>
       <c r="J22" t="s">
         <v>12</v>
@@ -3533,13 +3533,13 @@
       <c r="B23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="43"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="24" t="s">
+      <c r="C23" s="30"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="14" t="s">
+      <c r="G23" s="18" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -3559,15 +3559,15 @@
       <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="43"/>
-      <c r="D24" s="27" t="s">
+      <c r="C24" s="30"/>
+      <c r="D24" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="25"/>
-      <c r="G24" s="14"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="18"/>
       <c r="J24" t="s">
         <v>31</v>
       </c>
@@ -3583,21 +3583,21 @@
       <c r="B25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="43"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="14"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="18"/>
       <c r="O25" s="1"/>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="44"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="26"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="23"/>
       <c r="G26" s="6"/>
       <c r="O26" s="1"/>
     </row>
@@ -3633,19 +3633,19 @@
       <c r="B30" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="27" t="s">
+      <c r="C30" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="31" t="s">
+      <c r="F30" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="14" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="1"/>
@@ -3665,11 +3665,11 @@
       <c r="B31" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="31"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="14"/>
       <c r="J31" t="s">
         <v>12</v>
       </c>
@@ -3686,17 +3686,17 @@
       <c r="B32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="27" t="s">
+      <c r="C32" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="17"/>
-      <c r="E32" s="34" t="s">
+      <c r="D32" s="34"/>
+      <c r="E32" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="37" t="s">
+      <c r="F32" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="14" t="s">
+      <c r="G32" s="18" t="s">
         <v>22</v>
       </c>
       <c r="J32" s="1" t="s">
@@ -3716,13 +3716,13 @@
       <c r="B33" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="28"/>
-      <c r="D33" s="27" t="s">
+      <c r="C33" s="32"/>
+      <c r="D33" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="35"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="14"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="18"/>
       <c r="J33" t="s">
         <v>31</v>
       </c>
@@ -3738,21 +3738,21 @@
       <c r="B34" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="14"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="18"/>
       <c r="O34" s="1"/>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="39"/>
+      <c r="C35" s="33"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="41"/>
       <c r="G35" s="6"/>
       <c r="O35" s="1"/>
     </row>
@@ -3788,19 +3788,19 @@
       <c r="B39" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="30" t="s">
+      <c r="D39" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="18" t="s">
+      <c r="F39" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="21" t="s">
+      <c r="G39" s="48" t="s">
         <v>16</v>
       </c>
       <c r="I39" s="1"/>
@@ -3820,11 +3820,11 @@
       <c r="B40" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="14"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="22"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="42"/>
+      <c r="F40" s="46"/>
+      <c r="G40" s="49"/>
       <c r="I40" s="1"/>
       <c r="J40" t="s">
         <v>12</v>
@@ -3841,13 +3841,13 @@
       <c r="B41" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="24" t="s">
+      <c r="C41" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="17"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="22"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="42"/>
+      <c r="F41" s="46"/>
+      <c r="G41" s="49"/>
       <c r="I41" s="1"/>
       <c r="J41" t="s">
         <v>15</v>
@@ -3870,25 +3870,25 @@
       <c r="B42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="25"/>
-      <c r="D42" s="27" t="s">
+      <c r="C42" s="44"/>
+      <c r="D42" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E42" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="19"/>
-      <c r="G42" s="22"/>
+      <c r="F42" s="46"/>
+      <c r="G42" s="49"/>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C43" s="25"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="23"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="46"/>
+      <c r="G43" s="50"/>
       <c r="K43" s="1">
         <f>SUM(K3:K41)</f>
         <v>111</v>
@@ -3907,10 +3907,901 @@
       <c r="B44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="26"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="20"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="33"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="47"/>
+      <c r="G44" s="6"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K46">
+        <f>5*4*5</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K47">
+        <f>4*5</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K48">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="K49">
+        <f>120-5-4</f>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J50" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K50" s="1">
+        <f>K3+K12</f>
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="51" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J51" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K51" s="1">
+        <f>K13+K21+K30+K39</f>
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="52" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J52" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K52" s="1">
+        <f>K4+K14+K22+K31+K40</f>
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="53" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J53" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K53" s="1">
+        <f>K5+K15+K23+K24+K32+K33+K41</f>
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="54" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="K54">
+        <f>SUM(K50:K53)</f>
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="47">
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C21:C26"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B72F34B-8139-4D0E-8882-03145DDD5E1F}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:O54"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="2" customWidth="1"/>
+    <col min="2" max="2" width="10.90625" style="2"/>
+    <col min="3" max="4" width="12.6328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.7265625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="4.36328125" customWidth="1"/>
+    <col min="10" max="10" width="15.7265625" customWidth="1"/>
+    <col min="13" max="14" width="10.90625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B1" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B2" s="4"/>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="1">
+        <f>2.5+2.5+2.5+2.5+2</f>
+        <v>12</v>
+      </c>
+      <c r="M3" s="9">
+        <f>K3</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="17"/>
+      <c r="I4" s="1"/>
+      <c r="J4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4">
+        <f>2.5+2.5+2.5</f>
+        <v>7.5</v>
+      </c>
+      <c r="N4" s="2">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5">
+        <f>2.5+2</f>
+        <v>4.5</v>
+      </c>
+      <c r="M5" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="N5" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="18"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="18"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="5"/>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B10" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B11" s="4"/>
+      <c r="C11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" s="1">
+        <f>3+2.5+3+2</f>
+        <v>10.5</v>
+      </c>
+      <c r="M12" s="2">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="20"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="18"/>
+      <c r="J13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" s="1">
+        <v>3</v>
+      </c>
+      <c r="M13" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="23"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14">
+        <f>2+2.5+2+2</f>
+        <v>8.5</v>
+      </c>
+      <c r="N14" s="2">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="27"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="25"/>
+      <c r="J15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="N15" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="22"/>
+      <c r="G16" s="25"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="6"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B19" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B20" s="4"/>
+      <c r="C20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K21" s="1">
+        <f>2.5+3</f>
+        <v>5.5</v>
+      </c>
+      <c r="M21" s="2">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="29"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="14"/>
+      <c r="I22" s="1"/>
+      <c r="J22" t="s">
+        <v>12</v>
+      </c>
+      <c r="K22">
+        <f>2.5+2</f>
+        <v>4.5</v>
+      </c>
+      <c r="N22" s="2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="30"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K23" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="M23" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="O23" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="30"/>
+      <c r="D24" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="44"/>
+      <c r="G24" s="18"/>
+      <c r="J24" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24">
+        <v>4.5</v>
+      </c>
+      <c r="N24" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O24" s="1"/>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B25" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="30"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="18"/>
+      <c r="O25" s="1"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="31"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="6"/>
+      <c r="O26" s="1"/>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="O27" s="1"/>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B28" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="O28" s="1"/>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B29" s="4"/>
+      <c r="C29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O29" s="1"/>
+    </row>
+    <row r="30" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K30" s="1">
+        <f>3+2.5+2+3</f>
+        <v>10.5</v>
+      </c>
+      <c r="M30" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="O30" s="1"/>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="34"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="14"/>
+      <c r="J31" t="s">
+        <v>12</v>
+      </c>
+      <c r="K31">
+        <f>2+2.5+2</f>
+        <v>6.5</v>
+      </c>
+      <c r="N31" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="O31" s="1"/>
+    </row>
+    <row r="32" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="34"/>
+      <c r="E32" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K32" s="1">
+        <v>2</v>
+      </c>
+      <c r="M32" s="10">
+        <v>2</v>
+      </c>
+      <c r="O32" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="32"/>
+      <c r="D33" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="37"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="18"/>
+      <c r="J33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K33" s="1">
+        <v>5</v>
+      </c>
+      <c r="N33" s="2">
+        <v>5</v>
+      </c>
+      <c r="O33" s="1"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B34" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="18"/>
+      <c r="O34" s="1"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="33"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="41"/>
+      <c r="G35" s="6"/>
+      <c r="O35" s="1"/>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="O36" s="1"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B37" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O37" s="1"/>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B38" s="4"/>
+      <c r="C38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O38" s="1"/>
+    </row>
+    <row r="39" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K39" s="1">
+        <f>3+2.5</f>
+        <v>5.5</v>
+      </c>
+      <c r="M39" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="O39" s="1"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="18"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="42"/>
+      <c r="F40" s="46"/>
+      <c r="G40" s="49"/>
+      <c r="I40" s="1"/>
+      <c r="J40" t="s">
+        <v>12</v>
+      </c>
+      <c r="K40">
+        <v>2.5</v>
+      </c>
+      <c r="N40" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="O40" s="1"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="34"/>
+      <c r="E41" s="42"/>
+      <c r="F41" s="46"/>
+      <c r="G41" s="49"/>
+      <c r="I41" s="1"/>
+      <c r="J41" t="s">
+        <v>15</v>
+      </c>
+      <c r="K41">
+        <v>12</v>
+      </c>
+      <c r="M41" s="10">
+        <f>4.5</f>
+        <v>4.5</v>
+      </c>
+      <c r="N41" s="2">
+        <f>2+2.5+5</f>
+        <v>9.5</v>
+      </c>
+      <c r="O41" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="44"/>
+      <c r="D42" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="46"/>
+      <c r="G42" s="49"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" s="44"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="46"/>
+      <c r="G43" s="50"/>
+      <c r="K43" s="1">
+        <f>SUM(K3:K41)</f>
+        <v>111</v>
+      </c>
+      <c r="L43" s="1"/>
+      <c r="M43" s="9">
+        <f>SUM(M3:M41)</f>
+        <v>59.5</v>
+      </c>
+      <c r="N43" s="9">
+        <f>SUM(N3:N41)</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="23"/>
+      <c r="D44" s="33"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="47"/>
       <c r="G44" s="6"/>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.35">
@@ -4031,895 +4922,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B72F34B-8139-4D0E-8882-03145DDD5E1F}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B1:O54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="10.90625" style="2"/>
-    <col min="3" max="4" width="12.6328125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.7265625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.1796875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="4.36328125" customWidth="1"/>
-    <col min="10" max="10" width="15.7265625" customWidth="1"/>
-    <col min="13" max="14" width="10.90625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B1" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B2" s="4"/>
-      <c r="C2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="1">
-        <f>2.5+2.5+2.5+2.5+2</f>
-        <v>12</v>
-      </c>
-      <c r="M3" s="9">
-        <f>K3</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="50"/>
-      <c r="I4" s="1"/>
-      <c r="J4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K4">
-        <f>2.5+2.5+2.5</f>
-        <v>7.5</v>
-      </c>
-      <c r="N4" s="2">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5">
-        <f>2.5+2</f>
-        <v>4.5</v>
-      </c>
-      <c r="M5" s="10">
-        <v>1.5</v>
-      </c>
-      <c r="N5" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="14"/>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="14"/>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="5"/>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B10" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B11" s="4"/>
-      <c r="C11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K12" s="1">
-        <f>3+2.5+3+2</f>
-        <v>10.5</v>
-      </c>
-      <c r="M12" s="2">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B13" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="14"/>
-      <c r="J13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="1">
-        <v>3</v>
-      </c>
-      <c r="M13" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B14" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="J14" t="s">
-        <v>12</v>
-      </c>
-      <c r="K14">
-        <f>2+2.5+2+2</f>
-        <v>8.5</v>
-      </c>
-      <c r="N14" s="2">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="47"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="46"/>
-      <c r="J15" t="s">
-        <v>15</v>
-      </c>
-      <c r="K15">
-        <v>2</v>
-      </c>
-      <c r="N15" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B16" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="46"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="6"/>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B19" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B20" s="4"/>
-      <c r="C20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" s="41" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="F21" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K21" s="1">
-        <f>2.5+3</f>
-        <v>5.5</v>
-      </c>
-      <c r="M21" s="2">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B22" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="42"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="31"/>
-      <c r="I22" s="1"/>
-      <c r="J22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K22">
-        <f>2.5+2</f>
-        <v>4.5</v>
-      </c>
-      <c r="N22" s="2">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="23" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="43"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K23" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="M23" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="O23" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" s="43"/>
-      <c r="D24" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="F24" s="25"/>
-      <c r="G24" s="14"/>
-      <c r="J24" t="s">
-        <v>31</v>
-      </c>
-      <c r="K24">
-        <v>4.5</v>
-      </c>
-      <c r="N24" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="O24" s="1"/>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B25" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="43"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="14"/>
-      <c r="O25" s="1"/>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="44"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="6"/>
-      <c r="O26" s="1"/>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="O27" s="1"/>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B28" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="O28" s="1"/>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B29" s="4"/>
-      <c r="C29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="O29" s="1"/>
-    </row>
-    <row r="30" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="F30" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K30" s="1">
-        <f>3+2.5+2+3</f>
-        <v>10.5</v>
-      </c>
-      <c r="M30" s="2">
-        <v>10.5</v>
-      </c>
-      <c r="O30" s="1"/>
-    </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B31" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="31"/>
-      <c r="J31" t="s">
-        <v>12</v>
-      </c>
-      <c r="K31">
-        <f>2+2.5+2</f>
-        <v>6.5</v>
-      </c>
-      <c r="N31" s="2">
-        <v>6.5</v>
-      </c>
-      <c r="O31" s="1"/>
-    </row>
-    <row r="32" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="17"/>
-      <c r="E32" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K32" s="1">
-        <v>2</v>
-      </c>
-      <c r="M32" s="10">
-        <v>2</v>
-      </c>
-      <c r="O32" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" s="28"/>
-      <c r="D33" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="35"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="14"/>
-      <c r="J33" t="s">
-        <v>31</v>
-      </c>
-      <c r="K33" s="1">
-        <v>5</v>
-      </c>
-      <c r="N33" s="2">
-        <v>5</v>
-      </c>
-      <c r="O33" s="1"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B34" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="14"/>
-      <c r="O34" s="1"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="6"/>
-      <c r="O35" s="1"/>
-    </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="O36" s="1"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B37" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O37" s="1"/>
-    </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B38" s="4"/>
-      <c r="C38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="O38" s="1"/>
-    </row>
-    <row r="39" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="G39" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K39" s="1">
-        <f>3+2.5</f>
-        <v>5.5</v>
-      </c>
-      <c r="M39" s="2">
-        <v>5.5</v>
-      </c>
-      <c r="O39" s="1"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B40" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="14"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="22"/>
-      <c r="I40" s="1"/>
-      <c r="J40" t="s">
-        <v>12</v>
-      </c>
-      <c r="K40">
-        <v>2.5</v>
-      </c>
-      <c r="N40" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="O40" s="1"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41" s="17"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="22"/>
-      <c r="I41" s="1"/>
-      <c r="J41" t="s">
-        <v>15</v>
-      </c>
-      <c r="K41">
-        <v>12</v>
-      </c>
-      <c r="M41" s="10">
-        <f>4.5</f>
-        <v>4.5</v>
-      </c>
-      <c r="N41" s="2">
-        <f>2+2.5+5</f>
-        <v>9.5</v>
-      </c>
-      <c r="O41" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C42" s="25"/>
-      <c r="D42" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="19"/>
-      <c r="G42" s="22"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C43" s="25"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="23"/>
-      <c r="K43" s="1">
-        <f>SUM(K3:K41)</f>
-        <v>111</v>
-      </c>
-      <c r="L43" s="1"/>
-      <c r="M43" s="9">
-        <f>SUM(M3:M41)</f>
-        <v>59.5</v>
-      </c>
-      <c r="N43" s="9">
-        <f>SUM(N3:N41)</f>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C44" s="26"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="6"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K46">
-        <f>5*4*5</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K47">
-        <f>4*5</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K48">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="49" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="K49">
-        <f>120-5-4</f>
-        <v>111</v>
-      </c>
-    </row>
-    <row r="50" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J50" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K50" s="1">
-        <f>K3+K12</f>
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="51" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J51" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K51" s="1">
-        <f>K13+K21+K30+K39</f>
-        <v>24.5</v>
-      </c>
-    </row>
-    <row r="52" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J52" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K52" s="1">
-        <f>K4+K14+K22+K31+K40</f>
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="53" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J53" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K53" s="1">
-        <f>K5+K15+K23+K24+K32+K33+K41</f>
-        <v>34.5</v>
-      </c>
-    </row>
-    <row r="54" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="K54">
-        <f>SUM(K50:K53)</f>
-        <v>111</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="47">
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C21:C26"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Horarios/HorarioWAN_2026.xlsx
+++ b/Horarios/HorarioWAN_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecmx-my.sharepoint.com/personal/lperezf_tec_mx/Documents/Documents/GitLiz/WAN/Horarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="8_{FC23BDE9-CBF9-4CD9-B661-15FDB57BE38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8EFF27F-1D38-4B85-B337-DA811DC210E5}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="8_{FC23BDE9-CBF9-4CD9-B661-15FDB57BE38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B33A80D-EE9D-40D6-8D3E-495FF3816C2F}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
   </bookViews>
   <sheets>
     <sheet name="WAN_201" sheetId="5" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="65">
   <si>
     <t>3:00 - 4:00</t>
   </si>
@@ -357,6 +357,9 @@
     <t>Módulo 1                                               
                                  Visita                           
                                  BOHN</t>
+  </si>
+  <si>
+    <t>MODULO 1</t>
   </si>
 </sst>
 </file>
@@ -644,47 +647,119 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -696,78 +771,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1130,19 +1133,19 @@
       <c r="B3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="17" t="s">
+      <c r="D3" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="51" t="s">
+      <c r="F3" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="46" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1150,21 +1153,21 @@
       <c r="B4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="52"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="47"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="51" t="s">
+      <c r="C5" s="27"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="46" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1172,38 +1175,38 @@
       <c r="B6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="17" t="s">
+      <c r="E6" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="53"/>
+      <c r="G6" s="48"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="52"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="47"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
@@ -1233,19 +1236,19 @@
       <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="21" t="s">
+      <c r="C12" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="18" t="s">
+      <c r="F12" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1253,25 +1256,25 @@
       <c r="B13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="18"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="20"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="38" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="23"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="24" t="s">
+      <c r="E14" s="41"/>
+      <c r="F14" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="40" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1279,25 +1282,25 @@
       <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="21" t="s">
+      <c r="C15" s="39"/>
+      <c r="D15" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="27"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="25"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="40"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="22"/>
-      <c r="G16" s="25"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="39"/>
+      <c r="G16" s="40"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
@@ -1305,7 +1308,7 @@
       </c>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
-      <c r="E17" s="20"/>
+      <c r="E17" s="31"/>
       <c r="F17" s="23"/>
       <c r="G17" s="6"/>
     </row>
@@ -1336,19 +1339,19 @@
       <c r="B21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="42" t="s">
+      <c r="C21" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="28" t="s">
+      <c r="E21" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="14" t="s">
+      <c r="F21" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="27" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1356,23 +1359,23 @@
       <c r="B22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="14"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="27"/>
     </row>
     <row r="23" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C23" s="23"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="43" t="s">
+      <c r="D23" s="45"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="18" t="s">
+      <c r="G23" s="20" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1380,33 +1383,33 @@
       <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C24" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="E24" s="30"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="18"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="20"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="32"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="20"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="33"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="31"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="55"/>
       <c r="F26" s="23"/>
       <c r="G26" s="6"/>
     </row>
@@ -1437,19 +1440,19 @@
       <c r="B30" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="24" t="s">
+      <c r="C30" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="14" t="s">
+      <c r="F30" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="27" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1457,27 +1460,27 @@
       <c r="B31" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="34"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="14"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="27"/>
     </row>
     <row r="32" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="24" t="s">
+      <c r="C32" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="34"/>
-      <c r="E32" s="36" t="s">
+      <c r="D32" s="16"/>
+      <c r="E32" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="39" t="s">
+      <c r="F32" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="18" t="s">
+      <c r="G32" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1485,32 +1488,32 @@
       <c r="B33" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="32"/>
-      <c r="D33" s="24" t="s">
+      <c r="C33" s="18"/>
+      <c r="D33" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="37"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="18"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="20"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="20"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="33"/>
-      <c r="D35" s="33"/>
-      <c r="E35" s="38"/>
-      <c r="F35" s="41"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="37"/>
       <c r="G35" s="6"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.35">
@@ -1540,19 +1543,19 @@
       <c r="B39" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="18" t="s">
+      <c r="C39" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="42" t="s">
+      <c r="D39" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="24" t="s">
+      <c r="E39" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="F39" s="45" t="s">
+      <c r="F39" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="48" t="s">
+      <c r="G39" s="49" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1560,60 +1563,91 @@
       <c r="B40" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="18"/>
-      <c r="D40" s="42"/>
-      <c r="E40" s="32"/>
-      <c r="F40" s="46"/>
-      <c r="G40" s="49"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="45"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="50"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="43" t="s">
+      <c r="C41" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="42"/>
-      <c r="E41" s="33"/>
-      <c r="F41" s="46"/>
-      <c r="G41" s="49"/>
+      <c r="D41" s="45"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="28"/>
+      <c r="G41" s="50"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="44"/>
-      <c r="D42" s="18" t="s">
+      <c r="C42" s="22"/>
+      <c r="D42" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E42" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="F42" s="46"/>
-      <c r="G42" s="49"/>
+      <c r="E42" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F42" s="28"/>
+      <c r="G42" s="50"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C43" s="44"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="35"/>
-      <c r="F43" s="46"/>
-      <c r="G43" s="50"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="51"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C44" s="23"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="34"/>
-      <c r="F44" s="47"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="29"/>
       <c r="G44" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="E21:E26"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
     <mergeCell ref="C21:C23"/>
     <mergeCell ref="C24:C26"/>
     <mergeCell ref="D24:D26"/>
@@ -1630,37 +1664,6 @@
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="D12:D14"/>
     <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="E21:E26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="94" orientation="portrait" r:id="rId1"/>
@@ -1710,19 +1713,19 @@
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="17" t="s">
+      <c r="D3" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="17" t="s">
+      <c r="F3" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="42" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1730,21 +1733,21 @@
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="17"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="42"/>
     </row>
     <row r="5" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="18" t="s">
+      <c r="C5" s="27"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1752,38 +1755,38 @@
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="17" t="s">
+      <c r="E6" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="18"/>
+      <c r="G6" s="20"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="18"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="20"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
@@ -1813,19 +1816,19 @@
       <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="21" t="s">
+      <c r="C12" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="18" t="s">
+      <c r="F12" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1833,25 +1836,25 @@
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="18"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="20"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="38" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="23"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="24" t="s">
+      <c r="E14" s="41"/>
+      <c r="F14" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="40" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1859,25 +1862,25 @@
       <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="21" t="s">
+      <c r="C15" s="39"/>
+      <c r="D15" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="27"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="25"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="40"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="22"/>
-      <c r="G16" s="25"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="39"/>
+      <c r="G16" s="40"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
@@ -1885,7 +1888,7 @@
       </c>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
-      <c r="E17" s="20"/>
+      <c r="E17" s="31"/>
       <c r="F17" s="23"/>
       <c r="G17" s="6"/>
     </row>
@@ -1916,19 +1919,19 @@
       <c r="B21" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="42" t="s">
+      <c r="C21" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="28" t="s">
+      <c r="E21" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="14" t="s">
+      <c r="F21" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="27" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1936,23 +1939,23 @@
       <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="14"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="27"/>
     </row>
     <row r="23" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C23" s="23"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="43" t="s">
+      <c r="D23" s="45"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="18" t="s">
+      <c r="G23" s="20" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1960,33 +1963,33 @@
       <c r="B24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C24" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="E24" s="30"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="18"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="20"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="32"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="20"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="33"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="31"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="55"/>
       <c r="F26" s="23"/>
       <c r="G26" s="6"/>
     </row>
@@ -2017,19 +2020,19 @@
       <c r="B30" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="24" t="s">
+      <c r="C30" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="14" t="s">
+      <c r="F30" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="27" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2037,27 +2040,27 @@
       <c r="B31" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="34"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="14"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="27"/>
     </row>
     <row r="32" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="24" t="s">
+      <c r="C32" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="34"/>
-      <c r="E32" s="36" t="s">
+      <c r="D32" s="16"/>
+      <c r="E32" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="39" t="s">
+      <c r="F32" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="18" t="s">
+      <c r="G32" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2065,32 +2068,32 @@
       <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="32"/>
-      <c r="D33" s="24" t="s">
+      <c r="C33" s="18"/>
+      <c r="D33" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="37"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="18"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="20"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="20"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="33"/>
-      <c r="D35" s="33"/>
-      <c r="E35" s="38"/>
-      <c r="F35" s="41"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="37"/>
       <c r="G35" s="6"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.35">
@@ -2120,19 +2123,19 @@
       <c r="B39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="18" t="s">
+      <c r="C39" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="42" t="s">
+      <c r="D39" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="24" t="s">
+      <c r="E39" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="F39" s="45" t="s">
+      <c r="F39" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="48" t="s">
+      <c r="G39" s="49" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2140,87 +2143,70 @@
       <c r="B40" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="18"/>
-      <c r="D40" s="42"/>
-      <c r="E40" s="32"/>
-      <c r="F40" s="46"/>
-      <c r="G40" s="49"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="45"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="50"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="43" t="s">
+      <c r="C41" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="42"/>
-      <c r="E41" s="33"/>
-      <c r="F41" s="46"/>
-      <c r="G41" s="49"/>
+      <c r="D41" s="45"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="28"/>
+      <c r="G41" s="50"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="44"/>
-      <c r="D42" s="18" t="s">
+      <c r="C42" s="22"/>
+      <c r="D42" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E42" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="F42" s="46"/>
-      <c r="G42" s="49"/>
+      <c r="E42" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F42" s="28"/>
+      <c r="G42" s="50"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="44"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="35"/>
-      <c r="F43" s="46"/>
-      <c r="G43" s="50"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="51"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C44" s="23"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="34"/>
-      <c r="F44" s="47"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="29"/>
       <c r="G44" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E26"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
     <mergeCell ref="F12:F13"/>
     <mergeCell ref="G12:G13"/>
     <mergeCell ref="C14:C17"/>
@@ -2231,16 +2217,33 @@
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="D12:D14"/>
     <mergeCell ref="E12:E15"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E42:E44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="95" orientation="portrait" r:id="rId1"/>
@@ -2303,19 +2306,19 @@
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="17" t="s">
+      <c r="C3" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="17" t="s">
+      <c r="F3" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="42" t="s">
         <v>18</v>
       </c>
       <c r="I3" s="1"/>
@@ -2335,11 +2338,11 @@
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="17"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="42"/>
       <c r="I4" s="1"/>
       <c r="J4" t="s">
         <v>12</v>
@@ -2356,11 +2359,11 @@
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="18" t="s">
+      <c r="C5" s="42"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="20" t="s">
         <v>22</v>
       </c>
       <c r="J5" t="s">
@@ -2384,38 +2387,38 @@
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="E6" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="18"/>
+      <c r="G6" s="20"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="18"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="20"/>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.35">
@@ -2445,19 +2448,19 @@
       <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="21" t="s">
+      <c r="C12" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="18" t="s">
+      <c r="F12" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="20" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="1"/>
@@ -2476,11 +2479,11 @@
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="18"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="20"/>
       <c r="J13" s="1" t="s">
         <v>14</v>
       </c>
@@ -2495,15 +2498,15 @@
       <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="38" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="23"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="24" t="s">
+      <c r="E14" s="41"/>
+      <c r="F14" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="40" t="s">
         <v>23</v>
       </c>
       <c r="J14" t="s">
@@ -2521,13 +2524,13 @@
       <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="21" t="s">
+      <c r="C15" s="39"/>
+      <c r="D15" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="27"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="25"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="40"/>
       <c r="J15" t="s">
         <v>15</v>
       </c>
@@ -2542,13 +2545,13 @@
       <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="22"/>
-      <c r="G16" s="25"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="39"/>
+      <c r="G16" s="40"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
@@ -2558,7 +2561,7 @@
       </c>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
-      <c r="E17" s="20"/>
+      <c r="E17" s="31"/>
       <c r="F17" s="23"/>
       <c r="G17" s="6"/>
     </row>
@@ -2589,19 +2592,19 @@
       <c r="B21" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="42" t="s">
+      <c r="C21" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="14" t="s">
+      <c r="F21" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="27" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="1"/>
@@ -2620,11 +2623,11 @@
       <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="14"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="27"/>
       <c r="I22" s="1"/>
       <c r="J22" t="s">
         <v>12</v>
@@ -2642,14 +2645,14 @@
         <v>2</v>
       </c>
       <c r="C23" s="23"/>
-      <c r="D23" s="43" t="s">
+      <c r="D23" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="42"/>
-      <c r="F23" s="24" t="s">
+      <c r="E23" s="45"/>
+      <c r="F23" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="18" t="s">
+      <c r="G23" s="20" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -2669,15 +2672,15 @@
       <c r="B24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C24" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="44"/>
-      <c r="E24" s="18" t="s">
+      <c r="D24" s="22"/>
+      <c r="E24" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="32"/>
-      <c r="G24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="20"/>
       <c r="J24" t="s">
         <v>31</v>
       </c>
@@ -2693,21 +2696,21 @@
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="32"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="20"/>
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="33"/>
+      <c r="C26" s="19"/>
       <c r="D26" s="23"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="33"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="6"/>
       <c r="P26" s="1"/>
     </row>
@@ -2743,19 +2746,19 @@
       <c r="B30" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="24" t="s">
+      <c r="C30" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="14" t="s">
+      <c r="F30" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="27" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="1"/>
@@ -2775,11 +2778,11 @@
       <c r="B31" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="35"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="14"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="27"/>
       <c r="J31" t="s">
         <v>12</v>
       </c>
@@ -2796,15 +2799,15 @@
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="36" t="s">
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="39" t="s">
+      <c r="F32" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="18" t="s">
+      <c r="G32" s="20" t="s">
         <v>22</v>
       </c>
       <c r="J32" s="1" t="s">
@@ -2824,15 +2827,15 @@
       <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="24" t="s">
+      <c r="C33" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="24" t="s">
+      <c r="D33" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="37"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="18"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="20"/>
       <c r="J33" t="s">
         <v>31</v>
       </c>
@@ -2848,21 +2851,21 @@
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="20"/>
       <c r="P34" s="1"/>
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="33"/>
-      <c r="D35" s="33"/>
-      <c r="E35" s="38"/>
-      <c r="F35" s="41"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="37"/>
       <c r="G35" s="6"/>
       <c r="P35" s="1"/>
     </row>
@@ -2898,19 +2901,19 @@
       <c r="B39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="18" t="s">
+      <c r="C39" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="18" t="s">
+      <c r="D39" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="F39" s="18" t="s">
+      <c r="E39" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="G39" s="45" t="s">
+      <c r="G39" s="24" t="s">
         <v>57</v>
       </c>
       <c r="I39" s="1"/>
@@ -2929,11 +2932,11 @@
       <c r="B40" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="35"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="46"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="28"/>
       <c r="I40" s="1"/>
       <c r="J40" t="s">
         <v>12</v>
@@ -2950,13 +2953,13 @@
       <c r="B41" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="43" t="s">
+      <c r="C41" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="18"/>
-      <c r="E41" s="34"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="46"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="28"/>
       <c r="I41" s="1"/>
       <c r="J41" t="s">
         <v>15</v>
@@ -2979,27 +2982,27 @@
       <c r="B42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="44"/>
-      <c r="D42" s="45" t="s">
+      <c r="C42" s="22"/>
+      <c r="D42" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E42" s="45" t="s">
+      <c r="E42" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="45" t="s">
+      <c r="F42" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="G42" s="46"/>
+      <c r="G42" s="28"/>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="44"/>
-      <c r="D43" s="54"/>
-      <c r="E43" s="54"/>
-      <c r="F43" s="54"/>
-      <c r="G43" s="47"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="25"/>
+      <c r="G43" s="29"/>
       <c r="K43" s="1">
         <f>SUM(K3:K41)</f>
         <v>120</v>
@@ -3022,9 +3025,9 @@
         <v>5</v>
       </c>
       <c r="C44" s="23"/>
-      <c r="D44" s="55"/>
-      <c r="E44" s="55"/>
-      <c r="F44" s="55"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="26"/>
       <c r="G44" s="6"/>
     </row>
     <row r="46" spans="2:16" x14ac:dyDescent="0.35">
@@ -3088,11 +3091,34 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="D23:D26"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
     <mergeCell ref="G21:G22"/>
     <mergeCell ref="G23:G25"/>
     <mergeCell ref="G39:G43"/>
@@ -3109,37 +3135,14 @@
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="D42:D44"/>
     <mergeCell ref="F39:F41"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="D23:D26"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="F42:F44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="32" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3195,19 +3198,19 @@
       <c r="B3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="17" t="s">
+      <c r="D3" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="51" t="s">
+      <c r="F3" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="46" t="s">
         <v>62</v>
       </c>
       <c r="I3" s="1"/>
@@ -3227,11 +3230,11 @@
       <c r="B4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="52"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="47"/>
       <c r="I4" s="1"/>
       <c r="J4" t="s">
         <v>12</v>
@@ -3248,11 +3251,11 @@
       <c r="B5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="51" t="s">
+      <c r="C5" s="27"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="46" t="s">
         <v>63</v>
       </c>
       <c r="J5" t="s">
@@ -3276,38 +3279,38 @@
       <c r="B6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="17" t="s">
+      <c r="E6" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="53"/>
+      <c r="G6" s="48"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="52"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="47"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.35">
@@ -3337,19 +3340,19 @@
       <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="21" t="s">
+      <c r="C12" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="18" t="s">
+      <c r="F12" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="20" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="1"/>
@@ -3368,11 +3371,11 @@
       <c r="B13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="18"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="20"/>
       <c r="J13" s="1" t="s">
         <v>14</v>
       </c>
@@ -3387,15 +3390,15 @@
       <c r="B14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="38" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="23"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="24" t="s">
+      <c r="E14" s="41"/>
+      <c r="F14" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="40" t="s">
         <v>23</v>
       </c>
       <c r="J14" t="s">
@@ -3413,13 +3416,13 @@
       <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="21" t="s">
+      <c r="C15" s="39"/>
+      <c r="D15" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="27"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="25"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="40"/>
       <c r="J15" t="s">
         <v>15</v>
       </c>
@@ -3434,13 +3437,13 @@
       <c r="B16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="22"/>
-      <c r="G16" s="25"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="39"/>
+      <c r="G16" s="40"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
@@ -3450,7 +3453,7 @@
       </c>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
-      <c r="E17" s="20"/>
+      <c r="E17" s="31"/>
       <c r="F17" s="23"/>
       <c r="G17" s="6"/>
     </row>
@@ -3481,19 +3484,19 @@
       <c r="B21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="42" t="s">
+      <c r="D21" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="14" t="s">
+      <c r="F21" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="27" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="1"/>
@@ -3512,11 +3515,11 @@
       <c r="B22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="29"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="14"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="27"/>
       <c r="I22" s="1"/>
       <c r="J22" t="s">
         <v>12</v>
@@ -3533,13 +3536,13 @@
       <c r="B23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="30"/>
+      <c r="C23" s="54"/>
       <c r="D23" s="23"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="43" t="s">
+      <c r="E23" s="45"/>
+      <c r="F23" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="18" t="s">
+      <c r="G23" s="20" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -3559,15 +3562,15 @@
       <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="30"/>
-      <c r="D24" s="24" t="s">
+      <c r="C24" s="54"/>
+      <c r="D24" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="44"/>
-      <c r="G24" s="18"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="20"/>
       <c r="J24" t="s">
         <v>31</v>
       </c>
@@ -3583,20 +3586,20 @@
       <c r="B25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="30"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="18"/>
+      <c r="C25" s="54"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="20"/>
       <c r="O25" s="1"/>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="31"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="18"/>
+      <c r="C26" s="55"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="20"/>
       <c r="F26" s="23"/>
       <c r="G26" s="6"/>
       <c r="O26" s="1"/>
@@ -3633,19 +3636,19 @@
       <c r="B30" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="24" t="s">
+      <c r="C30" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="14" t="s">
+      <c r="F30" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="27" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="1"/>
@@ -3665,11 +3668,11 @@
       <c r="B31" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="34"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="14"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="27"/>
       <c r="J31" t="s">
         <v>12</v>
       </c>
@@ -3686,17 +3689,17 @@
       <c r="B32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="24" t="s">
+      <c r="C32" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="34"/>
-      <c r="E32" s="36" t="s">
+      <c r="D32" s="16"/>
+      <c r="E32" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="39" t="s">
+      <c r="F32" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="18" t="s">
+      <c r="G32" s="20" t="s">
         <v>22</v>
       </c>
       <c r="J32" s="1" t="s">
@@ -3716,13 +3719,13 @@
       <c r="B33" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="32"/>
-      <c r="D33" s="24" t="s">
+      <c r="C33" s="18"/>
+      <c r="D33" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="37"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="18"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="20"/>
       <c r="J33" t="s">
         <v>31</v>
       </c>
@@ -3738,21 +3741,21 @@
       <c r="B34" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="20"/>
       <c r="O34" s="1"/>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="33"/>
-      <c r="D35" s="33"/>
-      <c r="E35" s="38"/>
-      <c r="F35" s="41"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="37"/>
       <c r="G35" s="6"/>
       <c r="O35" s="1"/>
     </row>
@@ -3788,19 +3791,19 @@
       <c r="B39" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="18" t="s">
+      <c r="C39" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="42" t="s">
+      <c r="D39" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="45" t="s">
+      <c r="F39" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="48" t="s">
+      <c r="G39" s="49" t="s">
         <v>16</v>
       </c>
       <c r="I39" s="1"/>
@@ -3820,11 +3823,11 @@
       <c r="B40" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="18"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="42"/>
-      <c r="F40" s="46"/>
-      <c r="G40" s="49"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="50"/>
       <c r="I40" s="1"/>
       <c r="J40" t="s">
         <v>12</v>
@@ -3841,13 +3844,13 @@
       <c r="B41" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="43" t="s">
+      <c r="C41" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="34"/>
-      <c r="E41" s="42"/>
-      <c r="F41" s="46"/>
-      <c r="G41" s="49"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="28"/>
+      <c r="G41" s="50"/>
       <c r="I41" s="1"/>
       <c r="J41" t="s">
         <v>15</v>
@@ -3870,25 +3873,25 @@
       <c r="B42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="44"/>
-      <c r="D42" s="24" t="s">
+      <c r="C42" s="22"/>
+      <c r="D42" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="18" t="s">
+      <c r="E42" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="46"/>
-      <c r="G42" s="49"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="50"/>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C43" s="44"/>
-      <c r="D43" s="32"/>
-      <c r="E43" s="18"/>
-      <c r="F43" s="46"/>
-      <c r="G43" s="50"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="51"/>
       <c r="K43" s="1">
         <f>SUM(K3:K41)</f>
         <v>111</v>
@@ -3908,9 +3911,900 @@
         <v>39</v>
       </c>
       <c r="C44" s="23"/>
-      <c r="D44" s="33"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="47"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="6"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K46">
+        <f>5*4*5</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K47">
+        <f>4*5</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K48">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="K49">
+        <f>120-5-4</f>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J50" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K50" s="1">
+        <f>K3+K12</f>
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="51" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J51" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K51" s="1">
+        <f>K13+K21+K30+K39</f>
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="52" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J52" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K52" s="1">
+        <f>K4+K14+K22+K31+K40</f>
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="53" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J53" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K53" s="1">
+        <f>K5+K15+K23+K24+K32+K33+K41</f>
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="54" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="K54">
+        <f>SUM(K50:K53)</f>
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="47">
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="C21:C26"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B72F34B-8139-4D0E-8882-03145DDD5E1F}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:O54"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="2" customWidth="1"/>
+    <col min="2" max="2" width="10.90625" style="2"/>
+    <col min="3" max="4" width="12.6328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.7265625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="4.36328125" customWidth="1"/>
+    <col min="10" max="10" width="15.7265625" customWidth="1"/>
+    <col min="13" max="14" width="10.90625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B1" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B2" s="4"/>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="1">
+        <f>2.5+2.5+2.5+2.5+2</f>
+        <v>12</v>
+      </c>
+      <c r="M3" s="9">
+        <f>K3</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="27"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="42"/>
+      <c r="I4" s="1"/>
+      <c r="J4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4">
+        <f>2.5+2.5+2.5</f>
+        <v>7.5</v>
+      </c>
+      <c r="N4" s="2">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5">
+        <f>2.5+2</f>
+        <v>4.5</v>
+      </c>
+      <c r="M5" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="N5" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="20"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="20"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="5"/>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B10" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B11" s="4"/>
+      <c r="C11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" s="1">
+        <f>3+2.5+3+2</f>
+        <v>10.5</v>
+      </c>
+      <c r="M12" s="2">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="31"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="20"/>
+      <c r="J13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" s="1">
+        <v>3</v>
+      </c>
+      <c r="M13" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="23"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14">
+        <f>2+2.5+2+2</f>
+        <v>8.5</v>
+      </c>
+      <c r="N14" s="2">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="39"/>
+      <c r="D15" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="41"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="40"/>
+      <c r="J15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="N15" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="39"/>
+      <c r="G16" s="40"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="6"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B19" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B20" s="4"/>
+      <c r="C20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="45" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K21" s="1">
+        <f>2.5+3</f>
+        <v>5.5</v>
+      </c>
+      <c r="M21" s="2">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="53"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="27"/>
+      <c r="I22" s="1"/>
+      <c r="J22" t="s">
+        <v>12</v>
+      </c>
+      <c r="K22">
+        <f>2.5+2</f>
+        <v>4.5</v>
+      </c>
+      <c r="N22" s="2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="54"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K23" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="M23" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="O23" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="54"/>
+      <c r="D24" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="22"/>
+      <c r="G24" s="20"/>
+      <c r="J24" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24">
+        <v>4.5</v>
+      </c>
+      <c r="N24" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O24" s="1"/>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B25" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="54"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="20"/>
+      <c r="O25" s="1"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="55"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="6"/>
+      <c r="O26" s="1"/>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="O27" s="1"/>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B28" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="O28" s="1"/>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B29" s="4"/>
+      <c r="C29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O29" s="1"/>
+    </row>
+    <row r="30" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K30" s="1">
+        <f>3+2.5+2+3</f>
+        <v>10.5</v>
+      </c>
+      <c r="M30" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="O30" s="1"/>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="16"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="27"/>
+      <c r="J31" t="s">
+        <v>12</v>
+      </c>
+      <c r="K31">
+        <f>2+2.5+2</f>
+        <v>6.5</v>
+      </c>
+      <c r="N31" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="O31" s="1"/>
+    </row>
+    <row r="32" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="16"/>
+      <c r="E32" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K32" s="1">
+        <v>2</v>
+      </c>
+      <c r="M32" s="10">
+        <v>2</v>
+      </c>
+      <c r="O32" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="18"/>
+      <c r="D33" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="33"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="20"/>
+      <c r="J33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K33" s="1">
+        <v>5</v>
+      </c>
+      <c r="N33" s="2">
+        <v>5</v>
+      </c>
+      <c r="O33" s="1"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B34" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="20"/>
+      <c r="O34" s="1"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="6"/>
+      <c r="O35" s="1"/>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="O36" s="1"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B37" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O37" s="1"/>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B38" s="4"/>
+      <c r="C38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O38" s="1"/>
+    </row>
+    <row r="39" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K39" s="1">
+        <f>3+2.5</f>
+        <v>5.5</v>
+      </c>
+      <c r="M39" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="O39" s="1"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="20"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="50"/>
+      <c r="I40" s="1"/>
+      <c r="J40" t="s">
+        <v>12</v>
+      </c>
+      <c r="K40">
+        <v>2.5</v>
+      </c>
+      <c r="N40" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="O40" s="1"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="16"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="28"/>
+      <c r="G41" s="50"/>
+      <c r="I41" s="1"/>
+      <c r="J41" t="s">
+        <v>15</v>
+      </c>
+      <c r="K41">
+        <v>12</v>
+      </c>
+      <c r="M41" s="10">
+        <f>4.5</f>
+        <v>4.5</v>
+      </c>
+      <c r="N41" s="2">
+        <f>2+2.5+5</f>
+        <v>9.5</v>
+      </c>
+      <c r="O41" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="22"/>
+      <c r="D42" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="28"/>
+      <c r="G42" s="50"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" s="22"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="51"/>
+      <c r="K43" s="1">
+        <f>SUM(K3:K41)</f>
+        <v>111</v>
+      </c>
+      <c r="L43" s="1"/>
+      <c r="M43" s="9">
+        <f>SUM(M3:M41)</f>
+        <v>59.5</v>
+      </c>
+      <c r="N43" s="9">
+        <f>SUM(N3:N41)</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="23"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="29"/>
       <c r="G44" s="6"/>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.35">
@@ -4031,895 +4925,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B72F34B-8139-4D0E-8882-03145DDD5E1F}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B1:O54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="10.90625" style="2"/>
-    <col min="3" max="4" width="12.6328125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.7265625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.1796875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="4.36328125" customWidth="1"/>
-    <col min="10" max="10" width="15.7265625" customWidth="1"/>
-    <col min="13" max="14" width="10.90625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B1" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B2" s="4"/>
-      <c r="C2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="1">
-        <f>2.5+2.5+2.5+2.5+2</f>
-        <v>12</v>
-      </c>
-      <c r="M3" s="9">
-        <f>K3</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="17"/>
-      <c r="I4" s="1"/>
-      <c r="J4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K4">
-        <f>2.5+2.5+2.5</f>
-        <v>7.5</v>
-      </c>
-      <c r="N4" s="2">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5">
-        <f>2.5+2</f>
-        <v>4.5</v>
-      </c>
-      <c r="M5" s="10">
-        <v>1.5</v>
-      </c>
-      <c r="N5" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="18"/>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="18"/>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="5"/>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B10" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B11" s="4"/>
-      <c r="C11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K12" s="1">
-        <f>3+2.5+3+2</f>
-        <v>10.5</v>
-      </c>
-      <c r="M12" s="2">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B13" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="18"/>
-      <c r="J13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="1">
-        <v>3</v>
-      </c>
-      <c r="M13" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B14" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="23"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J14" t="s">
-        <v>12</v>
-      </c>
-      <c r="K14">
-        <f>2+2.5+2+2</f>
-        <v>8.5</v>
-      </c>
-      <c r="N14" s="2">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="27"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="25"/>
-      <c r="J15" t="s">
-        <v>15</v>
-      </c>
-      <c r="K15">
-        <v>2</v>
-      </c>
-      <c r="N15" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B16" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="22"/>
-      <c r="G16" s="25"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="6"/>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B19" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B20" s="4"/>
-      <c r="C20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="42" t="s">
-        <v>61</v>
-      </c>
-      <c r="F21" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K21" s="1">
-        <f>2.5+3</f>
-        <v>5.5</v>
-      </c>
-      <c r="M21" s="2">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B22" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="29"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="14"/>
-      <c r="I22" s="1"/>
-      <c r="J22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K22">
-        <f>2.5+2</f>
-        <v>4.5</v>
-      </c>
-      <c r="N22" s="2">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="23" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="30"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="43" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K23" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="M23" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="O23" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" s="30"/>
-      <c r="D24" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="F24" s="44"/>
-      <c r="G24" s="18"/>
-      <c r="J24" t="s">
-        <v>31</v>
-      </c>
-      <c r="K24">
-        <v>4.5</v>
-      </c>
-      <c r="N24" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="O24" s="1"/>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B25" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="30"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="18"/>
-      <c r="O25" s="1"/>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="31"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="6"/>
-      <c r="O26" s="1"/>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="O27" s="1"/>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B28" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="O28" s="1"/>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B29" s="4"/>
-      <c r="C29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="O29" s="1"/>
-    </row>
-    <row r="30" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K30" s="1">
-        <f>3+2.5+2+3</f>
-        <v>10.5</v>
-      </c>
-      <c r="M30" s="2">
-        <v>10.5</v>
-      </c>
-      <c r="O30" s="1"/>
-    </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B31" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" s="34"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="14"/>
-      <c r="J31" t="s">
-        <v>12</v>
-      </c>
-      <c r="K31">
-        <f>2+2.5+2</f>
-        <v>6.5</v>
-      </c>
-      <c r="N31" s="2">
-        <v>6.5</v>
-      </c>
-      <c r="O31" s="1"/>
-    </row>
-    <row r="32" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="34"/>
-      <c r="E32" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K32" s="1">
-        <v>2</v>
-      </c>
-      <c r="M32" s="10">
-        <v>2</v>
-      </c>
-      <c r="O32" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" s="32"/>
-      <c r="D33" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="37"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="18"/>
-      <c r="J33" t="s">
-        <v>31</v>
-      </c>
-      <c r="K33" s="1">
-        <v>5</v>
-      </c>
-      <c r="N33" s="2">
-        <v>5</v>
-      </c>
-      <c r="O33" s="1"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B34" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="18"/>
-      <c r="O34" s="1"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="33"/>
-      <c r="D35" s="33"/>
-      <c r="E35" s="38"/>
-      <c r="F35" s="41"/>
-      <c r="G35" s="6"/>
-      <c r="O35" s="1"/>
-    </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="O36" s="1"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B37" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O37" s="1"/>
-    </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B38" s="4"/>
-      <c r="C38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="O38" s="1"/>
-    </row>
-    <row r="39" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C39" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="G39" s="48" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K39" s="1">
-        <f>3+2.5</f>
-        <v>5.5</v>
-      </c>
-      <c r="M39" s="2">
-        <v>5.5</v>
-      </c>
-      <c r="O39" s="1"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B40" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="18"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="42"/>
-      <c r="F40" s="46"/>
-      <c r="G40" s="49"/>
-      <c r="I40" s="1"/>
-      <c r="J40" t="s">
-        <v>12</v>
-      </c>
-      <c r="K40">
-        <v>2.5</v>
-      </c>
-      <c r="N40" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="O40" s="1"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="43" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41" s="34"/>
-      <c r="E41" s="42"/>
-      <c r="F41" s="46"/>
-      <c r="G41" s="49"/>
-      <c r="I41" s="1"/>
-      <c r="J41" t="s">
-        <v>15</v>
-      </c>
-      <c r="K41">
-        <v>12</v>
-      </c>
-      <c r="M41" s="10">
-        <f>4.5</f>
-        <v>4.5</v>
-      </c>
-      <c r="N41" s="2">
-        <f>2+2.5+5</f>
-        <v>9.5</v>
-      </c>
-      <c r="O41" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C42" s="44"/>
-      <c r="D42" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="46"/>
-      <c r="G42" s="49"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C43" s="44"/>
-      <c r="D43" s="32"/>
-      <c r="E43" s="18"/>
-      <c r="F43" s="46"/>
-      <c r="G43" s="50"/>
-      <c r="K43" s="1">
-        <f>SUM(K3:K41)</f>
-        <v>111</v>
-      </c>
-      <c r="L43" s="1"/>
-      <c r="M43" s="9">
-        <f>SUM(M3:M41)</f>
-        <v>59.5</v>
-      </c>
-      <c r="N43" s="9">
-        <f>SUM(N3:N41)</f>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C44" s="23"/>
-      <c r="D44" s="33"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="47"/>
-      <c r="G44" s="6"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K46">
-        <f>5*4*5</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K47">
-        <f>4*5</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K48">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="49" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="K49">
-        <f>120-5-4</f>
-        <v>111</v>
-      </c>
-    </row>
-    <row r="50" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J50" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K50" s="1">
-        <f>K3+K12</f>
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="51" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J51" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K51" s="1">
-        <f>K13+K21+K30+K39</f>
-        <v>24.5</v>
-      </c>
-    </row>
-    <row r="52" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J52" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K52" s="1">
-        <f>K4+K14+K22+K31+K40</f>
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="53" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J53" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K53" s="1">
-        <f>K5+K15+K23+K24+K32+K33+K41</f>
-        <v>34.5</v>
-      </c>
-    </row>
-    <row r="54" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="K54">
-        <f>SUM(K50:K53)</f>
-        <v>111</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="47">
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="C21:C26"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Horarios/HorarioWAN_2026.xlsx
+++ b/Horarios/HorarioWAN_2026.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecmx-my.sharepoint.com/personal/lperezf_tec_mx/Documents/Documents/GitLiz/WAN/Horarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{FC23BDE9-CBF9-4CD9-B661-15FDB57BE38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B33A80D-EE9D-40D6-8D3E-495FF3816C2F}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="8_{FC23BDE9-CBF9-4CD9-B661-15FDB57BE38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AAD2FCD-CB72-4956-B4C6-84AD9BC4E68D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
   </bookViews>
   <sheets>
     <sheet name="WAN_201" sheetId="5" r:id="rId1"/>
     <sheet name="WAN_202" sheetId="7" r:id="rId2"/>
-    <sheet name="WAN_301" sheetId="8" r:id="rId3"/>
+    <sheet name="WAN_301" sheetId="11" r:id="rId3"/>
     <sheet name="WAN_201_Completo" sheetId="9" r:id="rId4"/>
-    <sheet name="WAN_202_COMPLETO" sheetId="10" r:id="rId5"/>
+    <sheet name="WAN_202_Completo" sheetId="10" r:id="rId5"/>
+    <sheet name="WAN_301_Completo" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="65">
   <si>
     <t>3:00 - 4:00</t>
   </si>
@@ -650,9 +651,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -665,7 +663,16 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -674,19 +681,34 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -695,10 +717,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -719,47 +738,11 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -772,6 +755,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -793,6 +794,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1133,19 +1138,19 @@
       <c r="B3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="42" t="s">
+      <c r="D3" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="46" t="s">
+      <c r="F3" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="53" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1153,21 +1158,21 @@
       <c r="B4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="47"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="54"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="46" t="s">
+      <c r="C5" s="28"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="53" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1175,38 +1180,38 @@
       <c r="B6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="C6" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="42" t="s">
+      <c r="D6" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="42" t="s">
+      <c r="E6" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="48"/>
+      <c r="G6" s="55"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="47"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="54"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
@@ -1236,19 +1241,19 @@
       <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C12" s="21" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="38" t="s">
+      <c r="E12" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="20" t="s">
+      <c r="F12" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="26" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1256,25 +1261,25 @@
       <c r="B13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="20"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="26"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="23"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="17" t="s">
+      <c r="D14" s="20"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="40" t="s">
+      <c r="G14" s="32" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1282,34 +1287,34 @@
       <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="39"/>
-      <c r="D15" s="38" t="s">
+      <c r="C15" s="19"/>
+      <c r="D15" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="41"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="40"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="32"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="39"/>
-      <c r="G16" s="40"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="19"/>
+      <c r="G16" s="32"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="23"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="20"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.35">
@@ -1342,16 +1347,16 @@
       <c r="C21" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="45" t="s">
+      <c r="D21" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="52" t="s">
+      <c r="E21" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="27" t="s">
+      <c r="F21" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="28" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1359,23 +1364,23 @@
       <c r="B22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="39"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="27"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="28"/>
     </row>
     <row r="23" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="23"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="21" t="s">
+      <c r="C23" s="20"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="20" t="s">
+      <c r="G23" s="26" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1383,34 +1388,34 @@
       <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="20" t="s">
+      <c r="D24" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="E24" s="54"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="20"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="26"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="54"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="20"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="26"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="55"/>
-      <c r="F26" s="23"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="20"/>
       <c r="G26" s="6"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
@@ -1446,13 +1451,13 @@
       <c r="D30" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E30" s="17" t="s">
+      <c r="E30" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="27" t="s">
+      <c r="F30" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="28" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1460,27 +1465,27 @@
       <c r="B31" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="27"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="28"/>
     </row>
     <row r="32" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="16"/>
-      <c r="E32" s="32" t="s">
+      <c r="D32" s="15"/>
+      <c r="E32" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="35" t="s">
+      <c r="F32" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="20" t="s">
+      <c r="G32" s="26" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1488,32 +1493,32 @@
       <c r="B33" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="18"/>
-      <c r="D33" s="17" t="s">
+      <c r="C33" s="17"/>
+      <c r="D33" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="33"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="20"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="26"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="20"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="26"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="37"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="43"/>
       <c r="G35" s="6"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.35">
@@ -1543,19 +1548,19 @@
       <c r="B39" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="20" t="s">
+      <c r="C39" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="45" t="s">
+      <c r="D39" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="17" t="s">
+      <c r="E39" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F39" s="24" t="s">
+      <c r="F39" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="49" t="s">
+      <c r="G39" s="50" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1563,60 +1568,91 @@
       <c r="B40" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="20"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="50"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="51"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="21" t="s">
+      <c r="C41" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="45"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="50"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="35"/>
+      <c r="G41" s="51"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="22"/>
-      <c r="D42" s="20" t="s">
+      <c r="C42" s="24"/>
+      <c r="D42" s="26" t="s">
         <v>13</v>
       </c>
       <c r="E42" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F42" s="28"/>
-      <c r="G42" s="50"/>
+      <c r="F42" s="35"/>
+      <c r="G42" s="51"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C43" s="22"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="51"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="37"/>
+      <c r="F43" s="35"/>
+      <c r="G43" s="52"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="23"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="29"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="36"/>
       <c r="G44" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="D42:D44"/>
     <mergeCell ref="G21:G22"/>
     <mergeCell ref="G23:G25"/>
     <mergeCell ref="G30:G31"/>
@@ -1633,37 +1669,6 @@
     <mergeCell ref="F21:F22"/>
     <mergeCell ref="F23:F26"/>
     <mergeCell ref="E21:E26"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="94" orientation="portrait" r:id="rId1"/>
@@ -1713,19 +1718,19 @@
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="42" t="s">
+      <c r="D3" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="42" t="s">
+      <c r="F3" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="27" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1733,21 +1738,21 @@
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="42"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="27"/>
     </row>
     <row r="5" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="20" t="s">
+      <c r="C5" s="28"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="26" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1755,38 +1760,38 @@
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="C6" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="42" t="s">
+      <c r="D6" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="42" t="s">
+      <c r="E6" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="20"/>
+      <c r="G6" s="26"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="20"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="26"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
@@ -1816,19 +1821,19 @@
       <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C12" s="21" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="38" t="s">
+      <c r="E12" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="20" t="s">
+      <c r="F12" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="26" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1836,25 +1841,25 @@
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="20"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="26"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="23"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="17" t="s">
+      <c r="D14" s="20"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="40" t="s">
+      <c r="G14" s="32" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1862,34 +1867,34 @@
       <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="39"/>
-      <c r="D15" s="38" t="s">
+      <c r="C15" s="19"/>
+      <c r="D15" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="41"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="40"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="32"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="39"/>
-      <c r="G16" s="40"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="19"/>
+      <c r="G16" s="32"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="23"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="20"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.35">
@@ -1922,16 +1927,16 @@
       <c r="C21" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="45" t="s">
+      <c r="D21" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="52" t="s">
+      <c r="E21" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="27" t="s">
+      <c r="F21" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="28" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1939,23 +1944,23 @@
       <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="39"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="27"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="28"/>
     </row>
     <row r="23" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="23"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="21" t="s">
+      <c r="C23" s="20"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="20" t="s">
+      <c r="G23" s="26" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1963,34 +1968,34 @@
       <c r="B24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="20" t="s">
+      <c r="D24" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="E24" s="54"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="20"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="26"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="54"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="20"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="26"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="55"/>
-      <c r="F26" s="23"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="20"/>
       <c r="G26" s="6"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
@@ -2026,13 +2031,13 @@
       <c r="D30" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E30" s="17" t="s">
+      <c r="E30" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="27" t="s">
+      <c r="F30" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="28" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2040,27 +2045,27 @@
       <c r="B31" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="27"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="28"/>
     </row>
     <row r="32" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="16"/>
-      <c r="E32" s="32" t="s">
+      <c r="D32" s="15"/>
+      <c r="E32" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="35" t="s">
+      <c r="F32" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="20" t="s">
+      <c r="G32" s="26" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2068,32 +2073,32 @@
       <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="18"/>
-      <c r="D33" s="17" t="s">
+      <c r="C33" s="17"/>
+      <c r="D33" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="33"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="20"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="26"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="20"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="26"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="37"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="43"/>
       <c r="G35" s="6"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.35">
@@ -2123,19 +2128,19 @@
       <c r="B39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="20" t="s">
+      <c r="C39" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="45" t="s">
+      <c r="D39" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="17" t="s">
+      <c r="E39" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F39" s="24" t="s">
+      <c r="F39" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="49" t="s">
+      <c r="G39" s="50" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2143,60 +2148,97 @@
       <c r="B40" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="20"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="50"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="51"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="21" t="s">
+      <c r="C41" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="45"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="50"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="35"/>
+      <c r="G41" s="51"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="22"/>
-      <c r="D42" s="20" t="s">
+      <c r="C42" s="24"/>
+      <c r="D42" s="26" t="s">
         <v>13</v>
       </c>
       <c r="E42" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F42" s="28"/>
-      <c r="G42" s="50"/>
+      <c r="F42" s="35"/>
+      <c r="G42" s="51"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="22"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="51"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="37"/>
+      <c r="F43" s="35"/>
+      <c r="G43" s="52"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="23"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="29"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="36"/>
       <c r="G44" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="E3:E5"/>
@@ -2207,43 +2249,6 @@
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="E6:E8"/>
     <mergeCell ref="F6:F8"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E26"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E42:E44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="95" orientation="portrait" r:id="rId1"/>
@@ -2251,11 +2256,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1185C20-CB13-4526-80BC-F11E35C8CC5F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18A3CA16-1EA6-4AF1-B2CF-6B0F311BFBF6}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:P54"/>
+  <dimension ref="B1:G44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -2265,26 +2270,14 @@
     <col min="5" max="5" width="16.7265625" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.1796875" style="2" customWidth="1"/>
     <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="4.36328125" customWidth="1"/>
-    <col min="10" max="10" width="15.7265625" customWidth="1"/>
-    <col min="13" max="15" width="10.90625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B1" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="M1" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="O1" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B2" s="4"/>
       <c r="C2" s="3" t="s">
         <v>6</v>
@@ -2302,131 +2295,92 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="42" t="s">
+      <c r="C3" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="42" t="s">
+      <c r="D3" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="42" t="s">
+      <c r="F3" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="1">
-        <f>2.5+2.5+2.5+2.5+2</f>
-        <v>12</v>
-      </c>
-      <c r="M3" s="9">
-        <f>K3</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="42"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="42"/>
-      <c r="I4" s="1"/>
-      <c r="J4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K4">
-        <f>2.5+2.5+2.5</f>
-        <v>7.5</v>
-      </c>
-      <c r="N4" s="2">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C4" s="27"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="27"/>
+    </row>
+    <row r="5" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="42"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="20" t="s">
+      <c r="C5" s="27"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="J5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5">
-        <f>2.5+2</f>
-        <v>4.5</v>
-      </c>
-      <c r="M5" s="10">
-        <v>1.5</v>
-      </c>
-      <c r="N5" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="P5" s="11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="42" t="s">
+      <c r="D6" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="42" t="s">
+      <c r="E6" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="20"/>
-    </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="G6" s="26"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="27"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="20"/>
-    </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C7" s="28"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="26"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="27"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
       <c r="G8" s="5"/>
     </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="8" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="4"/>
       <c r="C11" s="3" t="s">
         <v>6</v>
@@ -2444,133 +2398,92 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C12" s="21" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="38" t="s">
+      <c r="E12" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="20" t="s">
+      <c r="F12" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K12" s="1">
-        <f>3+2.5+3+2</f>
-        <v>10.5</v>
-      </c>
-      <c r="M12" s="2">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="20"/>
-      <c r="J13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="1">
-        <v>3</v>
-      </c>
-      <c r="M13" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C13" s="22"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="26"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="23"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="17" t="s">
+      <c r="D14" s="20"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="40" t="s">
+      <c r="G14" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="J14" t="s">
-        <v>12</v>
-      </c>
-      <c r="K14">
-        <f>2+2.5+2+2</f>
-        <v>8.5</v>
-      </c>
-      <c r="N14" s="2">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="39"/>
-      <c r="D15" s="38" t="s">
+      <c r="C15" s="19"/>
+      <c r="D15" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="41"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="40"/>
-      <c r="J15" t="s">
-        <v>15</v>
-      </c>
-      <c r="K15">
-        <v>2</v>
-      </c>
-      <c r="N15" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="E15" s="33"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="32"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="39"/>
-      <c r="G16" s="40"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="19"/>
+      <c r="G16" s="32"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="23"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="20"/>
       <c r="G17" s="6"/>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B19" s="8" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B20" s="4"/>
       <c r="C20" s="3" t="s">
         <v>6</v>
@@ -2588,142 +2501,92 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="45" t="s">
+      <c r="D21" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="25" t="s">
         <v>61</v>
       </c>
       <c r="F21" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G21" s="27" t="s">
+      <c r="G21" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K21" s="1">
-        <f>3+3+2.5</f>
-        <v>8.5</v>
-      </c>
-      <c r="M21" s="2">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="39"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="27"/>
-      <c r="I22" s="1"/>
-      <c r="J22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K22">
-        <f>2.5+4</f>
-        <v>6.5</v>
-      </c>
-      <c r="N22" s="2">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="23" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C22" s="19"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="28"/>
+    </row>
+    <row r="23" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="23"/>
-      <c r="D23" s="21" t="s">
+      <c r="C23" s="20"/>
+      <c r="D23" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="45"/>
-      <c r="F23" s="17" t="s">
+      <c r="E23" s="25"/>
+      <c r="F23" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="20" t="s">
+      <c r="G23" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="J23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K23" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="M23" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="P23" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="22"/>
-      <c r="E24" s="20" t="s">
+      <c r="D24" s="24"/>
+      <c r="E24" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="18"/>
-      <c r="G24" s="20"/>
-      <c r="J24" t="s">
-        <v>31</v>
-      </c>
-      <c r="K24">
-        <v>4.5</v>
-      </c>
-      <c r="N24" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="P24" s="1"/>
-    </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="F24" s="17"/>
+      <c r="G24" s="26"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="20"/>
-      <c r="P25" s="1"/>
-    </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C25" s="17"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="26"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="19"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="6"/>
-      <c r="P26" s="1"/>
-    </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="P27" s="1"/>
-    </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B28" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="P28" s="1"/>
-    </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B29" s="4"/>
       <c r="C29" s="3" t="s">
         <v>6</v>
@@ -2740,9 +2603,8 @@
       <c r="G29" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="P29" s="1"/>
-    </row>
-    <row r="30" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="3" t="s">
         <v>0</v>
       </c>
@@ -2752,133 +2614,82 @@
       <c r="D30" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E30" s="17" t="s">
+      <c r="E30" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="27" t="s">
+      <c r="F30" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K30" s="1">
-        <f>2.5+2.5+2+3</f>
-        <v>10</v>
-      </c>
-      <c r="M30" s="2">
-        <v>10</v>
-      </c>
-      <c r="P30" s="1"/>
-    </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B31" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="27"/>
-      <c r="J31" t="s">
-        <v>12</v>
-      </c>
-      <c r="K31">
-        <f>2.5+2.5+2</f>
-        <v>7</v>
-      </c>
-      <c r="N31" s="2">
-        <v>7</v>
-      </c>
-      <c r="P31" s="1"/>
-    </row>
-    <row r="32" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C31" s="37"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="28"/>
+    </row>
+    <row r="32" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="32" t="s">
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="35" t="s">
+      <c r="F32" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="20" t="s">
+      <c r="G32" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="J32" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K32" s="1">
-        <v>2</v>
-      </c>
-      <c r="M32" s="10">
-        <v>2</v>
-      </c>
-      <c r="P32" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="33"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="20"/>
-      <c r="J33" t="s">
-        <v>31</v>
-      </c>
-      <c r="K33" s="1">
-        <v>5</v>
-      </c>
-      <c r="N33" s="2">
-        <v>5</v>
-      </c>
-      <c r="P33" s="1"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="E33" s="39"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="26"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="20"/>
-      <c r="P34" s="1"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="26"/>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="37"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="43"/>
       <c r="G35" s="6"/>
-      <c r="P35" s="1"/>
-    </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="P36" s="1"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B37" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="P37" s="1"/>
-    </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B38" s="4"/>
       <c r="C38" s="3" t="s">
         <v>6</v>
@@ -2895,254 +2706,139 @@
       <c r="G38" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="P38" s="1"/>
-    </row>
-    <row r="39" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="39" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="20" t="s">
+      <c r="C39" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="20" t="s">
+      <c r="D39" s="26" t="s">
         <v>13</v>
       </c>
       <c r="E39" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F39" s="20" t="s">
+      <c r="F39" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="G39" s="24" t="s">
+      <c r="G39" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K39" s="1">
-        <v>3</v>
-      </c>
-      <c r="M39" s="2">
-        <v>3</v>
-      </c>
-      <c r="P39" s="1"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B40" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="20"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="28"/>
-      <c r="I40" s="1"/>
-      <c r="J40" t="s">
-        <v>12</v>
-      </c>
-      <c r="K40">
-        <v>2.5</v>
-      </c>
-      <c r="N40" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="P40" s="1"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C40" s="26"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="37"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="35"/>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="21" t="s">
+      <c r="C41" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="20"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="28"/>
-      <c r="I41" s="1"/>
-      <c r="J41" t="s">
-        <v>15</v>
-      </c>
-      <c r="K41">
-        <v>18.5</v>
-      </c>
-      <c r="M41" s="10"/>
-      <c r="N41" s="2">
-        <v>10.5</v>
-      </c>
-      <c r="O41" s="12">
-        <v>8</v>
-      </c>
-      <c r="P41" s="13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="D41" s="26"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="35"/>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="22"/>
-      <c r="D42" s="24" t="s">
+      <c r="C42" s="24"/>
+      <c r="D42" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="E42" s="24" t="s">
+      <c r="E42" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="24" t="s">
+      <c r="F42" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="G42" s="28"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="G42" s="35"/>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="22"/>
-      <c r="D43" s="25"/>
-      <c r="E43" s="25"/>
-      <c r="F43" s="25"/>
-      <c r="G43" s="29"/>
-      <c r="K43" s="1">
-        <f>SUM(K3:K41)</f>
-        <v>120</v>
-      </c>
-      <c r="L43" s="1"/>
-      <c r="M43" s="9">
-        <f>SUM(M3:M41)</f>
-        <v>54</v>
-      </c>
-      <c r="N43" s="9">
-        <f>SUM(N3:N41)</f>
-        <v>58.5</v>
-      </c>
-      <c r="O43" s="12">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C43" s="24"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="36"/>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="23"/>
-      <c r="D44" s="26"/>
-      <c r="E44" s="26"/>
-      <c r="F44" s="26"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="45"/>
+      <c r="E44" s="45"/>
+      <c r="F44" s="45"/>
       <c r="G44" s="6"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="K46">
-        <f>5*4*5</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="K47">
-        <f>4*5</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="K48">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="50" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J50" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K50" s="1">
-        <f>K3+K12</f>
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="51" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J51" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K51" s="1">
-        <f>K13+K21+K30+K39</f>
-        <v>24.5</v>
-      </c>
-    </row>
-    <row r="52" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J52" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K52" s="1">
-        <f>K4+K14+K22+K31+K40</f>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="53" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J53" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K53" s="1">
-        <f>K5+K15+K23+K24+K32+K33+K41</f>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="54" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="K54">
-        <f>SUM(K50:K53)</f>
-        <v>120</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="49">
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="F39:F41"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E23"/>
     <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="D23:D26"/>
     <mergeCell ref="F23:F26"/>
-    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="G23:G25"/>
     <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="D23:D26"/>
-    <mergeCell ref="E21:E23"/>
     <mergeCell ref="E24:E26"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="G5:G7"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="E6:E8"/>
     <mergeCell ref="F6:F8"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="F39:F41"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="F42:F44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="32" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="89" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3198,19 +2894,19 @@
       <c r="B3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="42" t="s">
+      <c r="D3" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="46" t="s">
+      <c r="F3" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="53" t="s">
         <v>62</v>
       </c>
       <c r="I3" s="1"/>
@@ -3230,11 +2926,11 @@
       <c r="B4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="47"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="54"/>
       <c r="I4" s="1"/>
       <c r="J4" t="s">
         <v>12</v>
@@ -3251,11 +2947,11 @@
       <c r="B5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="46" t="s">
+      <c r="C5" s="28"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="53" t="s">
         <v>63</v>
       </c>
       <c r="J5" t="s">
@@ -3279,38 +2975,38 @@
       <c r="B6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="C6" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="42" t="s">
+      <c r="D6" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="42" t="s">
+      <c r="E6" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="48"/>
+      <c r="G6" s="55"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="47"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="54"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.35">
@@ -3340,19 +3036,19 @@
       <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C12" s="21" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="38" t="s">
+      <c r="E12" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="20" t="s">
+      <c r="F12" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="26" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="1"/>
@@ -3371,11 +3067,11 @@
       <c r="B13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="20"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="26"/>
       <c r="J13" s="1" t="s">
         <v>14</v>
       </c>
@@ -3390,15 +3086,15 @@
       <c r="B14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="23"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="17" t="s">
+      <c r="D14" s="20"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="40" t="s">
+      <c r="G14" s="32" t="s">
         <v>23</v>
       </c>
       <c r="J14" t="s">
@@ -3416,13 +3112,13 @@
       <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="39"/>
-      <c r="D15" s="38" t="s">
+      <c r="C15" s="19"/>
+      <c r="D15" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="41"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="40"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="32"/>
       <c r="J15" t="s">
         <v>15</v>
       </c>
@@ -3437,13 +3133,13 @@
       <c r="B16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="39"/>
-      <c r="G16" s="40"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="19"/>
+      <c r="G16" s="32"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
@@ -3451,10 +3147,10 @@
       <c r="B17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="23"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="20"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.35">
@@ -3484,19 +3180,19 @@
       <c r="B21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="52" t="s">
+      <c r="C21" s="46" t="s">
         <v>17</v>
       </c>
       <c r="D21" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E21" s="45" t="s">
+      <c r="E21" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="27" t="s">
+      <c r="F21" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="28" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="1"/>
@@ -3515,11 +3211,11 @@
       <c r="B22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="53"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="27"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="28"/>
       <c r="I22" s="1"/>
       <c r="J22" t="s">
         <v>12</v>
@@ -3536,13 +3232,13 @@
       <c r="B23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="54"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="21" t="s">
+      <c r="C23" s="48"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="20" t="s">
+      <c r="G23" s="26" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -3562,15 +3258,15 @@
       <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="54"/>
-      <c r="D24" s="17" t="s">
+      <c r="C24" s="48"/>
+      <c r="D24" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="20" t="s">
+      <c r="E24" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="22"/>
-      <c r="G24" s="20"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="26"/>
       <c r="J24" t="s">
         <v>31</v>
       </c>
@@ -3586,21 +3282,21 @@
       <c r="B25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="54"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="20"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="26"/>
       <c r="O25" s="1"/>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="55"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="23"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="20"/>
       <c r="G26" s="6"/>
       <c r="O26" s="1"/>
     </row>
@@ -3642,13 +3338,13 @@
       <c r="D30" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E30" s="17" t="s">
+      <c r="E30" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="27" t="s">
+      <c r="F30" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="28" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="1"/>
@@ -3668,11 +3364,11 @@
       <c r="B31" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="27"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="28"/>
       <c r="J31" t="s">
         <v>12</v>
       </c>
@@ -3689,17 +3385,17 @@
       <c r="B32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="16"/>
-      <c r="E32" s="32" t="s">
+      <c r="D32" s="15"/>
+      <c r="E32" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="35" t="s">
+      <c r="F32" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="20" t="s">
+      <c r="G32" s="26" t="s">
         <v>22</v>
       </c>
       <c r="J32" s="1" t="s">
@@ -3719,13 +3415,13 @@
       <c r="B33" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="18"/>
-      <c r="D33" s="17" t="s">
+      <c r="C33" s="17"/>
+      <c r="D33" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="33"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="20"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="26"/>
       <c r="J33" t="s">
         <v>31</v>
       </c>
@@ -3741,21 +3437,21 @@
       <c r="B34" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="20"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="26"/>
       <c r="O34" s="1"/>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="37"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="43"/>
       <c r="G35" s="6"/>
       <c r="O35" s="1"/>
     </row>
@@ -3791,19 +3487,19 @@
       <c r="B39" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="20" t="s">
+      <c r="C39" s="26" t="s">
         <v>13</v>
       </c>
       <c r="D39" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E39" s="45" t="s">
+      <c r="E39" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="24" t="s">
+      <c r="F39" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="49" t="s">
+      <c r="G39" s="50" t="s">
         <v>16</v>
       </c>
       <c r="I39" s="1"/>
@@ -3823,11 +3519,11 @@
       <c r="B40" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="20"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="45"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="50"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="37"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="51"/>
       <c r="I40" s="1"/>
       <c r="J40" t="s">
         <v>12</v>
@@ -3844,13 +3540,13 @@
       <c r="B41" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="21" t="s">
+      <c r="C41" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="16"/>
-      <c r="E41" s="45"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="50"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="35"/>
+      <c r="G41" s="51"/>
       <c r="I41" s="1"/>
       <c r="J41" t="s">
         <v>15</v>
@@ -3873,25 +3569,25 @@
       <c r="B42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="22"/>
-      <c r="D42" s="17" t="s">
+      <c r="C42" s="24"/>
+      <c r="D42" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="20" t="s">
+      <c r="E42" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="28"/>
-      <c r="G42" s="50"/>
+      <c r="F42" s="35"/>
+      <c r="G42" s="51"/>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C43" s="22"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="51"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="35"/>
+      <c r="G43" s="52"/>
       <c r="K43" s="1">
         <f>SUM(K3:K41)</f>
         <v>111</v>
@@ -3910,10 +3606,901 @@
       <c r="B44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="23"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="29"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="36"/>
+      <c r="G44" s="6"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K46">
+        <f>5*4*5</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K47">
+        <f>4*5</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K48">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="K49">
+        <f>120-5-4</f>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J50" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K50" s="1">
+        <f>K3+K12</f>
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="51" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J51" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K51" s="1">
+        <f>K13+K21+K30+K39</f>
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="52" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J52" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K52" s="1">
+        <f>K4+K14+K22+K31+K40</f>
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="53" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J53" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K53" s="1">
+        <f>K5+K15+K23+K24+K32+K33+K41</f>
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="54" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="K54">
+        <f>SUM(K50:K53)</f>
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="47">
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C21:C26"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B72F34B-8139-4D0E-8882-03145DDD5E1F}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:O54"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="2" customWidth="1"/>
+    <col min="2" max="2" width="10.90625" style="2"/>
+    <col min="3" max="4" width="12.6328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.7265625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="4.36328125" customWidth="1"/>
+    <col min="10" max="10" width="15.7265625" customWidth="1"/>
+    <col min="13" max="14" width="10.90625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B1" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B2" s="4"/>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="1">
+        <f>2.5+2.5+2.5+2.5+2</f>
+        <v>12</v>
+      </c>
+      <c r="M3" s="9">
+        <f>K3</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="28"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="27"/>
+      <c r="I4" s="1"/>
+      <c r="J4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4">
+        <f>2.5+2.5+2.5</f>
+        <v>7.5</v>
+      </c>
+      <c r="N4" s="2">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="28"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5">
+        <f>2.5+2</f>
+        <v>4.5</v>
+      </c>
+      <c r="M5" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="N5" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="26"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="26"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="5"/>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B10" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B11" s="4"/>
+      <c r="C11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" s="1">
+        <f>3+2.5+3+2</f>
+        <v>10.5</v>
+      </c>
+      <c r="M12" s="2">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="22"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="26"/>
+      <c r="J13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" s="1">
+        <v>3</v>
+      </c>
+      <c r="M13" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="20"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14">
+        <f>2+2.5+2+2</f>
+        <v>8.5</v>
+      </c>
+      <c r="N14" s="2">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="33"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="32"/>
+      <c r="J15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="N15" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="19"/>
+      <c r="G16" s="32"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="6"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B19" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B20" s="4"/>
+      <c r="C20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K21" s="1">
+        <f>2.5+3</f>
+        <v>5.5</v>
+      </c>
+      <c r="M21" s="2">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="47"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="28"/>
+      <c r="I22" s="1"/>
+      <c r="J22" t="s">
+        <v>12</v>
+      </c>
+      <c r="K22">
+        <f>2.5+2</f>
+        <v>4.5</v>
+      </c>
+      <c r="N22" s="2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="48"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K23" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="M23" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="O23" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="48"/>
+      <c r="D24" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="24"/>
+      <c r="G24" s="26"/>
+      <c r="J24" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24">
+        <v>4.5</v>
+      </c>
+      <c r="N24" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O24" s="1"/>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B25" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="48"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="26"/>
+      <c r="O25" s="1"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="49"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="6"/>
+      <c r="O26" s="1"/>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="O27" s="1"/>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B28" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="O28" s="1"/>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B29" s="4"/>
+      <c r="C29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O29" s="1"/>
+    </row>
+    <row r="30" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K30" s="1">
+        <f>3+2.5+2+3</f>
+        <v>10.5</v>
+      </c>
+      <c r="M30" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="O30" s="1"/>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="15"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="28"/>
+      <c r="J31" t="s">
+        <v>12</v>
+      </c>
+      <c r="K31">
+        <f>2+2.5+2</f>
+        <v>6.5</v>
+      </c>
+      <c r="N31" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="O31" s="1"/>
+    </row>
+    <row r="32" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="15"/>
+      <c r="E32" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K32" s="1">
+        <v>2</v>
+      </c>
+      <c r="M32" s="10">
+        <v>2</v>
+      </c>
+      <c r="O32" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="17"/>
+      <c r="D33" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="39"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="26"/>
+      <c r="J33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K33" s="1">
+        <v>5</v>
+      </c>
+      <c r="N33" s="2">
+        <v>5</v>
+      </c>
+      <c r="O33" s="1"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B34" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="26"/>
+      <c r="O34" s="1"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="43"/>
+      <c r="G35" s="6"/>
+      <c r="O35" s="1"/>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="O36" s="1"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B37" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O37" s="1"/>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B38" s="4"/>
+      <c r="C38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O38" s="1"/>
+    </row>
+    <row r="39" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K39" s="1">
+        <f>3+2.5</f>
+        <v>5.5</v>
+      </c>
+      <c r="M39" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="O39" s="1"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="26"/>
+      <c r="D40" s="37"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="51"/>
+      <c r="I40" s="1"/>
+      <c r="J40" t="s">
+        <v>12</v>
+      </c>
+      <c r="K40">
+        <v>2.5</v>
+      </c>
+      <c r="N40" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="O40" s="1"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="15"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="35"/>
+      <c r="G41" s="51"/>
+      <c r="I41" s="1"/>
+      <c r="J41" t="s">
+        <v>15</v>
+      </c>
+      <c r="K41">
+        <v>12</v>
+      </c>
+      <c r="M41" s="10">
+        <f>4.5</f>
+        <v>4.5</v>
+      </c>
+      <c r="N41" s="2">
+        <f>2+2.5+5</f>
+        <v>9.5</v>
+      </c>
+      <c r="O41" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="24"/>
+      <c r="D42" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="35"/>
+      <c r="G42" s="51"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" s="24"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="35"/>
+      <c r="G43" s="52"/>
+      <c r="K43" s="1">
+        <f>SUM(K3:K41)</f>
+        <v>111</v>
+      </c>
+      <c r="L43" s="1"/>
+      <c r="M43" s="9">
+        <f>SUM(M3:M41)</f>
+        <v>59.5</v>
+      </c>
+      <c r="N43" s="9">
+        <f>SUM(N3:N41)</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="20"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="36"/>
       <c r="G44" s="6"/>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.35">
@@ -4036,28 +4623,29 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B72F34B-8139-4D0E-8882-03145DDD5E1F}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1185C20-CB13-4526-80BC-F11E35C8CC5F}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:O54"/>
+  <dimension ref="B1:P54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="10.90625" style="2"/>
-    <col min="3" max="4" width="12.6328125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="14.54296875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.6328125" style="2" customWidth="1"/>
     <col min="5" max="5" width="16.7265625" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.1796875" style="2" customWidth="1"/>
     <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
     <col min="8" max="8" width="4.36328125" customWidth="1"/>
     <col min="10" max="10" width="15.7265625" customWidth="1"/>
-    <col min="13" max="14" width="10.90625" style="2"/>
+    <col min="13" max="15" width="10.90625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B1" s="8" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="M1" s="9" t="s">
         <v>24</v>
@@ -4065,8 +4653,11 @@
       <c r="N1" s="9" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="O1" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B2" s="4"/>
       <c r="C2" s="3" t="s">
         <v>6</v>
@@ -4084,23 +4675,23 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="42" t="s">
+      <c r="F3" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="27" t="s">
         <v>18</v>
       </c>
       <c r="I3" s="1"/>
@@ -4116,15 +4707,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="27"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="42"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="27"/>
       <c r="I4" s="1"/>
       <c r="J4" t="s">
         <v>12</v>
@@ -4137,15 +4728,15 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="5" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="27"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="20" t="s">
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="26" t="s">
         <v>22</v>
       </c>
       <c r="J5" t="s">
@@ -4161,54 +4752,54 @@
       <c r="N5" s="2">
         <v>4.5</v>
       </c>
-      <c r="O5" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="P5" s="11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="C6" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="42" t="s">
+      <c r="E6" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="20"/>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="G6" s="26"/>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="20"/>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="C7" s="28"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="26"/>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
       <c r="G8" s="5"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B10" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B11" s="4"/>
       <c r="C11" s="3" t="s">
         <v>6</v>
@@ -4226,23 +4817,23 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C12" s="21" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="38" t="s">
+      <c r="E12" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="20" t="s">
+      <c r="F12" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="26" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="1"/>
@@ -4257,15 +4848,15 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="20"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="26"/>
       <c r="J13" s="1" t="s">
         <v>14</v>
       </c>
@@ -4276,19 +4867,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="23"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="17" t="s">
+      <c r="D14" s="20"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="40" t="s">
+      <c r="G14" s="32" t="s">
         <v>23</v>
       </c>
       <c r="J14" t="s">
@@ -4302,17 +4893,17 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="39"/>
-      <c r="D15" s="38" t="s">
+      <c r="C15" s="19"/>
+      <c r="D15" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="41"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="40"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="32"/>
       <c r="J15" t="s">
         <v>15</v>
       </c>
@@ -4323,36 +4914,36 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="39"/>
-      <c r="G16" s="40"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="19"/>
+      <c r="G16" s="32"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="23"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="20"/>
       <c r="G17" s="6"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B19" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B20" s="4"/>
       <c r="C20" s="3" t="s">
         <v>6</v>
@@ -4370,23 +4961,23 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="45" t="s">
+      <c r="C21" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="27" t="s">
+      <c r="F21" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="28" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="1"/>
@@ -4394,45 +4985,47 @@
         <v>14</v>
       </c>
       <c r="K21" s="1">
-        <f>2.5+3</f>
-        <v>5.5</v>
+        <f>3+3+2.5</f>
+        <v>8.5</v>
       </c>
       <c r="M21" s="2">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="53"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="27"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="28"/>
       <c r="I22" s="1"/>
       <c r="J22" t="s">
         <v>12</v>
       </c>
       <c r="K22">
-        <f>2.5+2</f>
-        <v>4.5</v>
+        <f>2.5+4</f>
+        <v>6.5</v>
       </c>
       <c r="N22" s="2">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="23" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="54"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="21" t="s">
+      <c r="C23" s="20"/>
+      <c r="D23" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="20" t="s">
+      <c r="E23" s="25"/>
+      <c r="F23" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="26" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -4444,23 +5037,23 @@
       <c r="M23" s="10">
         <v>4.5</v>
       </c>
-      <c r="O23" s="11" t="s">
+      <c r="P23" s="11" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="54"/>
-      <c r="D24" s="17" t="s">
+      <c r="C24" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="20" t="s">
+      <c r="D24" s="24"/>
+      <c r="E24" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="22"/>
-      <c r="G24" s="20"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="26"/>
       <c r="J24" t="s">
         <v>31</v>
       </c>
@@ -4470,40 +5063,40 @@
       <c r="N24" s="2">
         <v>4.5</v>
       </c>
-      <c r="O24" s="1"/>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="54"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="20"/>
-      <c r="O25" s="1"/>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="C25" s="17"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="26"/>
+      <c r="P25" s="1"/>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="55"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="23"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="6"/>
-      <c r="O26" s="1"/>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="O27" s="1"/>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="P26" s="1"/>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="P27" s="1"/>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B28" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="O28" s="1"/>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B29" s="4"/>
       <c r="C29" s="3" t="s">
         <v>6</v>
@@ -4520,9 +5113,9 @@
       <c r="G29" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="O29" s="1"/>
-    </row>
-    <row r="30" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P29" s="1"/>
+    </row>
+    <row r="30" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="3" t="s">
         <v>0</v>
       </c>
@@ -4532,13 +5125,13 @@
       <c r="D30" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E30" s="17" t="s">
+      <c r="E30" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="27" t="s">
+      <c r="F30" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="28" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="1"/>
@@ -4546,50 +5139,48 @@
         <v>14</v>
       </c>
       <c r="K30" s="1">
-        <f>3+2.5+2+3</f>
-        <v>10.5</v>
+        <f>2.5+2.5+2+3</f>
+        <v>10</v>
       </c>
       <c r="M30" s="2">
-        <v>10.5</v>
-      </c>
-      <c r="O30" s="1"/>
-    </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B31" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="27"/>
+      <c r="C31" s="37"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="28"/>
       <c r="J31" t="s">
         <v>12</v>
       </c>
       <c r="K31">
-        <f>2+2.5+2</f>
-        <v>6.5</v>
+        <f>2.5+2.5+2</f>
+        <v>7</v>
       </c>
       <c r="N31" s="2">
-        <v>6.5</v>
-      </c>
-      <c r="O31" s="1"/>
-    </row>
-    <row r="32" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="16"/>
-      <c r="E32" s="32" t="s">
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="35" t="s">
+      <c r="F32" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="20" t="s">
+      <c r="G32" s="26" t="s">
         <v>22</v>
       </c>
       <c r="J32" s="1" t="s">
@@ -4601,21 +5192,23 @@
       <c r="M32" s="10">
         <v>2</v>
       </c>
-      <c r="O32" s="11" t="s">
+      <c r="P32" s="11" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="18"/>
-      <c r="D33" s="17" t="s">
+      <c r="C33" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="33"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="20"/>
+      <c r="D33" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="39"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="26"/>
       <c r="J33" t="s">
         <v>31</v>
       </c>
@@ -4625,40 +5218,40 @@
       <c r="N33" s="2">
         <v>5</v>
       </c>
-      <c r="O33" s="1"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="P33" s="1"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="20"/>
-      <c r="O34" s="1"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="26"/>
+      <c r="P34" s="1"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="37"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="43"/>
       <c r="G35" s="6"/>
-      <c r="O35" s="1"/>
-    </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="O36" s="1"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="P35" s="1"/>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="P36" s="1"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B37" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O37" s="1"/>
-    </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
+        <v>56</v>
+      </c>
+      <c r="P37" s="1"/>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B38" s="4"/>
       <c r="C38" s="3" t="s">
         <v>6</v>
@@ -4675,49 +5268,48 @@
       <c r="G38" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="O38" s="1"/>
-    </row>
-    <row r="39" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P38" s="1"/>
+    </row>
+    <row r="39" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="20" t="s">
+      <c r="C39" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="45" t="s">
+      <c r="D39" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="G39" s="49" t="s">
-        <v>16</v>
+      <c r="E39" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="34" t="s">
+        <v>57</v>
       </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1" t="s">
         <v>14</v>
       </c>
       <c r="K39" s="1">
-        <f>3+2.5</f>
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="M39" s="2">
-        <v>5.5</v>
-      </c>
-      <c r="O39" s="1"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+      <c r="P39" s="1"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B40" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="20"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="45"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="50"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="37"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="35"/>
       <c r="I40" s="1"/>
       <c r="J40" t="s">
         <v>12</v>
@@ -4728,106 +5320,104 @@
       <c r="N40" s="2">
         <v>2.5</v>
       </c>
-      <c r="O40" s="1"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="P40" s="1"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="21" t="s">
+      <c r="C41" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="16"/>
-      <c r="E41" s="45"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="50"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="35"/>
       <c r="I41" s="1"/>
       <c r="J41" t="s">
         <v>15</v>
       </c>
       <c r="K41">
-        <v>12</v>
-      </c>
-      <c r="M41" s="10">
-        <f>4.5</f>
-        <v>4.5</v>
-      </c>
+        <v>18.5</v>
+      </c>
+      <c r="M41" s="10"/>
       <c r="N41" s="2">
-        <f>2+2.5+5</f>
-        <v>9.5</v>
-      </c>
-      <c r="O41" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
+        <v>10.5</v>
+      </c>
+      <c r="O41" s="12">
+        <v>8</v>
+      </c>
+      <c r="P41" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="22"/>
-      <c r="D42" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" s="20" t="s">
+      <c r="C42" s="24"/>
+      <c r="D42" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="28"/>
-      <c r="G42" s="50"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="E42" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" s="35"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="22"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="51"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="36"/>
       <c r="K43" s="1">
         <f>SUM(K3:K41)</f>
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="9">
         <f>SUM(M3:M41)</f>
-        <v>59.5</v>
+        <v>54</v>
       </c>
       <c r="N43" s="9">
         <f>SUM(N3:N41)</f>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
+        <v>58.5</v>
+      </c>
+      <c r="O43" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="23"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="29"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="45"/>
+      <c r="E44" s="45"/>
+      <c r="F44" s="45"/>
       <c r="G44" s="6"/>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.35">
       <c r="K46">
         <f>5*4*5</f>
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.35">
       <c r="K47">
         <f>4*5</f>
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.35">
       <c r="K48">
         <v>120</v>
-      </c>
-    </row>
-    <row r="49" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="K49">
-        <f>120-5-4</f>
-        <v>111</v>
       </c>
     </row>
     <row r="50" spans="10:11" x14ac:dyDescent="0.35">
@@ -4854,7 +5444,7 @@
       </c>
       <c r="K52" s="1">
         <f>K4+K14+K22+K31+K40</f>
-        <v>29.5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53" spans="10:11" x14ac:dyDescent="0.35">
@@ -4863,66 +5453,68 @@
       </c>
       <c r="K53" s="1">
         <f>K5+K15+K23+K24+K32+K33+K41</f>
-        <v>34.5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="54" spans="10:11" x14ac:dyDescent="0.35">
       <c r="K54">
         <f>SUM(K50:K53)</f>
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="47">
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
+  <mergeCells count="49">
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="F39:F41"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="G5:G7"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="E6:E8"/>
     <mergeCell ref="F6:F8"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C21:C26"/>
-    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="D23:D26"/>
     <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="D24:D26"/>
     <mergeCell ref="E24:E26"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Horarios/HorarioWAN_2026.xlsx
+++ b/Horarios/HorarioWAN_2026.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="52" documentId="8_{FC23BDE9-CBF9-4CD9-B661-15FDB57BE38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AAD2FCD-CB72-4956-B4C6-84AD9BC4E68D}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
   </bookViews>
   <sheets>
     <sheet name="WAN_201" sheetId="5" r:id="rId1"/>
@@ -648,64 +648,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -717,7 +669,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -738,11 +717,50 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -755,24 +773,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -794,10 +794,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1138,19 +1134,19 @@
       <c r="B3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="27" t="s">
+      <c r="D3" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="53" t="s">
+      <c r="F3" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="46" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1158,21 +1154,21 @@
       <c r="B4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="28"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="54"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="47"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="53" t="s">
+      <c r="C5" s="30"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="46" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1180,38 +1176,38 @@
       <c r="B6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="27" t="s">
+      <c r="E6" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="55"/>
+      <c r="G6" s="48"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="54"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="47"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
@@ -1241,19 +1237,19 @@
       <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="31" t="s">
+      <c r="C12" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="26" t="s">
+      <c r="F12" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1261,25 +1257,25 @@
       <c r="B13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="26"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="14"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="16" t="s">
+      <c r="D14" s="23"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="42" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1287,34 +1283,34 @@
       <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="31" t="s">
+      <c r="C15" s="38"/>
+      <c r="D15" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="33"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="32"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="42"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="19"/>
-      <c r="G16" s="32"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="38"/>
+      <c r="G16" s="42"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="20"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="23"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.35">
@@ -1344,19 +1340,19 @@
       <c r="B21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="25" t="s">
+      <c r="C21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="46" t="s">
+      <c r="E21" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="28" t="s">
+      <c r="F21" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="30" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1364,23 +1360,23 @@
       <c r="B22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="19"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="28"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="30"/>
     </row>
     <row r="23" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="20"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="23" t="s">
+      <c r="C23" s="23"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="26" t="s">
+      <c r="G23" s="14" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1388,34 +1384,34 @@
       <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="26" t="s">
+      <c r="D24" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E24" s="48"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="26"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="14"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="26"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="14"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="20"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="55"/>
+      <c r="F26" s="23"/>
       <c r="G26" s="6"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
@@ -1445,19 +1441,19 @@
       <c r="B30" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="16" t="s">
+      <c r="C30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="28" t="s">
+      <c r="F30" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="30" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1465,27 +1461,27 @@
       <c r="B31" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="15"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="28"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="30"/>
     </row>
     <row r="32" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="15"/>
-      <c r="E32" s="38" t="s">
+      <c r="D32" s="17"/>
+      <c r="E32" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="41" t="s">
+      <c r="F32" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="26" t="s">
+      <c r="G32" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1493,32 +1489,32 @@
       <c r="B33" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="17"/>
-      <c r="D33" s="16" t="s">
+      <c r="C33" s="37"/>
+      <c r="D33" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="39"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="26"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="14"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="26"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="14"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="43"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="36"/>
       <c r="G35" s="6"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.35">
@@ -1548,19 +1544,19 @@
       <c r="B39" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="26" t="s">
+      <c r="C39" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="25" t="s">
+      <c r="D39" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="16" t="s">
+      <c r="E39" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="F39" s="34" t="s">
+      <c r="F39" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="50" t="s">
+      <c r="G39" s="49" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1568,60 +1564,91 @@
       <c r="B40" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="26"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="51"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="37"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="50"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C41" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="25"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="35"/>
-      <c r="G41" s="51"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="50"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="24"/>
-      <c r="D42" s="26" t="s">
+      <c r="C42" s="22"/>
+      <c r="D42" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E42" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F42" s="35"/>
-      <c r="G42" s="51"/>
+      <c r="E42" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F42" s="19"/>
+      <c r="G42" s="50"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C43" s="24"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="37"/>
-      <c r="F43" s="35"/>
-      <c r="G43" s="52"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="51"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="20"/>
-      <c r="D44" s="26"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="36"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="20"/>
       <c r="G44" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="E21:E26"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
     <mergeCell ref="C21:C23"/>
     <mergeCell ref="C24:C26"/>
     <mergeCell ref="D24:D26"/>
@@ -1638,37 +1665,6 @@
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="D12:D14"/>
     <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="E21:E26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="94" orientation="portrait" r:id="rId1"/>
@@ -1718,19 +1714,19 @@
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="27" t="s">
+      <c r="D3" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="27" t="s">
+      <c r="F3" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="43" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1738,21 +1734,21 @@
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="28"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="27"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="43"/>
     </row>
     <row r="5" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="26" t="s">
+      <c r="C5" s="30"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1760,38 +1756,38 @@
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="27" t="s">
+      <c r="E6" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="26"/>
+      <c r="G6" s="14"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="26"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="14"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
@@ -1821,19 +1817,19 @@
       <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="31" t="s">
+      <c r="C12" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="26" t="s">
+      <c r="F12" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1841,25 +1837,25 @@
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="26"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="14"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="16" t="s">
+      <c r="D14" s="23"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="42" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1867,34 +1863,34 @@
       <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="31" t="s">
+      <c r="C15" s="38"/>
+      <c r="D15" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="33"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="32"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="42"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="19"/>
-      <c r="G16" s="32"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="38"/>
+      <c r="G16" s="42"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="20"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="23"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.35">
@@ -1924,19 +1920,19 @@
       <c r="B21" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="25" t="s">
+      <c r="C21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="46" t="s">
+      <c r="E21" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="28" t="s">
+      <c r="F21" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="30" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1944,23 +1940,23 @@
       <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="19"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="28"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="30"/>
     </row>
     <row r="23" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="20"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="23" t="s">
+      <c r="C23" s="23"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="26" t="s">
+      <c r="G23" s="14" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1968,34 +1964,34 @@
       <c r="B24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="26" t="s">
+      <c r="D24" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E24" s="48"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="26"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="14"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="26"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="14"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="20"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="55"/>
+      <c r="F26" s="23"/>
       <c r="G26" s="6"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
@@ -2025,19 +2021,19 @@
       <c r="B30" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="16" t="s">
+      <c r="C30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="28" t="s">
+      <c r="F30" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="30" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2045,27 +2041,27 @@
       <c r="B31" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="15"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="28"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="30"/>
     </row>
     <row r="32" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="15"/>
-      <c r="E32" s="38" t="s">
+      <c r="D32" s="17"/>
+      <c r="E32" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="41" t="s">
+      <c r="F32" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="26" t="s">
+      <c r="G32" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2073,32 +2069,32 @@
       <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="17"/>
-      <c r="D33" s="16" t="s">
+      <c r="C33" s="37"/>
+      <c r="D33" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="39"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="26"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="14"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="26"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="14"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="43"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="36"/>
       <c r="G35" s="6"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.35">
@@ -2128,19 +2124,19 @@
       <c r="B39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="26" t="s">
+      <c r="C39" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="25" t="s">
+      <c r="D39" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="16" t="s">
+      <c r="E39" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="F39" s="34" t="s">
+      <c r="F39" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="50" t="s">
+      <c r="G39" s="49" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2148,87 +2144,70 @@
       <c r="B40" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="26"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="51"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="37"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="50"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C41" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="25"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="35"/>
-      <c r="G41" s="51"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="50"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="24"/>
-      <c r="D42" s="26" t="s">
+      <c r="C42" s="22"/>
+      <c r="D42" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E42" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F42" s="35"/>
-      <c r="G42" s="51"/>
+      <c r="E42" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F42" s="19"/>
+      <c r="G42" s="50"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="24"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="37"/>
-      <c r="F43" s="35"/>
-      <c r="G43" s="52"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="51"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="20"/>
-      <c r="D44" s="26"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="36"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="20"/>
       <c r="G44" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E26"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
     <mergeCell ref="F12:F13"/>
     <mergeCell ref="G12:G13"/>
     <mergeCell ref="C14:C17"/>
@@ -2239,16 +2218,33 @@
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="D12:D14"/>
     <mergeCell ref="E12:E15"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E42:E44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="95" orientation="portrait" r:id="rId1"/>
@@ -2299,19 +2295,19 @@
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="27" t="s">
+      <c r="D3" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="27" t="s">
+      <c r="F3" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="43" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2319,21 +2315,21 @@
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="27"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="43"/>
     </row>
     <row r="5" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="26" t="s">
+      <c r="C5" s="43"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2341,38 +2337,38 @@
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="27" t="s">
+      <c r="E6" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="26"/>
+      <c r="G6" s="14"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="26"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="14"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
@@ -2402,19 +2398,19 @@
       <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="31" t="s">
+      <c r="C12" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="26" t="s">
+      <c r="F12" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2422,25 +2418,25 @@
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="26"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="14"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="16" t="s">
+      <c r="D14" s="23"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="42" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2448,34 +2444,34 @@
       <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="31" t="s">
+      <c r="C15" s="38"/>
+      <c r="D15" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="33"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="32"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="42"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="19"/>
-      <c r="G16" s="32"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="38"/>
+      <c r="G16" s="42"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="20"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="23"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.35">
@@ -2505,19 +2501,19 @@
       <c r="B21" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="25" t="s">
+      <c r="C21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="28" t="s">
+      <c r="F21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="30" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2525,25 +2521,25 @@
       <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="19"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="28"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="30"/>
     </row>
     <row r="23" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="20"/>
-      <c r="D23" s="23" t="s">
+      <c r="C23" s="23"/>
+      <c r="D23" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="25"/>
-      <c r="F23" s="16" t="s">
+      <c r="E23" s="39"/>
+      <c r="F23" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="26" t="s">
+      <c r="G23" s="14" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2551,34 +2547,34 @@
       <c r="B24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="24"/>
-      <c r="E24" s="26" t="s">
+      <c r="D24" s="22"/>
+      <c r="E24" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="17"/>
-      <c r="G24" s="26"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="14"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="26"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="14"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="18"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="27"/>
       <c r="G26" s="6"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
@@ -2608,19 +2604,19 @@
       <c r="B30" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="16" t="s">
+      <c r="C30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="28" t="s">
+      <c r="F30" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="30" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2628,25 +2624,25 @@
       <c r="B31" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="37"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="28"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="30"/>
     </row>
     <row r="32" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="38" t="s">
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="41" t="s">
+      <c r="F32" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="26" t="s">
+      <c r="G32" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2654,34 +2650,34 @@
       <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="16" t="s">
+      <c r="D33" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="39"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="26"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="14"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="26"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="14"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="43"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="36"/>
       <c r="G35" s="6"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.35">
@@ -2711,19 +2707,19 @@
       <c r="B39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="26" t="s">
+      <c r="C39" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="26" t="s">
+      <c r="D39" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F39" s="26" t="s">
+      <c r="E39" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G39" s="34" t="s">
+      <c r="G39" s="18" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2731,71 +2727,92 @@
       <c r="B40" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="37"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="35"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="19"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C41" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="26"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="35"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="19"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="24"/>
-      <c r="D42" s="34" t="s">
+      <c r="C42" s="22"/>
+      <c r="D42" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E42" s="34" t="s">
+      <c r="E42" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="34" t="s">
+      <c r="F42" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="G42" s="35"/>
+      <c r="G42" s="19"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="24"/>
-      <c r="D43" s="44"/>
-      <c r="E43" s="44"/>
-      <c r="F43" s="44"/>
-      <c r="G43" s="36"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="20"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="20"/>
-      <c r="D44" s="45"/>
-      <c r="E44" s="45"/>
-      <c r="F44" s="45"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="25"/>
+      <c r="F44" s="25"/>
       <c r="G44" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="F39:F41"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="D23:D26"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="E24:E26"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="D30:D32"/>
     <mergeCell ref="E30:E31"/>
@@ -2806,36 +2823,15 @@
     <mergeCell ref="G32:G34"/>
     <mergeCell ref="C33:C35"/>
     <mergeCell ref="D33:D35"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="D23:D26"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="F39:F41"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="F42:F44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="89" orientation="portrait" r:id="rId1"/>
@@ -2894,19 +2890,19 @@
       <c r="B3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="27" t="s">
+      <c r="D3" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="53" t="s">
+      <c r="F3" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="46" t="s">
         <v>62</v>
       </c>
       <c r="I3" s="1"/>
@@ -2926,11 +2922,11 @@
       <c r="B4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="28"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="54"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="47"/>
       <c r="I4" s="1"/>
       <c r="J4" t="s">
         <v>12</v>
@@ -2947,11 +2943,11 @@
       <c r="B5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="53" t="s">
+      <c r="C5" s="30"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="46" t="s">
         <v>63</v>
       </c>
       <c r="J5" t="s">
@@ -2975,38 +2971,38 @@
       <c r="B6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="27" t="s">
+      <c r="E6" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="55"/>
+      <c r="G6" s="48"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="54"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="47"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.35">
@@ -3036,19 +3032,19 @@
       <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="31" t="s">
+      <c r="C12" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="26" t="s">
+      <c r="F12" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="1"/>
@@ -3067,11 +3063,11 @@
       <c r="B13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="26"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="14"/>
       <c r="J13" s="1" t="s">
         <v>14</v>
       </c>
@@ -3086,15 +3082,15 @@
       <c r="B14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="16" t="s">
+      <c r="D14" s="23"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="42" t="s">
         <v>23</v>
       </c>
       <c r="J14" t="s">
@@ -3112,13 +3108,13 @@
       <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="31" t="s">
+      <c r="C15" s="38"/>
+      <c r="D15" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="33"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="32"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="42"/>
       <c r="J15" t="s">
         <v>15</v>
       </c>
@@ -3133,13 +3129,13 @@
       <c r="B16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="19"/>
-      <c r="G16" s="32"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="38"/>
+      <c r="G16" s="42"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
@@ -3147,10 +3143,10 @@
       <c r="B17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="20"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="23"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.35">
@@ -3180,19 +3176,19 @@
       <c r="B21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="46" t="s">
+      <c r="C21" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="25" t="s">
+      <c r="D21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="28" t="s">
+      <c r="F21" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="30" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="1"/>
@@ -3211,11 +3207,11 @@
       <c r="B22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="47"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="28"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="30"/>
       <c r="I22" s="1"/>
       <c r="J22" t="s">
         <v>12</v>
@@ -3232,13 +3228,13 @@
       <c r="B23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="48"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="23" t="s">
+      <c r="C23" s="54"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="26" t="s">
+      <c r="G23" s="14" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -3258,15 +3254,15 @@
       <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="48"/>
-      <c r="D24" s="16" t="s">
+      <c r="C24" s="54"/>
+      <c r="D24" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="26" t="s">
+      <c r="E24" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="24"/>
-      <c r="G24" s="26"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="14"/>
       <c r="J24" t="s">
         <v>31</v>
       </c>
@@ -3282,21 +3278,21 @@
       <c r="B25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="48"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="26"/>
+      <c r="C25" s="54"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="14"/>
       <c r="O25" s="1"/>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="49"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="20"/>
+      <c r="C26" s="55"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="23"/>
       <c r="G26" s="6"/>
       <c r="O26" s="1"/>
     </row>
@@ -3332,19 +3328,19 @@
       <c r="B30" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="16" t="s">
+      <c r="C30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="28" t="s">
+      <c r="F30" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="30" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="1"/>
@@ -3364,11 +3360,11 @@
       <c r="B31" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="15"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="28"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="30"/>
       <c r="J31" t="s">
         <v>12</v>
       </c>
@@ -3385,17 +3381,17 @@
       <c r="B32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="15"/>
-      <c r="E32" s="38" t="s">
+      <c r="D32" s="17"/>
+      <c r="E32" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="41" t="s">
+      <c r="F32" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="26" t="s">
+      <c r="G32" s="14" t="s">
         <v>22</v>
       </c>
       <c r="J32" s="1" t="s">
@@ -3415,13 +3411,13 @@
       <c r="B33" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="17"/>
-      <c r="D33" s="16" t="s">
+      <c r="C33" s="37"/>
+      <c r="D33" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="39"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="26"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="14"/>
       <c r="J33" t="s">
         <v>31</v>
       </c>
@@ -3437,21 +3433,21 @@
       <c r="B34" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="26"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="14"/>
       <c r="O34" s="1"/>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="43"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="36"/>
       <c r="G35" s="6"/>
       <c r="O35" s="1"/>
     </row>
@@ -3487,19 +3483,19 @@
       <c r="B39" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="26" t="s">
+      <c r="C39" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="25" t="s">
+      <c r="D39" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="34" t="s">
+      <c r="F39" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="50" t="s">
+      <c r="G39" s="49" t="s">
         <v>16</v>
       </c>
       <c r="I39" s="1"/>
@@ -3519,11 +3515,11 @@
       <c r="B40" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="26"/>
-      <c r="D40" s="37"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="51"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="39"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="50"/>
       <c r="I40" s="1"/>
       <c r="J40" t="s">
         <v>12</v>
@@ -3540,13 +3536,13 @@
       <c r="B41" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C41" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="15"/>
-      <c r="E41" s="25"/>
-      <c r="F41" s="35"/>
-      <c r="G41" s="51"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="39"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="50"/>
       <c r="I41" s="1"/>
       <c r="J41" t="s">
         <v>15</v>
@@ -3569,25 +3565,25 @@
       <c r="B42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="24"/>
-      <c r="D42" s="16" t="s">
+      <c r="C42" s="22"/>
+      <c r="D42" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="26" t="s">
+      <c r="E42" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="35"/>
-      <c r="G42" s="51"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="50"/>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C43" s="24"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="35"/>
-      <c r="G43" s="52"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="51"/>
       <c r="K43" s="1">
         <f>SUM(K3:K41)</f>
         <v>111</v>
@@ -3606,10 +3602,901 @@
       <c r="B44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="20"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="26"/>
-      <c r="F44" s="36"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="6"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K46">
+        <f>5*4*5</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K47">
+        <f>4*5</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K48">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="K49">
+        <f>120-5-4</f>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J50" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K50" s="1">
+        <f>K3+K12</f>
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="51" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J51" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K51" s="1">
+        <f>K13+K21+K30+K39</f>
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="52" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J52" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K52" s="1">
+        <f>K4+K14+K22+K31+K40</f>
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="53" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J53" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K53" s="1">
+        <f>K5+K15+K23+K24+K32+K33+K41</f>
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="54" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="K54">
+        <f>SUM(K50:K53)</f>
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="47">
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="C21:C26"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B72F34B-8139-4D0E-8882-03145DDD5E1F}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:O54"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="2" customWidth="1"/>
+    <col min="2" max="2" width="10.90625" style="2"/>
+    <col min="3" max="4" width="12.6328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.7265625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="4.36328125" customWidth="1"/>
+    <col min="10" max="10" width="15.7265625" customWidth="1"/>
+    <col min="13" max="14" width="10.90625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B1" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B2" s="4"/>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="1">
+        <f>2.5+2.5+2.5+2.5+2</f>
+        <v>12</v>
+      </c>
+      <c r="M3" s="9">
+        <f>K3</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="30"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="43"/>
+      <c r="I4" s="1"/>
+      <c r="J4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4">
+        <f>2.5+2.5+2.5</f>
+        <v>7.5</v>
+      </c>
+      <c r="N4" s="2">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="30"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5">
+        <f>2.5+2</f>
+        <v>4.5</v>
+      </c>
+      <c r="M5" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="N5" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="14"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="5"/>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B10" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B11" s="4"/>
+      <c r="C11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" s="1">
+        <f>3+2.5+3+2</f>
+        <v>10.5</v>
+      </c>
+      <c r="M12" s="2">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="29"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="14"/>
+      <c r="J13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" s="1">
+        <v>3</v>
+      </c>
+      <c r="M13" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="23"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14">
+        <f>2+2.5+2+2</f>
+        <v>8.5</v>
+      </c>
+      <c r="N14" s="2">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="38"/>
+      <c r="D15" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="41"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="42"/>
+      <c r="J15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="N15" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="38"/>
+      <c r="G16" s="42"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="6"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B19" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B20" s="4"/>
+      <c r="C20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K21" s="1">
+        <f>2.5+3</f>
+        <v>5.5</v>
+      </c>
+      <c r="M21" s="2">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="53"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="30"/>
+      <c r="I22" s="1"/>
+      <c r="J22" t="s">
+        <v>12</v>
+      </c>
+      <c r="K22">
+        <f>2.5+2</f>
+        <v>4.5</v>
+      </c>
+      <c r="N22" s="2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="54"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K23" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="M23" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="O23" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="54"/>
+      <c r="D24" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="22"/>
+      <c r="G24" s="14"/>
+      <c r="J24" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24">
+        <v>4.5</v>
+      </c>
+      <c r="N24" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O24" s="1"/>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B25" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="54"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="14"/>
+      <c r="O25" s="1"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="55"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="6"/>
+      <c r="O26" s="1"/>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="O27" s="1"/>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B28" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="O28" s="1"/>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B29" s="4"/>
+      <c r="C29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O29" s="1"/>
+    </row>
+    <row r="30" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K30" s="1">
+        <f>3+2.5+2+3</f>
+        <v>10.5</v>
+      </c>
+      <c r="M30" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="O30" s="1"/>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="17"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="30"/>
+      <c r="J31" t="s">
+        <v>12</v>
+      </c>
+      <c r="K31">
+        <f>2+2.5+2</f>
+        <v>6.5</v>
+      </c>
+      <c r="N31" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="O31" s="1"/>
+    </row>
+    <row r="32" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="17"/>
+      <c r="E32" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K32" s="1">
+        <v>2</v>
+      </c>
+      <c r="M32" s="10">
+        <v>2</v>
+      </c>
+      <c r="O32" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="37"/>
+      <c r="D33" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="32"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="14"/>
+      <c r="J33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K33" s="1">
+        <v>5</v>
+      </c>
+      <c r="N33" s="2">
+        <v>5</v>
+      </c>
+      <c r="O33" s="1"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B34" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="14"/>
+      <c r="O34" s="1"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="36"/>
+      <c r="G35" s="6"/>
+      <c r="O35" s="1"/>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="O36" s="1"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B37" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O37" s="1"/>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B38" s="4"/>
+      <c r="C38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O38" s="1"/>
+    </row>
+    <row r="39" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K39" s="1">
+        <f>3+2.5</f>
+        <v>5.5</v>
+      </c>
+      <c r="M39" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="O39" s="1"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="14"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="39"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="50"/>
+      <c r="I40" s="1"/>
+      <c r="J40" t="s">
+        <v>12</v>
+      </c>
+      <c r="K40">
+        <v>2.5</v>
+      </c>
+      <c r="N40" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="O40" s="1"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="17"/>
+      <c r="E41" s="39"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="50"/>
+      <c r="I41" s="1"/>
+      <c r="J41" t="s">
+        <v>15</v>
+      </c>
+      <c r="K41">
+        <v>12</v>
+      </c>
+      <c r="M41" s="10">
+        <f>4.5</f>
+        <v>4.5</v>
+      </c>
+      <c r="N41" s="2">
+        <f>2+2.5+5</f>
+        <v>9.5</v>
+      </c>
+      <c r="O41" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="22"/>
+      <c r="D42" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="19"/>
+      <c r="G42" s="50"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" s="22"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="51"/>
+      <c r="K43" s="1">
+        <f>SUM(K3:K41)</f>
+        <v>111</v>
+      </c>
+      <c r="L43" s="1"/>
+      <c r="M43" s="9">
+        <f>SUM(M3:M41)</f>
+        <v>59.5</v>
+      </c>
+      <c r="N43" s="9">
+        <f>SUM(N3:N41)</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="23"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="20"/>
       <c r="G44" s="6"/>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.35">
@@ -3732,897 +4619,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B72F34B-8139-4D0E-8882-03145DDD5E1F}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B1:O54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="10.90625" style="2"/>
-    <col min="3" max="4" width="12.6328125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.7265625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.1796875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="4.36328125" customWidth="1"/>
-    <col min="10" max="10" width="15.7265625" customWidth="1"/>
-    <col min="13" max="14" width="10.90625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B1" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B2" s="4"/>
-      <c r="C2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="1">
-        <f>2.5+2.5+2.5+2.5+2</f>
-        <v>12</v>
-      </c>
-      <c r="M3" s="9">
-        <f>K3</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="28"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="27"/>
-      <c r="I4" s="1"/>
-      <c r="J4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K4">
-        <f>2.5+2.5+2.5</f>
-        <v>7.5</v>
-      </c>
-      <c r="N4" s="2">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5">
-        <f>2.5+2</f>
-        <v>4.5</v>
-      </c>
-      <c r="M5" s="10">
-        <v>1.5</v>
-      </c>
-      <c r="N5" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="26"/>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="26"/>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="5"/>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B10" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B11" s="4"/>
-      <c r="C11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K12" s="1">
-        <f>3+2.5+3+2</f>
-        <v>10.5</v>
-      </c>
-      <c r="M12" s="2">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B13" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="26"/>
-      <c r="J13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="1">
-        <v>3</v>
-      </c>
-      <c r="M13" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B14" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="J14" t="s">
-        <v>12</v>
-      </c>
-      <c r="K14">
-        <f>2+2.5+2+2</f>
-        <v>8.5</v>
-      </c>
-      <c r="N14" s="2">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="33"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="32"/>
-      <c r="J15" t="s">
-        <v>15</v>
-      </c>
-      <c r="K15">
-        <v>2</v>
-      </c>
-      <c r="N15" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B16" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="19"/>
-      <c r="G16" s="32"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="6"/>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B19" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B20" s="4"/>
-      <c r="C20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="F21" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K21" s="1">
-        <f>2.5+3</f>
-        <v>5.5</v>
-      </c>
-      <c r="M21" s="2">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B22" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="47"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="28"/>
-      <c r="I22" s="1"/>
-      <c r="J22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K22">
-        <f>2.5+2</f>
-        <v>4.5</v>
-      </c>
-      <c r="N22" s="2">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="23" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="48"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K23" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="M23" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="O23" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" s="48"/>
-      <c r="D24" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="F24" s="24"/>
-      <c r="G24" s="26"/>
-      <c r="J24" t="s">
-        <v>31</v>
-      </c>
-      <c r="K24">
-        <v>4.5</v>
-      </c>
-      <c r="N24" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="O24" s="1"/>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B25" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="48"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="26"/>
-      <c r="O25" s="1"/>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="49"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="6"/>
-      <c r="O26" s="1"/>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="O27" s="1"/>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B28" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="O28" s="1"/>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B29" s="4"/>
-      <c r="C29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="O29" s="1"/>
-    </row>
-    <row r="30" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="F30" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K30" s="1">
-        <f>3+2.5+2+3</f>
-        <v>10.5</v>
-      </c>
-      <c r="M30" s="2">
-        <v>10.5</v>
-      </c>
-      <c r="O30" s="1"/>
-    </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B31" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" s="15"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="28"/>
-      <c r="J31" t="s">
-        <v>12</v>
-      </c>
-      <c r="K31">
-        <f>2+2.5+2</f>
-        <v>6.5</v>
-      </c>
-      <c r="N31" s="2">
-        <v>6.5</v>
-      </c>
-      <c r="O31" s="1"/>
-    </row>
-    <row r="32" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="15"/>
-      <c r="E32" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="41" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K32" s="1">
-        <v>2</v>
-      </c>
-      <c r="M32" s="10">
-        <v>2</v>
-      </c>
-      <c r="O32" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" s="17"/>
-      <c r="D33" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="39"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="26"/>
-      <c r="J33" t="s">
-        <v>31</v>
-      </c>
-      <c r="K33" s="1">
-        <v>5</v>
-      </c>
-      <c r="N33" s="2">
-        <v>5</v>
-      </c>
-      <c r="O33" s="1"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B34" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="26"/>
-      <c r="O34" s="1"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="6"/>
-      <c r="O35" s="1"/>
-    </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="O36" s="1"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B37" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O37" s="1"/>
-    </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B38" s="4"/>
-      <c r="C38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="O38" s="1"/>
-    </row>
-    <row r="39" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C39" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="G39" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K39" s="1">
-        <f>3+2.5</f>
-        <v>5.5</v>
-      </c>
-      <c r="M39" s="2">
-        <v>5.5</v>
-      </c>
-      <c r="O39" s="1"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B40" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="26"/>
-      <c r="D40" s="37"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="51"/>
-      <c r="I40" s="1"/>
-      <c r="J40" t="s">
-        <v>12</v>
-      </c>
-      <c r="K40">
-        <v>2.5</v>
-      </c>
-      <c r="N40" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="O40" s="1"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41" s="15"/>
-      <c r="E41" s="25"/>
-      <c r="F41" s="35"/>
-      <c r="G41" s="51"/>
-      <c r="I41" s="1"/>
-      <c r="J41" t="s">
-        <v>15</v>
-      </c>
-      <c r="K41">
-        <v>12</v>
-      </c>
-      <c r="M41" s="10">
-        <f>4.5</f>
-        <v>4.5</v>
-      </c>
-      <c r="N41" s="2">
-        <f>2+2.5+5</f>
-        <v>9.5</v>
-      </c>
-      <c r="O41" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C42" s="24"/>
-      <c r="D42" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="35"/>
-      <c r="G42" s="51"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C43" s="24"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="35"/>
-      <c r="G43" s="52"/>
-      <c r="K43" s="1">
-        <f>SUM(K3:K41)</f>
-        <v>111</v>
-      </c>
-      <c r="L43" s="1"/>
-      <c r="M43" s="9">
-        <f>SUM(M3:M41)</f>
-        <v>59.5</v>
-      </c>
-      <c r="N43" s="9">
-        <f>SUM(N3:N41)</f>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C44" s="20"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="26"/>
-      <c r="F44" s="36"/>
-      <c r="G44" s="6"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K46">
-        <f>5*4*5</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K47">
-        <f>4*5</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K48">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="49" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="K49">
-        <f>120-5-4</f>
-        <v>111</v>
-      </c>
-    </row>
-    <row r="50" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J50" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K50" s="1">
-        <f>K3+K12</f>
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="51" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J51" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K51" s="1">
-        <f>K13+K21+K30+K39</f>
-        <v>24.5</v>
-      </c>
-    </row>
-    <row r="52" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J52" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K52" s="1">
-        <f>K4+K14+K22+K31+K40</f>
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="53" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J53" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K53" s="1">
-        <f>K5+K15+K23+K24+K32+K33+K41</f>
-        <v>34.5</v>
-      </c>
-    </row>
-    <row r="54" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="K54">
-        <f>SUM(K50:K53)</f>
-        <v>111</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="47">
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="C21:C26"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1185C20-CB13-4526-80BC-F11E35C8CC5F}">
   <sheetPr>
@@ -4679,19 +4675,19 @@
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="27" t="s">
+      <c r="D3" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="27" t="s">
+      <c r="F3" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="43" t="s">
         <v>18</v>
       </c>
       <c r="I3" s="1"/>
@@ -4711,11 +4707,11 @@
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="27"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="43"/>
       <c r="I4" s="1"/>
       <c r="J4" t="s">
         <v>12</v>
@@ -4732,11 +4728,11 @@
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="26" t="s">
+      <c r="C5" s="43"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="14" t="s">
         <v>22</v>
       </c>
       <c r="J5" t="s">
@@ -4760,38 +4756,38 @@
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="27" t="s">
+      <c r="E6" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="26"/>
+      <c r="G6" s="14"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="26"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="14"/>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.35">
@@ -4821,19 +4817,19 @@
       <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="31" t="s">
+      <c r="C12" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="26" t="s">
+      <c r="F12" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="1"/>
@@ -4852,11 +4848,11 @@
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="26"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="14"/>
       <c r="J13" s="1" t="s">
         <v>14</v>
       </c>
@@ -4871,15 +4867,15 @@
       <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="16" t="s">
+      <c r="D14" s="23"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="42" t="s">
         <v>23</v>
       </c>
       <c r="J14" t="s">
@@ -4897,13 +4893,13 @@
       <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="31" t="s">
+      <c r="C15" s="38"/>
+      <c r="D15" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="33"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="32"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="42"/>
       <c r="J15" t="s">
         <v>15</v>
       </c>
@@ -4918,13 +4914,13 @@
       <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="19"/>
-      <c r="G16" s="32"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="38"/>
+      <c r="G16" s="42"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
@@ -4932,10 +4928,10 @@
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="20"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="23"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.35">
@@ -4965,19 +4961,19 @@
       <c r="B21" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="25" t="s">
+      <c r="C21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="28" t="s">
+      <c r="F21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="30" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="1"/>
@@ -4996,11 +4992,11 @@
       <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="19"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="28"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="30"/>
       <c r="I22" s="1"/>
       <c r="J22" t="s">
         <v>12</v>
@@ -5017,15 +5013,15 @@
       <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="20"/>
-      <c r="D23" s="23" t="s">
+      <c r="C23" s="23"/>
+      <c r="D23" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="25"/>
-      <c r="F23" s="16" t="s">
+      <c r="E23" s="39"/>
+      <c r="F23" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="26" t="s">
+      <c r="G23" s="14" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -5045,15 +5041,15 @@
       <c r="B24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="24"/>
-      <c r="E24" s="26" t="s">
+      <c r="D24" s="22"/>
+      <c r="E24" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="17"/>
-      <c r="G24" s="26"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="14"/>
       <c r="J24" t="s">
         <v>31</v>
       </c>
@@ -5069,21 +5065,21 @@
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="26"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="14"/>
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="18"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="27"/>
       <c r="G26" s="6"/>
       <c r="P26" s="1"/>
     </row>
@@ -5119,19 +5115,19 @@
       <c r="B30" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="16" t="s">
+      <c r="C30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="28" t="s">
+      <c r="F30" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="30" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="1"/>
@@ -5151,11 +5147,11 @@
       <c r="B31" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="37"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="28"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="30"/>
       <c r="J31" t="s">
         <v>12</v>
       </c>
@@ -5172,15 +5168,15 @@
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="38" t="s">
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="41" t="s">
+      <c r="F32" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="26" t="s">
+      <c r="G32" s="14" t="s">
         <v>22</v>
       </c>
       <c r="J32" s="1" t="s">
@@ -5200,15 +5196,15 @@
       <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="16" t="s">
+      <c r="D33" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="39"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="26"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="14"/>
       <c r="J33" t="s">
         <v>31</v>
       </c>
@@ -5224,21 +5220,21 @@
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="26"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="14"/>
       <c r="P34" s="1"/>
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="43"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="36"/>
       <c r="G35" s="6"/>
       <c r="P35" s="1"/>
     </row>
@@ -5274,19 +5270,19 @@
       <c r="B39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="26" t="s">
+      <c r="C39" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="26" t="s">
+      <c r="D39" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F39" s="26" t="s">
+      <c r="E39" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G39" s="34" t="s">
+      <c r="G39" s="18" t="s">
         <v>57</v>
       </c>
       <c r="I39" s="1"/>
@@ -5305,11 +5301,11 @@
       <c r="B40" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="37"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="35"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="19"/>
       <c r="I40" s="1"/>
       <c r="J40" t="s">
         <v>12</v>
@@ -5326,13 +5322,13 @@
       <c r="B41" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C41" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="26"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="35"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="19"/>
       <c r="I41" s="1"/>
       <c r="J41" t="s">
         <v>15</v>
@@ -5355,27 +5351,27 @@
       <c r="B42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="24"/>
-      <c r="D42" s="34" t="s">
+      <c r="C42" s="22"/>
+      <c r="D42" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E42" s="34" t="s">
+      <c r="E42" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="34" t="s">
+      <c r="F42" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="G42" s="35"/>
+      <c r="G42" s="19"/>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="24"/>
-      <c r="D43" s="44"/>
-      <c r="E43" s="44"/>
-      <c r="F43" s="44"/>
-      <c r="G43" s="36"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="20"/>
       <c r="K43" s="1">
         <f>SUM(K3:K41)</f>
         <v>120</v>
@@ -5397,10 +5393,10 @@
       <c r="B44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="20"/>
-      <c r="D44" s="45"/>
-      <c r="E44" s="45"/>
-      <c r="F44" s="45"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="25"/>
+      <c r="F44" s="25"/>
       <c r="G44" s="6"/>
     </row>
     <row r="46" spans="2:16" x14ac:dyDescent="0.35">
@@ -5464,11 +5460,34 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="D23:D26"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
     <mergeCell ref="G21:G22"/>
     <mergeCell ref="G23:G25"/>
     <mergeCell ref="G39:G43"/>
@@ -5485,34 +5504,11 @@
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="D42:D44"/>
     <mergeCell ref="F39:F41"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="D23:D26"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="F42:F44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
